--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="291">
   <si>
     <t>Id</t>
   </si>
@@ -931,6 +931,12 @@
   </si>
   <si>
     <t>湖光月色</t>
+  </si>
+  <si>
+    <t>WJBeta144</t>
+  </si>
+  <si>
+    <t>无尽王国</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1998,7 +2004,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I150"/>
+  <dimension ref="C3:I151"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4616,36 +4622,53 @@
     </row>
     <row r="149" spans="3:7">
       <c r="C149" s="3">
-        <v>202</v>
+        <v>144</v>
       </c>
       <c r="D149" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E149" s="5">
-        <v>202</v>
+        <v>144</v>
       </c>
       <c r="F149" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="G149" s="2" t="s">
+      <c r="G149" s="12" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="150" spans="3:7">
       <c r="C150" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D150" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E150" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F150" s="5" t="s">
         <v>287</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>288</v>
+      </c>
+    </row>
+    <row r="151" spans="3:7">
+      <c r="C151" s="3">
+        <v>203</v>
+      </c>
+      <c r="D151" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E151" s="5">
+        <v>203</v>
+      </c>
+      <c r="F151" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>290</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="292">
   <si>
     <t>Id</t>
   </si>
@@ -937,6 +937,9 @@
   </si>
   <si>
     <t>无尽王国</t>
+  </si>
+  <si>
+    <t>WJBeta145</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2004,7 +2007,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I151"/>
+  <dimension ref="C3:I152"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4639,36 +4642,51 @@
     </row>
     <row r="150" spans="3:7">
       <c r="C150" s="3">
-        <v>202</v>
+        <v>145</v>
       </c>
       <c r="D150" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E150" s="5">
-        <v>202</v>
+        <v>145</v>
       </c>
       <c r="F150" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="G150" s="2" t="s">
-        <v>288</v>
-      </c>
+      <c r="G150" s="12"/>
     </row>
     <row r="151" spans="3:7">
       <c r="C151" s="3">
+        <v>202</v>
+      </c>
+      <c r="D151" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E151" s="5">
+        <v>202</v>
+      </c>
+      <c r="F151" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="152" spans="3:7">
+      <c r="C152" s="3">
         <v>203</v>
       </c>
-      <c r="D151" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E151" s="5">
+      <c r="D152" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E152" s="5">
         <v>203</v>
       </c>
-      <c r="F151" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="G151" s="2" t="s">
+      <c r="F152" s="5" t="s">
         <v>290</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>291</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="294">
   <si>
     <t>Id</t>
   </si>
@@ -940,6 +940,12 @@
   </si>
   <si>
     <t>WJBeta145</t>
+  </si>
+  <si>
+    <t>一统山河</t>
+  </si>
+  <si>
+    <t>WJBeta146</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2007,7 +2013,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I152"/>
+  <dimension ref="C3:I153"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4653,40 +4659,57 @@
       <c r="F150" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="G150" s="12"/>
+      <c r="G150" s="12" t="s">
+        <v>288</v>
+      </c>
     </row>
     <row r="151" spans="3:7">
       <c r="C151" s="3">
-        <v>202</v>
+        <v>146</v>
       </c>
       <c r="D151" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E151" s="5">
-        <v>202</v>
+        <v>146</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="G151" s="2" t="s">
         <v>289</v>
       </c>
+      <c r="G151" s="12"/>
     </row>
     <row r="152" spans="3:7">
       <c r="C152" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D152" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E152" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F152" s="5" t="s">
         <v>290</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>291</v>
+      </c>
+    </row>
+    <row r="153" spans="3:7">
+      <c r="C153" s="3">
+        <v>203</v>
+      </c>
+      <c r="D153" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E153" s="5">
+        <v>203</v>
+      </c>
+      <c r="F153" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>293</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="295">
   <si>
     <t>Id</t>
   </si>
@@ -946,6 +946,9 @@
   </si>
   <si>
     <t>WJBeta146</t>
+  </si>
+  <si>
+    <t>星辰坠落</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -4676,7 +4679,9 @@
       <c r="F151" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="G151" s="12"/>
+      <c r="G151" s="12" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="152" spans="3:7">
       <c r="C152" s="3">
@@ -4689,10 +4694,10 @@
         <v>202</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="153" spans="3:7">
@@ -4706,10 +4711,10 @@
         <v>203</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="296">
   <si>
     <t>Id</t>
   </si>
@@ -949,6 +949,9 @@
   </si>
   <si>
     <t>星辰坠落</t>
+  </si>
+  <si>
+    <t>WJBeta147</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2016,7 +2019,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I153"/>
+  <dimension ref="C3:I154"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4685,36 +4688,53 @@
     </row>
     <row r="152" spans="3:7">
       <c r="C152" s="3">
-        <v>202</v>
+        <v>147</v>
       </c>
       <c r="D152" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E152" s="5">
-        <v>202</v>
+        <v>147</v>
       </c>
       <c r="F152" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="G152" s="2" t="s">
-        <v>292</v>
+      <c r="G152" s="12" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="153" spans="3:7">
       <c r="C153" s="3">
+        <v>202</v>
+      </c>
+      <c r="D153" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E153" s="5">
+        <v>202</v>
+      </c>
+      <c r="F153" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="154" spans="3:7">
+      <c r="C154" s="3">
         <v>203</v>
       </c>
-      <c r="D153" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E153" s="5">
+      <c r="D154" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E154" s="5">
         <v>203</v>
       </c>
-      <c r="F153" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="G153" s="2" t="s">
+      <c r="F154" s="5" t="s">
         <v>294</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>295</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="297">
   <si>
     <t>Id</t>
   </si>
@@ -952,6 +952,9 @@
   </si>
   <si>
     <t>WJBeta147</t>
+  </si>
+  <si>
+    <t>WJBeta148</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2019,7 +2022,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I154"/>
+  <dimension ref="C3:I155"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4705,36 +4708,51 @@
     </row>
     <row r="153" spans="3:7">
       <c r="C153" s="3">
-        <v>202</v>
+        <v>148</v>
       </c>
       <c r="D153" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E153" s="5">
-        <v>202</v>
+        <v>148</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="G153" s="2" t="s">
-        <v>293</v>
-      </c>
+      <c r="G153" s="12"/>
     </row>
     <row r="154" spans="3:7">
       <c r="C154" s="3">
+        <v>202</v>
+      </c>
+      <c r="D154" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E154" s="5">
+        <v>202</v>
+      </c>
+      <c r="F154" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="155" spans="3:7">
+      <c r="C155" s="3">
         <v>203</v>
       </c>
-      <c r="D154" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E154" s="5">
+      <c r="D155" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E155" s="5">
         <v>203</v>
       </c>
-      <c r="F154" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="G154" s="2" t="s">
+      <c r="F155" s="5" t="s">
         <v>295</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>296</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="298">
   <si>
     <t>Id</t>
   </si>
@@ -955,6 +955,9 @@
   </si>
   <si>
     <t>WJBeta148</t>
+  </si>
+  <si>
+    <t>威震天下</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1163,12 +1166,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4497,7 +4500,7 @@
       <c r="G140" t="s">
         <v>271</v>
       </c>
-      <c r="H140" s="11"/>
+      <c r="H140" s="6"/>
     </row>
     <row r="141" spans="3:8">
       <c r="C141" s="3">
@@ -4515,7 +4518,7 @@
       <c r="G141" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="H141" s="11"/>
+      <c r="H141" s="6"/>
     </row>
     <row r="142" spans="3:8">
       <c r="C142" s="3">
@@ -4525,7 +4528,7 @@
         <v>9</v>
       </c>
       <c r="E142" s="5">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F142" s="5" t="s">
         <v>274</v>
@@ -4533,7 +4536,7 @@
       <c r="G142" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="H142" s="10"/>
+      <c r="H142" s="6"/>
     </row>
     <row r="143" spans="3:8">
       <c r="C143" s="3">
@@ -4543,7 +4546,7 @@
         <v>9</v>
       </c>
       <c r="E143" s="5">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F143" s="5" t="s">
         <v>276</v>
@@ -4551,9 +4554,9 @@
       <c r="G143" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="H143" s="10"/>
-    </row>
-    <row r="144" spans="3:7">
+      <c r="H143" s="6"/>
+    </row>
+    <row r="144" spans="3:8">
       <c r="C144" s="3">
         <v>139</v>
       </c>
@@ -4569,8 +4572,9 @@
       <c r="G144" s="12" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="145" spans="3:7">
+      <c r="H144" s="11"/>
+    </row>
+    <row r="145" spans="3:8">
       <c r="C145" s="3">
         <v>140</v>
       </c>
@@ -4578,7 +4582,7 @@
         <v>9</v>
       </c>
       <c r="E145" s="5">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>280</v>
@@ -4586,8 +4590,9 @@
       <c r="G145" s="12" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="146" spans="3:7">
+      <c r="H145" s="11"/>
+    </row>
+    <row r="146" spans="3:8">
       <c r="C146" s="3">
         <v>141</v>
       </c>
@@ -4603,8 +4608,9 @@
       <c r="G146" s="12" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="147" spans="3:7">
+      <c r="H146" s="10"/>
+    </row>
+    <row r="147" spans="3:8">
       <c r="C147" s="3">
         <v>142</v>
       </c>
@@ -4612,7 +4618,7 @@
         <v>9</v>
       </c>
       <c r="E147" s="5">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F147" s="5" t="s">
         <v>282</v>
@@ -4620,6 +4626,7 @@
       <c r="G147" s="12" t="s">
         <v>36</v>
       </c>
+      <c r="H147" s="10"/>
     </row>
     <row r="148" spans="3:7">
       <c r="C148" s="3">
@@ -4719,7 +4726,9 @@
       <c r="F153" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="G153" s="12"/>
+      <c r="G153" s="12" t="s">
+        <v>293</v>
+      </c>
     </row>
     <row r="154" spans="3:7">
       <c r="C154" s="3">
@@ -4732,10 +4741,10 @@
         <v>202</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="155" spans="3:7">
@@ -4749,10 +4758,10 @@
         <v>203</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="300">
   <si>
     <t>Id</t>
   </si>
@@ -958,6 +958,12 @@
   </si>
   <si>
     <t>威震天下</t>
+  </si>
+  <si>
+    <t>WJBeta149</t>
+  </si>
+  <si>
+    <t>春暖花开</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1166,12 +1172,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2025,7 +2031,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I155"/>
+  <dimension ref="C3:I156"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4732,36 +4738,53 @@
     </row>
     <row r="154" spans="3:7">
       <c r="C154" s="3">
-        <v>202</v>
+        <v>149</v>
       </c>
       <c r="D154" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E154" s="5">
-        <v>202</v>
+        <v>149</v>
       </c>
       <c r="F154" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="G154" s="2" t="s">
+      <c r="G154" s="12" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="155" spans="3:7">
       <c r="C155" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D155" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E155" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F155" s="5" t="s">
         <v>296</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>297</v>
+      </c>
+    </row>
+    <row r="156" spans="3:7">
+      <c r="C156" s="3">
+        <v>203</v>
+      </c>
+      <c r="D156" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E156" s="5">
+        <v>203</v>
+      </c>
+      <c r="F156" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>299</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="302">
   <si>
     <t>Id</t>
   </si>
@@ -964,6 +964,12 @@
   </si>
   <si>
     <t>春暖花开</t>
+  </si>
+  <si>
+    <t>WJBeta150</t>
+  </si>
+  <si>
+    <t>破晓之战</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2031,7 +2037,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I156"/>
+  <dimension ref="C3:I157"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4254,7 +4260,7 @@
       <c r="G126" t="s">
         <v>244</v>
       </c>
-      <c r="H126" s="11"/>
+      <c r="H126" s="6"/>
     </row>
     <row r="127" spans="3:8">
       <c r="C127" s="3">
@@ -4272,7 +4278,7 @@
       <c r="G127" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="H127" s="11"/>
+      <c r="H127" s="6"/>
     </row>
     <row r="128" spans="3:8">
       <c r="C128" s="3">
@@ -4290,7 +4296,7 @@
       <c r="G128" t="s">
         <v>247</v>
       </c>
-      <c r="H128" s="11"/>
+      <c r="H128" s="6"/>
     </row>
     <row r="129" spans="3:8">
       <c r="C129" s="3">
@@ -4308,7 +4314,7 @@
       <c r="G129" t="s">
         <v>249</v>
       </c>
-      <c r="H129" s="11"/>
+      <c r="H129" s="6"/>
     </row>
     <row r="130" spans="3:8">
       <c r="C130" s="3">
@@ -4318,7 +4324,7 @@
         <v>9</v>
       </c>
       <c r="E130" s="5">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F130" s="5" t="s">
         <v>250</v>
@@ -4336,7 +4342,7 @@
         <v>9</v>
       </c>
       <c r="E131" s="5">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F131" s="5" t="s">
         <v>252</v>
@@ -4354,7 +4360,7 @@
         <v>9</v>
       </c>
       <c r="E132" s="5">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F132" s="5" t="s">
         <v>254</v>
@@ -4390,7 +4396,7 @@
         <v>9</v>
       </c>
       <c r="E134" s="5">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F134" s="5" t="s">
         <v>258</v>
@@ -4408,7 +4414,7 @@
         <v>9</v>
       </c>
       <c r="E135" s="5">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F135" s="5" t="s">
         <v>260</v>
@@ -4634,7 +4640,7 @@
       </c>
       <c r="H147" s="10"/>
     </row>
-    <row r="148" spans="3:7">
+    <row r="148" spans="3:8">
       <c r="C148" s="3">
         <v>143</v>
       </c>
@@ -4650,8 +4656,9 @@
       <c r="G148" s="12" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="149" spans="3:7">
+      <c r="H148" s="6"/>
+    </row>
+    <row r="149" spans="3:8">
       <c r="C149" s="3">
         <v>144</v>
       </c>
@@ -4659,7 +4666,7 @@
         <v>9</v>
       </c>
       <c r="E149" s="5">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F149" s="5" t="s">
         <v>285</v>
@@ -4667,8 +4674,9 @@
       <c r="G149" s="12" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="150" spans="3:7">
+      <c r="H149" s="6"/>
+    </row>
+    <row r="150" spans="3:8">
       <c r="C150" s="3">
         <v>145</v>
       </c>
@@ -4684,8 +4692,9 @@
       <c r="G150" s="12" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="151" spans="3:7">
+      <c r="H150" s="8"/>
+    </row>
+    <row r="151" spans="3:8">
       <c r="C151" s="3">
         <v>146</v>
       </c>
@@ -4693,7 +4702,7 @@
         <v>9</v>
       </c>
       <c r="E151" s="5">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F151" s="5" t="s">
         <v>289</v>
@@ -4701,6 +4710,7 @@
       <c r="G151" s="12" t="s">
         <v>290</v>
       </c>
+      <c r="H151" s="8"/>
     </row>
     <row r="152" spans="3:7">
       <c r="C152" s="3">
@@ -4755,36 +4765,53 @@
     </row>
     <row r="155" spans="3:7">
       <c r="C155" s="3">
-        <v>202</v>
+        <v>150</v>
       </c>
       <c r="D155" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E155" s="5">
-        <v>202</v>
+        <v>150</v>
       </c>
       <c r="F155" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="G155" s="2" t="s">
+      <c r="G155" s="12" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="156" spans="3:7">
       <c r="C156" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D156" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E156" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F156" s="5" t="s">
         <v>298</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>299</v>
+      </c>
+    </row>
+    <row r="157" spans="3:7">
+      <c r="C157" s="3">
+        <v>203</v>
+      </c>
+      <c r="D157" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E157" s="5">
+        <v>203</v>
+      </c>
+      <c r="F157" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>301</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="304">
   <si>
     <t>Id</t>
   </si>
@@ -970,6 +970,12 @@
   </si>
   <si>
     <t>破晓之战</t>
+  </si>
+  <si>
+    <t>WJBeta151</t>
+  </si>
+  <si>
+    <t>龙裔国度</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1178,12 +1184,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1667,7 +1673,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1688,6 +1694,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -2037,7 +2044,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I157"/>
+  <dimension ref="C3:I158"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4782,36 +4789,53 @@
     </row>
     <row r="156" spans="3:7">
       <c r="C156" s="3">
-        <v>202</v>
+        <v>151</v>
       </c>
       <c r="D156" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E156" s="5">
-        <v>202</v>
+        <v>151</v>
       </c>
       <c r="F156" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="G156" s="2" t="s">
+      <c r="G156" s="13" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="157" spans="3:7">
       <c r="C157" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D157" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E157" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F157" s="5" t="s">
         <v>300</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>301</v>
+      </c>
+    </row>
+    <row r="158" spans="3:7">
+      <c r="C158" s="3">
+        <v>203</v>
+      </c>
+      <c r="D158" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E158" s="5">
+        <v>203</v>
+      </c>
+      <c r="F158" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>303</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="306">
   <si>
     <t>Id</t>
   </si>
@@ -976,6 +976,12 @@
   </si>
   <si>
     <t>龙裔国度</t>
+  </si>
+  <si>
+    <t>WJBeta152</t>
+  </si>
+  <si>
+    <t>秘境森林</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1184,12 +1190,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1673,7 +1679,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1694,7 +1700,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -2044,7 +2049,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I158"/>
+  <dimension ref="C3:I159"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4800,42 +4805,59 @@
       <c r="F156" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="G156" s="13" t="s">
+      <c r="G156" s="12" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="157" spans="3:7">
       <c r="C157" s="3">
-        <v>202</v>
+        <v>152</v>
       </c>
       <c r="D157" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E157" s="5">
-        <v>202</v>
+        <v>152</v>
       </c>
       <c r="F157" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="G157" s="2" t="s">
+      <c r="G157" s="12" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="158" spans="3:7">
       <c r="C158" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D158" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E158" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F158" s="5" t="s">
         <v>302</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>303</v>
+      </c>
+    </row>
+    <row r="159" spans="3:7">
+      <c r="C159" s="3">
+        <v>203</v>
+      </c>
+      <c r="D159" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E159" s="5">
+        <v>203</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="308">
   <si>
     <t>Id</t>
   </si>
@@ -982,6 +982,12 @@
   </si>
   <si>
     <t>秘境森林</t>
+  </si>
+  <si>
+    <t>WJBeta153</t>
+  </si>
+  <si>
+    <t>荣耀之路</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2049,7 +2055,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I159"/>
+  <dimension ref="C3:I160"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4828,36 +4834,53 @@
     </row>
     <row r="158" spans="3:7">
       <c r="C158" s="3">
-        <v>202</v>
+        <v>153</v>
       </c>
       <c r="D158" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E158" s="5">
-        <v>202</v>
+        <v>153</v>
       </c>
       <c r="F158" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="G158" s="2" t="s">
+      <c r="G158" s="12" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="159" spans="3:7">
       <c r="C159" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D159" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E159" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F159" s="5" t="s">
         <v>304</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>305</v>
+      </c>
+    </row>
+    <row r="160" spans="3:7">
+      <c r="C160" s="3">
+        <v>203</v>
+      </c>
+      <c r="D160" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E160" s="5">
+        <v>203</v>
+      </c>
+      <c r="F160" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>307</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="310">
   <si>
     <t>Id</t>
   </si>
@@ -988,6 +988,12 @@
   </si>
   <si>
     <t>荣耀之路</t>
+  </si>
+  <si>
+    <t>WJBeta154</t>
+  </si>
+  <si>
+    <t>龙息之境</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2055,7 +2061,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I160"/>
+  <dimension ref="C3:I161"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4851,36 +4857,53 @@
     </row>
     <row r="159" spans="3:7">
       <c r="C159" s="3">
-        <v>202</v>
+        <v>154</v>
       </c>
       <c r="D159" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E159" s="5">
-        <v>202</v>
+        <v>154</v>
       </c>
       <c r="F159" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="G159" s="2" t="s">
+      <c r="G159" s="12" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="160" spans="3:7">
       <c r="C160" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D160" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E160" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F160" s="5" t="s">
         <v>306</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>307</v>
+      </c>
+    </row>
+    <row r="161" spans="3:7">
+      <c r="C161" s="3">
+        <v>203</v>
+      </c>
+      <c r="D161" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E161" s="5">
+        <v>203</v>
+      </c>
+      <c r="F161" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>309</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="312">
   <si>
     <t>Id</t>
   </si>
@@ -994,6 +994,12 @@
   </si>
   <si>
     <t>龙息之境</t>
+  </si>
+  <si>
+    <t>WJBeta155</t>
+  </si>
+  <si>
+    <t>雷霆万钧</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1691,7 +1697,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1712,6 +1718,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -2061,7 +2068,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I161"/>
+  <dimension ref="C3:I162"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4874,36 +4881,53 @@
     </row>
     <row r="160" spans="3:7">
       <c r="C160" s="3">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="D160" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E160" s="5">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="F160" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="G160" s="2" t="s">
+      <c r="G160" s="13" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="161" spans="3:7">
       <c r="C161" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D161" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E161" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F161" s="5" t="s">
         <v>308</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>309</v>
+      </c>
+    </row>
+    <row r="162" spans="3:7">
+      <c r="C162" s="3">
+        <v>203</v>
+      </c>
+      <c r="D162" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E162" s="5">
+        <v>203</v>
+      </c>
+      <c r="F162" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>311</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="314">
   <si>
     <t>Id</t>
   </si>
@@ -1000,6 +1000,12 @@
   </si>
   <si>
     <t>雷霆万钧</t>
+  </si>
+  <si>
+    <t>WJBeta156</t>
+  </si>
+  <si>
+    <t>龙翔九天</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2068,7 +2074,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I162"/>
+  <dimension ref="C3:I163"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4892,42 +4898,59 @@
       <c r="F160" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="G160" s="13" t="s">
+      <c r="G160" s="12" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="161" spans="3:7">
       <c r="C161" s="3">
-        <v>202</v>
+        <v>156</v>
       </c>
       <c r="D161" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E161" s="5">
-        <v>202</v>
+        <v>156</v>
       </c>
       <c r="F161" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="G161" s="2" t="s">
+      <c r="G161" s="13" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="162" spans="3:7">
       <c r="C162" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D162" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E162" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F162" s="5" t="s">
         <v>310</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>311</v>
+      </c>
+    </row>
+    <row r="163" spans="3:7">
+      <c r="C163" s="3">
+        <v>203</v>
+      </c>
+      <c r="D163" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E163" s="5">
+        <v>203</v>
+      </c>
+      <c r="F163" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>313</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="316">
   <si>
     <t>Id</t>
   </si>
@@ -1006,6 +1006,12 @@
   </si>
   <si>
     <t>龙翔九天</t>
+  </si>
+  <si>
+    <t>WJBeta157</t>
+  </si>
+  <si>
+    <t>神谕森林</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1725,7 +1731,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2074,7 +2080,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I163"/>
+  <dimension ref="C3:I164"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4621,7 +4627,7 @@
       <c r="G144" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="H144" s="11"/>
+      <c r="H144" s="13"/>
     </row>
     <row r="145" spans="3:8">
       <c r="C145" s="3">
@@ -4639,7 +4645,7 @@
       <c r="G145" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="H145" s="11"/>
+      <c r="H145" s="13"/>
     </row>
     <row r="146" spans="3:8">
       <c r="C146" s="3">
@@ -4649,7 +4655,7 @@
         <v>9</v>
       </c>
       <c r="E146" s="5">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F146" s="5" t="s">
         <v>281</v>
@@ -4657,7 +4663,7 @@
       <c r="G146" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="H146" s="10"/>
+      <c r="H146" s="13"/>
     </row>
     <row r="147" spans="3:8">
       <c r="C147" s="3">
@@ -4667,7 +4673,7 @@
         <v>9</v>
       </c>
       <c r="E147" s="5">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F147" s="5" t="s">
         <v>282</v>
@@ -4675,7 +4681,7 @@
       <c r="G147" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="H147" s="10"/>
+      <c r="H147" s="13"/>
     </row>
     <row r="148" spans="3:8">
       <c r="C148" s="3">
@@ -4721,7 +4727,7 @@
         <v>9</v>
       </c>
       <c r="E150" s="5">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F150" s="5" t="s">
         <v>287</v>
@@ -4729,7 +4735,7 @@
       <c r="G150" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="H150" s="8"/>
+      <c r="H150" s="6"/>
     </row>
     <row r="151" spans="3:8">
       <c r="C151" s="3">
@@ -4739,7 +4745,7 @@
         <v>9</v>
       </c>
       <c r="E151" s="5">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F151" s="5" t="s">
         <v>289</v>
@@ -4747,9 +4753,9 @@
       <c r="G151" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="H151" s="8"/>
-    </row>
-    <row r="152" spans="3:7">
+      <c r="H151" s="6"/>
+    </row>
+    <row r="152" spans="3:8">
       <c r="C152" s="3">
         <v>147</v>
       </c>
@@ -4765,8 +4771,9 @@
       <c r="G152" s="12" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="153" spans="3:7">
+      <c r="H152" s="8"/>
+    </row>
+    <row r="153" spans="3:8">
       <c r="C153" s="3">
         <v>148</v>
       </c>
@@ -4774,7 +4781,7 @@
         <v>9</v>
       </c>
       <c r="E153" s="5">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>292</v>
@@ -4782,8 +4789,9 @@
       <c r="G153" s="12" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="154" spans="3:7">
+      <c r="H153" s="8"/>
+    </row>
+    <row r="154" spans="3:8">
       <c r="C154" s="3">
         <v>149</v>
       </c>
@@ -4799,8 +4807,9 @@
       <c r="G154" s="12" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="155" spans="3:7">
+      <c r="H154" s="6"/>
+    </row>
+    <row r="155" spans="3:8">
       <c r="C155" s="3">
         <v>150</v>
       </c>
@@ -4808,7 +4817,7 @@
         <v>9</v>
       </c>
       <c r="E155" s="5">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F155" s="5" t="s">
         <v>296</v>
@@ -4816,6 +4825,7 @@
       <c r="G155" s="12" t="s">
         <v>297</v>
       </c>
+      <c r="H155" s="6"/>
     </row>
     <row r="156" spans="3:7">
       <c r="C156" s="3">
@@ -4915,42 +4925,59 @@
       <c r="F161" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="G161" s="13" t="s">
+      <c r="G161" s="12" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="162" spans="3:7">
       <c r="C162" s="3">
-        <v>202</v>
+        <v>157</v>
       </c>
       <c r="D162" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E162" s="5">
-        <v>202</v>
+        <v>157</v>
       </c>
       <c r="F162" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="G162" s="2" t="s">
+      <c r="G162" s="12" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="163" spans="3:7">
       <c r="C163" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D163" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E163" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F163" s="5" t="s">
         <v>312</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>313</v>
+      </c>
+    </row>
+    <row r="164" spans="3:7">
+      <c r="C164" s="3">
+        <v>203</v>
+      </c>
+      <c r="D164" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E164" s="5">
+        <v>203</v>
+      </c>
+      <c r="F164" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>315</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="318">
   <si>
     <t>Id</t>
   </si>
@@ -1012,6 +1012,12 @@
   </si>
   <si>
     <t>神谕森林</t>
+  </si>
+  <si>
+    <t>WJBeta158</t>
+  </si>
+  <si>
+    <t>泰坦神殿</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2080,7 +2086,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I164"/>
+  <dimension ref="C3:I165"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -3727,7 +3733,7 @@
       <c r="G94" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="H94" s="11"/>
+      <c r="H94" s="10"/>
     </row>
     <row r="95" spans="3:8">
       <c r="C95" s="3">
@@ -3745,7 +3751,7 @@
       <c r="G95" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="H95" s="11"/>
+      <c r="H95" s="10"/>
     </row>
     <row r="96" spans="3:8">
       <c r="C96" s="3">
@@ -3763,7 +3769,7 @@
       <c r="G96" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="H96" s="11"/>
+      <c r="H96" s="10"/>
     </row>
     <row r="97" spans="3:8">
       <c r="C97" s="3">
@@ -3781,7 +3787,7 @@
       <c r="G97" t="s">
         <v>186</v>
       </c>
-      <c r="H97" s="11"/>
+      <c r="H97" s="10"/>
     </row>
     <row r="98" spans="3:8">
       <c r="C98" s="3">
@@ -3799,7 +3805,7 @@
       <c r="G98" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="H98" s="11"/>
+      <c r="H98" s="10"/>
     </row>
     <row r="99" spans="3:8">
       <c r="C99" s="3">
@@ -3817,7 +3823,7 @@
       <c r="G99" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="H99" s="11"/>
+      <c r="H99" s="10"/>
     </row>
     <row r="100" spans="3:8">
       <c r="C100" s="3">
@@ -3835,7 +3841,7 @@
       <c r="G100" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="H100" s="11"/>
+      <c r="H100" s="10"/>
     </row>
     <row r="101" spans="3:8">
       <c r="C101" s="3">
@@ -3853,7 +3859,7 @@
       <c r="G101" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="H101" s="11"/>
+      <c r="H101" s="10"/>
     </row>
     <row r="102" spans="3:8">
       <c r="C102" s="3">
@@ -3863,7 +3869,7 @@
         <v>9</v>
       </c>
       <c r="E102" s="5">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F102" s="5" t="s">
         <v>195</v>
@@ -3871,7 +3877,7 @@
       <c r="G102" t="s">
         <v>196</v>
       </c>
-      <c r="H102" s="6"/>
+      <c r="H102" s="10"/>
     </row>
     <row r="103" spans="3:8">
       <c r="C103" s="3">
@@ -3881,7 +3887,7 @@
         <v>9</v>
       </c>
       <c r="E103" s="5">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F103" s="5" t="s">
         <v>197</v>
@@ -3889,7 +3895,7 @@
       <c r="G103" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="H103" s="6"/>
+      <c r="H103" s="10"/>
     </row>
     <row r="104" spans="3:8">
       <c r="C104" s="3">
@@ -3899,7 +3905,7 @@
         <v>9</v>
       </c>
       <c r="E104" s="5">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F104" s="5" t="s">
         <v>199</v>
@@ -3907,7 +3913,7 @@
       <c r="G104" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="H104" s="6"/>
+      <c r="H104" s="10"/>
     </row>
     <row r="105" spans="3:8">
       <c r="C105" s="3">
@@ -3917,7 +3923,7 @@
         <v>9</v>
       </c>
       <c r="E105" s="5">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F105" s="5" t="s">
         <v>201</v>
@@ -3925,7 +3931,7 @@
       <c r="G105" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="H105" s="6"/>
+      <c r="H105" s="10"/>
     </row>
     <row r="106" spans="3:8">
       <c r="C106" s="3">
@@ -3935,7 +3941,7 @@
         <v>9</v>
       </c>
       <c r="E106" s="5">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F106" s="5" t="s">
         <v>203</v>
@@ -3943,7 +3949,7 @@
       <c r="G106" t="s">
         <v>204</v>
       </c>
-      <c r="H106" s="6"/>
+      <c r="H106" s="10"/>
     </row>
     <row r="107" spans="3:8">
       <c r="C107" s="3">
@@ -3953,7 +3959,7 @@
         <v>9</v>
       </c>
       <c r="E107" s="5">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F107" s="5" t="s">
         <v>205</v>
@@ -3961,7 +3967,7 @@
       <c r="G107" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="H107" s="6"/>
+      <c r="H107" s="10"/>
     </row>
     <row r="108" spans="3:8">
       <c r="C108" s="3">
@@ -3971,7 +3977,7 @@
         <v>9</v>
       </c>
       <c r="E108" s="5">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F108" s="5" t="s">
         <v>207</v>
@@ -3979,7 +3985,7 @@
       <c r="G108" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="H108" s="6"/>
+      <c r="H108" s="10"/>
     </row>
     <row r="109" spans="3:8">
       <c r="C109" s="3">
@@ -3989,7 +3995,7 @@
         <v>9</v>
       </c>
       <c r="E109" s="5">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F109" s="5" t="s">
         <v>209</v>
@@ -3997,7 +4003,7 @@
       <c r="G109" t="s">
         <v>210</v>
       </c>
-      <c r="H109" s="6"/>
+      <c r="H109" s="10"/>
     </row>
     <row r="110" spans="3:8">
       <c r="C110" s="3">
@@ -4151,7 +4157,7 @@
         <v>9</v>
       </c>
       <c r="E118" s="5">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F118" s="5" t="s">
         <v>227</v>
@@ -4159,7 +4165,7 @@
       <c r="G118" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="H118" s="10"/>
+      <c r="H118" s="11"/>
     </row>
     <row r="119" spans="3:8">
       <c r="C119" s="3">
@@ -4169,7 +4175,7 @@
         <v>9</v>
       </c>
       <c r="E119" s="5">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F119" s="5" t="s">
         <v>229</v>
@@ -4177,7 +4183,7 @@
       <c r="G119" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="H119" s="10"/>
+      <c r="H119" s="11"/>
     </row>
     <row r="120" spans="3:8">
       <c r="C120" s="3">
@@ -4187,7 +4193,7 @@
         <v>9</v>
       </c>
       <c r="E120" s="5">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F120" s="5" t="s">
         <v>231</v>
@@ -4195,7 +4201,7 @@
       <c r="G120" t="s">
         <v>232</v>
       </c>
-      <c r="H120" s="10"/>
+      <c r="H120" s="11"/>
     </row>
     <row r="121" spans="3:8">
       <c r="C121" s="3">
@@ -4205,7 +4211,7 @@
         <v>9</v>
       </c>
       <c r="E121" s="5">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F121" s="5" t="s">
         <v>233</v>
@@ -4213,7 +4219,7 @@
       <c r="G121" t="s">
         <v>234</v>
       </c>
-      <c r="H121" s="10"/>
+      <c r="H121" s="11"/>
     </row>
     <row r="122" spans="3:8">
       <c r="C122" s="3">
@@ -4223,7 +4229,7 @@
         <v>9</v>
       </c>
       <c r="E122" s="5">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F122" s="5" t="s">
         <v>235</v>
@@ -4231,7 +4237,7 @@
       <c r="G122" t="s">
         <v>236</v>
       </c>
-      <c r="H122" s="10"/>
+      <c r="H122" s="11"/>
     </row>
     <row r="123" spans="3:8">
       <c r="C123" s="3">
@@ -4241,7 +4247,7 @@
         <v>9</v>
       </c>
       <c r="E123" s="5">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F123" s="5" t="s">
         <v>237</v>
@@ -4249,7 +4255,7 @@
       <c r="G123" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="H123" s="10"/>
+      <c r="H123" s="11"/>
     </row>
     <row r="124" spans="3:8">
       <c r="C124" s="3">
@@ -4259,7 +4265,7 @@
         <v>9</v>
       </c>
       <c r="E124" s="5">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F124" s="5" t="s">
         <v>239</v>
@@ -4267,7 +4273,7 @@
       <c r="G124" t="s">
         <v>240</v>
       </c>
-      <c r="H124" s="10"/>
+      <c r="H124" s="11"/>
     </row>
     <row r="125" spans="3:8">
       <c r="C125" s="3">
@@ -4277,7 +4283,7 @@
         <v>9</v>
       </c>
       <c r="E125" s="5">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F125" s="5" t="s">
         <v>241</v>
@@ -4285,7 +4291,7 @@
       <c r="G125" t="s">
         <v>242</v>
       </c>
-      <c r="H125" s="10"/>
+      <c r="H125" s="11"/>
     </row>
     <row r="126" spans="3:8">
       <c r="C126" s="3">
@@ -4547,7 +4553,7 @@
         <v>9</v>
       </c>
       <c r="E140" s="5">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F140" s="5" t="s">
         <v>270</v>
@@ -4555,7 +4561,7 @@
       <c r="G140" t="s">
         <v>271</v>
       </c>
-      <c r="H140" s="6"/>
+      <c r="H140" s="10"/>
     </row>
     <row r="141" spans="3:8">
       <c r="C141" s="3">
@@ -4565,7 +4571,7 @@
         <v>9</v>
       </c>
       <c r="E141" s="5">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F141" s="5" t="s">
         <v>272</v>
@@ -4573,7 +4579,7 @@
       <c r="G141" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="H141" s="6"/>
+      <c r="H141" s="10"/>
     </row>
     <row r="142" spans="3:8">
       <c r="C142" s="3">
@@ -4583,7 +4589,7 @@
         <v>9</v>
       </c>
       <c r="E142" s="5">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F142" s="5" t="s">
         <v>274</v>
@@ -4591,7 +4597,7 @@
       <c r="G142" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="H142" s="6"/>
+      <c r="H142" s="10"/>
     </row>
     <row r="143" spans="3:8">
       <c r="C143" s="3">
@@ -4601,7 +4607,7 @@
         <v>9</v>
       </c>
       <c r="E143" s="5">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F143" s="5" t="s">
         <v>276</v>
@@ -4609,7 +4615,7 @@
       <c r="G143" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="H143" s="6"/>
+      <c r="H143" s="10"/>
     </row>
     <row r="144" spans="3:8">
       <c r="C144" s="3">
@@ -4827,7 +4833,7 @@
       </c>
       <c r="H155" s="6"/>
     </row>
-    <row r="156" spans="3:7">
+    <row r="156" spans="3:8">
       <c r="C156" s="3">
         <v>151</v>
       </c>
@@ -4843,8 +4849,9 @@
       <c r="G156" s="12" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="157" spans="3:7">
+      <c r="H156" s="10"/>
+    </row>
+    <row r="157" spans="3:8">
       <c r="C157" s="3">
         <v>152</v>
       </c>
@@ -4852,7 +4859,7 @@
         <v>9</v>
       </c>
       <c r="E157" s="5">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F157" s="5" t="s">
         <v>300</v>
@@ -4860,6 +4867,7 @@
       <c r="G157" s="12" t="s">
         <v>301</v>
       </c>
+      <c r="H157" s="10"/>
     </row>
     <row r="158" spans="3:7">
       <c r="C158" s="3">
@@ -4948,36 +4956,53 @@
     </row>
     <row r="163" spans="3:7">
       <c r="C163" s="3">
-        <v>202</v>
+        <v>158</v>
       </c>
       <c r="D163" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E163" s="5">
-        <v>202</v>
+        <v>158</v>
       </c>
       <c r="F163" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="G163" s="2" t="s">
+      <c r="G163" s="12" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="164" spans="3:7">
       <c r="C164" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D164" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E164" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F164" s="5" t="s">
         <v>314</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>315</v>
+      </c>
+    </row>
+    <row r="165" spans="3:7">
+      <c r="C165" s="3">
+        <v>203</v>
+      </c>
+      <c r="D165" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E165" s="5">
+        <v>203</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>317</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="320">
   <si>
     <t>Id</t>
   </si>
@@ -1018,6 +1018,12 @@
   </si>
   <si>
     <t>泰坦神殿</t>
+  </si>
+  <si>
+    <t>WJBeta159</t>
+  </si>
+  <si>
+    <t>星辰之巅</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1715,7 +1721,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1738,6 +1744,7 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1797,6 +1804,13 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2086,7 +2100,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I165"/>
+  <dimension ref="C3:I166"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4973,36 +4987,53 @@
     </row>
     <row r="164" spans="3:7">
       <c r="C164" s="3">
-        <v>202</v>
+        <v>159</v>
       </c>
       <c r="D164" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E164" s="5">
-        <v>202</v>
+        <v>159</v>
       </c>
       <c r="F164" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="G164" s="2" t="s">
+      <c r="G164" s="14" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="165" spans="3:7">
       <c r="C165" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D165" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E165" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F165" s="5" t="s">
         <v>316</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>317</v>
+      </c>
+    </row>
+    <row r="166" spans="3:7">
+      <c r="C166" s="3">
+        <v>203</v>
+      </c>
+      <c r="D166" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E166" s="5">
+        <v>203</v>
+      </c>
+      <c r="F166" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>319</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="322">
   <si>
     <t>Id</t>
   </si>
@@ -1024,6 +1024,12 @@
   </si>
   <si>
     <t>星辰之巅</t>
+  </si>
+  <si>
+    <t>WJBeta160</t>
+  </si>
+  <si>
+    <t>微风草原</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1243,7 +1249,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1277,6 +1283,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1597,7 +1609,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1621,16 +1633,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1639,85 +1651,85 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1743,8 +1755,8 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2100,7 +2112,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I166"/>
+  <dimension ref="C3:I167"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -3642,7 +3654,7 @@
       </c>
       <c r="H88" s="6"/>
     </row>
-    <row r="89" spans="3:7">
+    <row r="89" spans="3:9">
       <c r="C89" s="3">
         <v>84</v>
       </c>
@@ -3658,6 +3670,7 @@
       <c r="G89" s="2" t="s">
         <v>170</v>
       </c>
+      <c r="I89" s="6"/>
     </row>
     <row r="90" spans="3:8">
       <c r="C90" s="3">
@@ -3667,7 +3680,7 @@
         <v>9</v>
       </c>
       <c r="E90" s="5">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>171</v>
@@ -3685,7 +3698,7 @@
         <v>9</v>
       </c>
       <c r="E91" s="5">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>173</v>
@@ -3703,7 +3716,7 @@
         <v>9</v>
       </c>
       <c r="E92" s="5">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>175</v>
@@ -3721,7 +3734,7 @@
         <v>9</v>
       </c>
       <c r="E93" s="5">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F93" s="5" t="s">
         <v>177</v>
@@ -4711,7 +4724,7 @@
         <v>9</v>
       </c>
       <c r="E148" s="5">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F148" s="5" t="s">
         <v>283</v>
@@ -4719,7 +4732,7 @@
       <c r="G148" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="H148" s="6"/>
+      <c r="H148" s="14"/>
     </row>
     <row r="149" spans="3:8">
       <c r="C149" s="3">
@@ -4729,7 +4742,7 @@
         <v>9</v>
       </c>
       <c r="E149" s="5">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F149" s="5" t="s">
         <v>285</v>
@@ -4737,7 +4750,7 @@
       <c r="G149" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="H149" s="6"/>
+      <c r="H149" s="14"/>
     </row>
     <row r="150" spans="3:8">
       <c r="C150" s="3">
@@ -4747,7 +4760,7 @@
         <v>9</v>
       </c>
       <c r="E150" s="5">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F150" s="5" t="s">
         <v>287</v>
@@ -4755,7 +4768,7 @@
       <c r="G150" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="H150" s="6"/>
+      <c r="H150" s="14"/>
     </row>
     <row r="151" spans="3:8">
       <c r="C151" s="3">
@@ -4765,7 +4778,7 @@
         <v>9</v>
       </c>
       <c r="E151" s="5">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F151" s="5" t="s">
         <v>289</v>
@@ -4773,7 +4786,7 @@
       <c r="G151" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="H151" s="6"/>
+      <c r="H151" s="14"/>
     </row>
     <row r="152" spans="3:8">
       <c r="C152" s="3">
@@ -4791,7 +4804,7 @@
       <c r="G152" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="H152" s="8"/>
+      <c r="H152" s="11"/>
     </row>
     <row r="153" spans="3:8">
       <c r="C153" s="3">
@@ -4809,7 +4822,7 @@
       <c r="G153" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="H153" s="8"/>
+      <c r="H153" s="11"/>
     </row>
     <row r="154" spans="3:8">
       <c r="C154" s="3">
@@ -4819,7 +4832,7 @@
         <v>9</v>
       </c>
       <c r="E154" s="5">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F154" s="5" t="s">
         <v>294</v>
@@ -4827,7 +4840,7 @@
       <c r="G154" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="H154" s="6"/>
+      <c r="H154" s="11"/>
     </row>
     <row r="155" spans="3:8">
       <c r="C155" s="3">
@@ -4837,7 +4850,7 @@
         <v>9</v>
       </c>
       <c r="E155" s="5">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F155" s="5" t="s">
         <v>296</v>
@@ -4845,7 +4858,7 @@
       <c r="G155" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="H155" s="6"/>
+      <c r="H155" s="11"/>
     </row>
     <row r="156" spans="3:8">
       <c r="C156" s="3">
@@ -4883,7 +4896,7 @@
       </c>
       <c r="H157" s="10"/>
     </row>
-    <row r="158" spans="3:7">
+    <row r="158" spans="3:8">
       <c r="C158" s="3">
         <v>153</v>
       </c>
@@ -4899,8 +4912,9 @@
       <c r="G158" s="12" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="159" spans="3:7">
+      <c r="H158" s="11"/>
+    </row>
+    <row r="159" spans="3:8">
       <c r="C159" s="3">
         <v>154</v>
       </c>
@@ -4908,7 +4922,7 @@
         <v>9</v>
       </c>
       <c r="E159" s="5">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F159" s="5" t="s">
         <v>304</v>
@@ -4916,6 +4930,7 @@
       <c r="G159" s="12" t="s">
         <v>305</v>
       </c>
+      <c r="H159" s="11"/>
     </row>
     <row r="160" spans="3:7">
       <c r="C160" s="3">
@@ -4998,42 +5013,59 @@
       <c r="F164" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="G164" s="14" t="s">
+      <c r="G164" s="12" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="165" spans="3:7">
       <c r="C165" s="3">
-        <v>202</v>
+        <v>160</v>
       </c>
       <c r="D165" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E165" s="5">
-        <v>202</v>
+        <v>160</v>
       </c>
       <c r="F165" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="G165" s="2" t="s">
+      <c r="G165" s="12" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="166" spans="3:7">
       <c r="C166" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D166" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E166" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F166" s="5" t="s">
         <v>318</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>319</v>
+      </c>
+    </row>
+    <row r="167" spans="3:7">
+      <c r="C167" s="3">
+        <v>203</v>
+      </c>
+      <c r="D167" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E167" s="5">
+        <v>203</v>
+      </c>
+      <c r="F167" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>321</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="324">
   <si>
     <t>Id</t>
   </si>
@@ -1030,6 +1030,12 @@
   </si>
   <si>
     <t>微风草原</t>
+  </si>
+  <si>
+    <t>WJBeta161</t>
+  </si>
+  <si>
+    <t>时光镇</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1733,7 +1739,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1757,6 +1763,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2112,7 +2119,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I167"/>
+  <dimension ref="C3:I168"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5036,36 +5043,53 @@
     </row>
     <row r="166" spans="3:7">
       <c r="C166" s="3">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="D166" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E166" s="5">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="F166" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="G166" s="2" t="s">
+      <c r="G166" s="15" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="167" spans="3:7">
       <c r="C167" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D167" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E167" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F167" s="5" t="s">
         <v>320</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>321</v>
+      </c>
+    </row>
+    <row r="168" spans="3:7">
+      <c r="C168" s="3">
+        <v>203</v>
+      </c>
+      <c r="D168" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E168" s="5">
+        <v>203</v>
+      </c>
+      <c r="F168" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>323</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="326">
   <si>
     <t>Id</t>
   </si>
@@ -1036,6 +1036,12 @@
   </si>
   <si>
     <t>时光镇</t>
+  </si>
+  <si>
+    <t>WJBeta162</t>
+  </si>
+  <si>
+    <t>棉花糖</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1825,13 +1831,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
@@ -2119,7 +2118,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I168"/>
+  <dimension ref="C3:I169"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5054,42 +5053,59 @@
       <c r="F166" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="G166" s="15" t="s">
+      <c r="G166" s="12" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="167" spans="3:7">
       <c r="C167" s="3">
-        <v>202</v>
+        <v>162</v>
       </c>
       <c r="D167" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E167" s="5">
-        <v>202</v>
+        <v>162</v>
       </c>
       <c r="F167" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="G167" s="2" t="s">
+      <c r="G167" s="15" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="168" spans="3:7">
       <c r="C168" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D168" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E168" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F168" s="5" t="s">
         <v>322</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>323</v>
+      </c>
+    </row>
+    <row r="169" spans="3:7">
+      <c r="C169" s="3">
+        <v>203</v>
+      </c>
+      <c r="D169" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E169" s="5">
+        <v>203</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>325</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="327">
   <si>
     <t>Id</t>
   </si>
@@ -1042,6 +1042,9 @@
   </si>
   <si>
     <t>棉花糖</t>
+  </si>
+  <si>
+    <t>WJBeta163</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1745,7 +1748,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1769,7 +1772,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2118,7 +2120,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I169"/>
+  <dimension ref="C3:I170"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5070,42 +5072,57 @@
       <c r="F167" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="G167" s="15" t="s">
+      <c r="G167" s="12" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="168" spans="3:7">
       <c r="C168" s="3">
-        <v>202</v>
+        <v>163</v>
       </c>
       <c r="D168" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E168" s="5">
-        <v>202</v>
+        <v>163</v>
       </c>
       <c r="F168" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="G168" s="2" t="s">
-        <v>323</v>
-      </c>
+      <c r="G168" s="12"/>
     </row>
     <row r="169" spans="3:7">
       <c r="C169" s="3">
+        <v>202</v>
+      </c>
+      <c r="D169" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E169" s="5">
+        <v>202</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="170" spans="3:7">
+      <c r="C170" s="3">
         <v>203</v>
       </c>
-      <c r="D169" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E169" s="5">
+      <c r="D170" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E170" s="5">
         <v>203</v>
       </c>
-      <c r="F169" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="G169" s="2" t="s">
+      <c r="F170" s="5" t="s">
         <v>325</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>326</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="328">
   <si>
     <t>Id</t>
   </si>
@@ -1045,6 +1045,9 @@
   </si>
   <si>
     <t>WJBeta163</t>
+  </si>
+  <si>
+    <t>破晓战歌</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1253,12 +1256,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5089,7 +5092,9 @@
       <c r="F168" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="G168" s="12"/>
+      <c r="G168" s="12" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="169" spans="3:7">
       <c r="C169" s="3">
@@ -5102,10 +5107,10 @@
         <v>202</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="170" spans="3:7">
@@ -5119,10 +5124,10 @@
         <v>203</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="330">
   <si>
     <t>Id</t>
   </si>
@@ -1048,6 +1048,12 @@
   </si>
   <si>
     <t>破晓战歌</t>
+  </si>
+  <si>
+    <t>WJBeta164</t>
+  </si>
+  <si>
+    <t>翡翠仙境</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1256,12 +1262,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2123,7 +2129,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I170"/>
+  <dimension ref="C3:I171"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4887,7 +4893,7 @@
       <c r="G156" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="H156" s="10"/>
+      <c r="H156" s="6"/>
     </row>
     <row r="157" spans="3:8">
       <c r="C157" s="3">
@@ -4905,7 +4911,7 @@
       <c r="G157" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="H157" s="10"/>
+      <c r="H157" s="6"/>
     </row>
     <row r="158" spans="3:8">
       <c r="C158" s="3">
@@ -4915,7 +4921,7 @@
         <v>9</v>
       </c>
       <c r="E158" s="5">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F158" s="5" t="s">
         <v>302</v>
@@ -4923,7 +4929,7 @@
       <c r="G158" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="H158" s="11"/>
+      <c r="H158" s="6"/>
     </row>
     <row r="159" spans="3:8">
       <c r="C159" s="3">
@@ -4933,7 +4939,7 @@
         <v>9</v>
       </c>
       <c r="E159" s="5">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F159" s="5" t="s">
         <v>304</v>
@@ -4941,9 +4947,9 @@
       <c r="G159" s="12" t="s">
         <v>305</v>
       </c>
-      <c r="H159" s="11"/>
-    </row>
-    <row r="160" spans="3:7">
+      <c r="H159" s="6"/>
+    </row>
+    <row r="160" spans="3:8">
       <c r="C160" s="3">
         <v>155</v>
       </c>
@@ -4959,8 +4965,9 @@
       <c r="G160" s="12" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="161" spans="3:7">
+      <c r="H160" s="10"/>
+    </row>
+    <row r="161" spans="3:8">
       <c r="C161" s="3">
         <v>156</v>
       </c>
@@ -4968,7 +4975,7 @@
         <v>9</v>
       </c>
       <c r="E161" s="5">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F161" s="5" t="s">
         <v>308</v>
@@ -4976,8 +4983,9 @@
       <c r="G161" s="12" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="162" spans="3:7">
+      <c r="H161" s="10"/>
+    </row>
+    <row r="162" spans="3:8">
       <c r="C162" s="3">
         <v>157</v>
       </c>
@@ -4993,8 +5001,9 @@
       <c r="G162" s="12" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="163" spans="3:7">
+      <c r="H162" s="11"/>
+    </row>
+    <row r="163" spans="3:8">
       <c r="C163" s="3">
         <v>158</v>
       </c>
@@ -5002,7 +5011,7 @@
         <v>9</v>
       </c>
       <c r="E163" s="5">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F163" s="5" t="s">
         <v>312</v>
@@ -5010,8 +5019,9 @@
       <c r="G163" s="12" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="164" spans="3:7">
+      <c r="H163" s="11"/>
+    </row>
+    <row r="164" spans="3:8">
       <c r="C164" s="3">
         <v>159</v>
       </c>
@@ -5027,8 +5037,9 @@
       <c r="G164" s="12" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="165" spans="3:7">
+      <c r="H164" s="10"/>
+    </row>
+    <row r="165" spans="3:8">
       <c r="C165" s="3">
         <v>160</v>
       </c>
@@ -5036,7 +5047,7 @@
         <v>9</v>
       </c>
       <c r="E165" s="5">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F165" s="5" t="s">
         <v>316</v>
@@ -5044,6 +5055,7 @@
       <c r="G165" s="12" t="s">
         <v>317</v>
       </c>
+      <c r="H165" s="10"/>
     </row>
     <row r="166" spans="3:7">
       <c r="C166" s="3">
@@ -5098,36 +5110,53 @@
     </row>
     <row r="169" spans="3:7">
       <c r="C169" s="3">
-        <v>202</v>
+        <v>164</v>
       </c>
       <c r="D169" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E169" s="5">
-        <v>202</v>
+        <v>164</v>
       </c>
       <c r="F169" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="G169" s="2" t="s">
+      <c r="G169" s="12" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="170" spans="3:7">
       <c r="C170" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D170" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E170" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F170" s="5" t="s">
         <v>326</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>327</v>
+      </c>
+    </row>
+    <row r="171" spans="3:7">
+      <c r="C171" s="3">
+        <v>203</v>
+      </c>
+      <c r="D171" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E171" s="5">
+        <v>203</v>
+      </c>
+      <c r="F171" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>329</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="332">
   <si>
     <t>Id</t>
   </si>
@@ -1054,6 +1054,12 @@
   </si>
   <si>
     <t>翡翠仙境</t>
+  </si>
+  <si>
+    <t>WJBeta165</t>
+  </si>
+  <si>
+    <t>繁花谷</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2129,7 +2135,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I171"/>
+  <dimension ref="C3:I172"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5127,36 +5133,53 @@
     </row>
     <row r="170" spans="3:7">
       <c r="C170" s="3">
-        <v>202</v>
+        <v>165</v>
       </c>
       <c r="D170" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E170" s="5">
-        <v>202</v>
+        <v>165</v>
       </c>
       <c r="F170" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="G170" s="2" t="s">
+      <c r="G170" s="12" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="171" spans="3:7">
       <c r="C171" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D171" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E171" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F171" s="5" t="s">
         <v>328</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>329</v>
+      </c>
+    </row>
+    <row r="172" spans="3:7">
+      <c r="C172" s="3">
+        <v>203</v>
+      </c>
+      <c r="D172" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E172" s="5">
+        <v>203</v>
+      </c>
+      <c r="F172" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="333">
   <si>
     <t>Id</t>
   </si>
@@ -1060,6 +1060,9 @@
   </si>
   <si>
     <t>繁花谷</t>
+  </si>
+  <si>
+    <t>WJBeta166</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2135,7 +2138,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I172"/>
+  <dimension ref="C3:I173"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5150,36 +5153,53 @@
     </row>
     <row r="171" spans="3:7">
       <c r="C171" s="3">
-        <v>202</v>
+        <v>166</v>
       </c>
       <c r="D171" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E171" s="5">
-        <v>202</v>
+        <v>166</v>
       </c>
       <c r="F171" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="G171" s="2" t="s">
-        <v>329</v>
+      <c r="G171" s="12" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="172" spans="3:7">
       <c r="C172" s="3">
+        <v>202</v>
+      </c>
+      <c r="D172" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E172" s="5">
+        <v>202</v>
+      </c>
+      <c r="F172" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="173" spans="3:7">
+      <c r="C173" s="3">
         <v>203</v>
       </c>
-      <c r="D172" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E172" s="5">
+      <c r="D173" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E173" s="5">
         <v>203</v>
       </c>
-      <c r="F172" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="G172" s="2" t="s">
+      <c r="F173" s="5" t="s">
         <v>331</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>332</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="335">
   <si>
     <t>Id</t>
   </si>
@@ -1063,6 +1063,12 @@
   </si>
   <si>
     <t>WJBeta166</t>
+  </si>
+  <si>
+    <t>WJBeta167</t>
+  </si>
+  <si>
+    <t>青云之巅</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1271,12 +1277,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1766,7 +1772,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1788,6 +1794,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
@@ -2138,7 +2145,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I173"/>
+  <dimension ref="C3:I174"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4362,7 +4369,7 @@
       <c r="G126" t="s">
         <v>244</v>
       </c>
-      <c r="H126" s="6"/>
+      <c r="H126" s="10"/>
     </row>
     <row r="127" spans="3:8">
       <c r="C127" s="3">
@@ -4380,7 +4387,7 @@
       <c r="G127" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="H127" s="6"/>
+      <c r="H127" s="10"/>
     </row>
     <row r="128" spans="3:8">
       <c r="C128" s="3">
@@ -4398,7 +4405,7 @@
       <c r="G128" t="s">
         <v>247</v>
       </c>
-      <c r="H128" s="6"/>
+      <c r="H128" s="10"/>
     </row>
     <row r="129" spans="3:8">
       <c r="C129" s="3">
@@ -4416,7 +4423,7 @@
       <c r="G129" t="s">
         <v>249</v>
       </c>
-      <c r="H129" s="6"/>
+      <c r="H129" s="10"/>
     </row>
     <row r="130" spans="3:8">
       <c r="C130" s="3">
@@ -4434,7 +4441,7 @@
       <c r="G130" t="s">
         <v>251</v>
       </c>
-      <c r="H130" s="7"/>
+      <c r="H130" s="13"/>
     </row>
     <row r="131" spans="3:8">
       <c r="C131" s="3">
@@ -4452,7 +4459,7 @@
       <c r="G131" t="s">
         <v>253</v>
       </c>
-      <c r="H131" s="7"/>
+      <c r="H131" s="13"/>
     </row>
     <row r="132" spans="3:8">
       <c r="C132" s="3">
@@ -4470,7 +4477,7 @@
       <c r="G132" t="s">
         <v>255</v>
       </c>
-      <c r="H132" s="7"/>
+      <c r="H132" s="13"/>
     </row>
     <row r="133" spans="3:9">
       <c r="C133" s="3">
@@ -4506,7 +4513,7 @@
       <c r="G134" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="H134" s="7"/>
+      <c r="H134" s="13"/>
     </row>
     <row r="135" spans="3:8">
       <c r="C135" s="3">
@@ -4524,7 +4531,7 @@
       <c r="G135" t="s">
         <v>261</v>
       </c>
-      <c r="H135" s="7"/>
+      <c r="H135" s="13"/>
     </row>
     <row r="136" spans="3:8">
       <c r="C136" s="3">
@@ -4534,7 +4541,7 @@
         <v>9</v>
       </c>
       <c r="E136" s="5">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F136" s="5" t="s">
         <v>262</v>
@@ -4552,7 +4559,7 @@
         <v>9</v>
       </c>
       <c r="E137" s="5">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F137" s="5" t="s">
         <v>264</v>
@@ -4570,7 +4577,7 @@
         <v>9</v>
       </c>
       <c r="E138" s="5">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F138" s="5" t="s">
         <v>266</v>
@@ -4588,7 +4595,7 @@
         <v>9</v>
       </c>
       <c r="E139" s="5">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F139" s="5" t="s">
         <v>268</v>
@@ -4606,7 +4613,7 @@
         <v>9</v>
       </c>
       <c r="E140" s="5">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F140" s="5" t="s">
         <v>270</v>
@@ -4624,7 +4631,7 @@
         <v>9</v>
       </c>
       <c r="E141" s="5">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F141" s="5" t="s">
         <v>272</v>
@@ -4642,7 +4649,7 @@
         <v>9</v>
       </c>
       <c r="E142" s="5">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F142" s="5" t="s">
         <v>274</v>
@@ -4660,7 +4667,7 @@
         <v>9</v>
       </c>
       <c r="E143" s="5">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F143" s="5" t="s">
         <v>276</v>
@@ -4686,7 +4693,7 @@
       <c r="G144" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="H144" s="13"/>
+      <c r="H144" s="14"/>
     </row>
     <row r="145" spans="3:8">
       <c r="C145" s="3">
@@ -4704,7 +4711,7 @@
       <c r="G145" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="H145" s="13"/>
+      <c r="H145" s="14"/>
     </row>
     <row r="146" spans="3:8">
       <c r="C146" s="3">
@@ -4722,7 +4729,7 @@
       <c r="G146" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="H146" s="13"/>
+      <c r="H146" s="14"/>
     </row>
     <row r="147" spans="3:8">
       <c r="C147" s="3">
@@ -4740,7 +4747,7 @@
       <c r="G147" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="H147" s="13"/>
+      <c r="H147" s="14"/>
     </row>
     <row r="148" spans="3:8">
       <c r="C148" s="3">
@@ -4758,7 +4765,7 @@
       <c r="G148" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="H148" s="14"/>
+      <c r="H148" s="15"/>
     </row>
     <row r="149" spans="3:8">
       <c r="C149" s="3">
@@ -4776,7 +4783,7 @@
       <c r="G149" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="H149" s="14"/>
+      <c r="H149" s="15"/>
     </row>
     <row r="150" spans="3:8">
       <c r="C150" s="3">
@@ -4794,7 +4801,7 @@
       <c r="G150" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="H150" s="14"/>
+      <c r="H150" s="15"/>
     </row>
     <row r="151" spans="3:8">
       <c r="C151" s="3">
@@ -4812,7 +4819,7 @@
       <c r="G151" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="H151" s="14"/>
+      <c r="H151" s="15"/>
     </row>
     <row r="152" spans="3:8">
       <c r="C152" s="3">
@@ -4974,7 +4981,7 @@
       <c r="G160" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="H160" s="10"/>
+      <c r="H160" s="11"/>
     </row>
     <row r="161" spans="3:8">
       <c r="C161" s="3">
@@ -4992,7 +4999,7 @@
       <c r="G161" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="H161" s="10"/>
+      <c r="H161" s="11"/>
     </row>
     <row r="162" spans="3:8">
       <c r="C162" s="3">
@@ -5002,7 +5009,7 @@
         <v>9</v>
       </c>
       <c r="E162" s="5">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F162" s="5" t="s">
         <v>310</v>
@@ -5020,7 +5027,7 @@
         <v>9</v>
       </c>
       <c r="E163" s="5">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F163" s="5" t="s">
         <v>312</v>
@@ -5066,7 +5073,7 @@
       </c>
       <c r="H165" s="10"/>
     </row>
-    <row r="166" spans="3:7">
+    <row r="166" spans="3:8">
       <c r="C166" s="3">
         <v>161</v>
       </c>
@@ -5082,8 +5089,9 @@
       <c r="G166" s="12" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="167" spans="3:7">
+      <c r="H166" s="11"/>
+    </row>
+    <row r="167" spans="3:8">
       <c r="C167" s="3">
         <v>162</v>
       </c>
@@ -5091,7 +5099,7 @@
         <v>9</v>
       </c>
       <c r="E167" s="5">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F167" s="5" t="s">
         <v>320</v>
@@ -5099,6 +5107,7 @@
       <c r="G167" s="12" t="s">
         <v>321</v>
       </c>
+      <c r="H167" s="11"/>
     </row>
     <row r="168" spans="3:7">
       <c r="C168" s="3">
@@ -5170,36 +5179,53 @@
     </row>
     <row r="172" spans="3:7">
       <c r="C172" s="3">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="D172" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E172" s="5">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="F172" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="G172" s="2" t="s">
+      <c r="G172" s="12" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="173" spans="3:7">
       <c r="C173" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D173" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E173" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F173" s="5" t="s">
         <v>331</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>332</v>
+      </c>
+    </row>
+    <row r="174" spans="3:7">
+      <c r="C174" s="3">
+        <v>203</v>
+      </c>
+      <c r="D174" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E174" s="5">
+        <v>203</v>
+      </c>
+      <c r="F174" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>334</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="336">
   <si>
     <t>Id</t>
   </si>
@@ -1069,6 +1069,9 @@
   </si>
   <si>
     <t>青云之巅</t>
+  </si>
+  <si>
+    <t>WJBeta168</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2145,7 +2148,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I174"/>
+  <dimension ref="C3:I175"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5196,36 +5199,51 @@
     </row>
     <row r="173" spans="3:7">
       <c r="C173" s="3">
-        <v>202</v>
+        <v>168</v>
       </c>
       <c r="D173" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E173" s="5">
-        <v>202</v>
+        <v>168</v>
       </c>
       <c r="F173" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="G173" s="2" t="s">
-        <v>332</v>
-      </c>
+      <c r="G173" s="12"/>
     </row>
     <row r="174" spans="3:7">
       <c r="C174" s="3">
+        <v>202</v>
+      </c>
+      <c r="D174" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E174" s="5">
+        <v>202</v>
+      </c>
+      <c r="F174" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="175" spans="3:7">
+      <c r="C175" s="3">
         <v>203</v>
       </c>
-      <c r="D174" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E174" s="5">
+      <c r="D175" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E175" s="5">
         <v>203</v>
       </c>
-      <c r="F174" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="G174" s="2" t="s">
+      <c r="F175" s="5" t="s">
         <v>334</v>
+      </c>
+      <c r="G175" s="2" t="s">
+        <v>335</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="337">
   <si>
     <t>Id</t>
   </si>
@@ -1072,6 +1072,9 @@
   </si>
   <si>
     <t>WJBeta168</t>
+  </si>
+  <si>
+    <t>时光之歌</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1280,12 +1283,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1775,7 +1778,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1800,6 +1803,7 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5210,7 +5214,9 @@
       <c r="F173" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="G173" s="12"/>
+      <c r="G173" s="16" t="s">
+        <v>332</v>
+      </c>
     </row>
     <row r="174" spans="3:7">
       <c r="C174" s="3">
@@ -5223,10 +5229,10 @@
         <v>202</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="175" spans="3:7">
@@ -5240,10 +5246,10 @@
         <v>203</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="339">
   <si>
     <t>Id</t>
   </si>
@@ -1075,6 +1075,12 @@
   </si>
   <si>
     <t>时光之歌</t>
+  </si>
+  <si>
+    <t>WJBeta169</t>
+  </si>
+  <si>
+    <t>决战之巅</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2152,7 +2158,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I175"/>
+  <dimension ref="C3:I176"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5214,42 +5220,59 @@
       <c r="F173" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="G173" s="16" t="s">
+      <c r="G173" s="12" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="174" spans="3:7">
       <c r="C174" s="3">
-        <v>202</v>
+        <v>169</v>
       </c>
       <c r="D174" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E174" s="5">
-        <v>202</v>
+        <v>169</v>
       </c>
       <c r="F174" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="G174" s="2" t="s">
+      <c r="G174" s="16" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="175" spans="3:7">
       <c r="C175" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D175" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E175" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F175" s="5" t="s">
         <v>335</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>336</v>
+      </c>
+    </row>
+    <row r="176" spans="3:7">
+      <c r="C176" s="3">
+        <v>203</v>
+      </c>
+      <c r="D176" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E176" s="5">
+        <v>203</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>338</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="341">
   <si>
     <t>Id</t>
   </si>
@@ -1081,6 +1081,12 @@
   </si>
   <si>
     <t>决战之巅</t>
+  </si>
+  <si>
+    <t>WJBeta170</t>
+  </si>
+  <si>
+    <t>迷雾森境</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1289,12 +1295,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1784,7 +1790,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1809,7 +1815,6 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2158,7 +2163,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I176"/>
+  <dimension ref="C3:I177"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5237,42 +5242,59 @@
       <c r="F174" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="G174" s="16" t="s">
+      <c r="G174" s="12" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="175" spans="3:7">
       <c r="C175" s="3">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="D175" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E175" s="5">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="F175" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="G175" s="2" t="s">
+      <c r="G175" s="12" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="176" spans="3:7">
       <c r="C176" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D176" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E176" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F176" s="5" t="s">
         <v>337</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>338</v>
+      </c>
+    </row>
+    <row r="177" spans="3:7">
+      <c r="C177" s="3">
+        <v>203</v>
+      </c>
+      <c r="D177" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E177" s="5">
+        <v>203</v>
+      </c>
+      <c r="F177" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="G177" s="2" t="s">
+        <v>340</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="343">
   <si>
     <t>Id</t>
   </si>
@@ -1087,6 +1087,12 @@
   </si>
   <si>
     <t>迷雾森境</t>
+  </si>
+  <si>
+    <t>WJBeta171</t>
+  </si>
+  <si>
+    <t>WJBeta172</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1295,12 +1301,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2163,7 +2169,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I177"/>
+  <dimension ref="C3:I179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5265,36 +5271,66 @@
     </row>
     <row r="176" spans="3:7">
       <c r="C176" s="3">
-        <v>202</v>
+        <v>171</v>
       </c>
       <c r="D176" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E176" s="5">
-        <v>202</v>
+        <v>171</v>
       </c>
       <c r="F176" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="G176" s="2" t="s">
-        <v>338</v>
-      </c>
+      <c r="G176" s="12"/>
     </row>
     <row r="177" spans="3:7">
       <c r="C177" s="3">
+        <v>172</v>
+      </c>
+      <c r="D177" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E177" s="5">
+        <v>172</v>
+      </c>
+      <c r="F177" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="G177" s="12"/>
+    </row>
+    <row r="178" spans="3:7">
+      <c r="C178" s="3">
+        <v>202</v>
+      </c>
+      <c r="D178" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E178" s="5">
+        <v>202</v>
+      </c>
+      <c r="F178" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="G178" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="179" spans="3:7">
+      <c r="C179" s="3">
         <v>203</v>
       </c>
-      <c r="D177" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E177" s="5">
+      <c r="D179" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E179" s="5">
         <v>203</v>
       </c>
-      <c r="F177" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="G177" s="2" t="s">
-        <v>340</v>
+      <c r="F179" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>342</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="343">
   <si>
     <t>Id</t>
   </si>
@@ -1089,10 +1089,10 @@
     <t>迷雾森境</t>
   </si>
   <si>
-    <t>WJBeta171</t>
-  </si>
-  <si>
     <t>WJBeta172</t>
+  </si>
+  <si>
+    <t>星辰殿堂</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2169,7 +2169,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I179"/>
+  <dimension ref="C3:I178"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5271,65 +5271,52 @@
     </row>
     <row r="176" spans="3:7">
       <c r="C176" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D176" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E176" s="5">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F176" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="G176" s="12"/>
+      <c r="G176" s="12" t="s">
+        <v>338</v>
+      </c>
     </row>
     <row r="177" spans="3:7">
       <c r="C177" s="3">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="D177" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E177" s="5">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="G177" s="12"/>
+        <v>339</v>
+      </c>
+      <c r="G177" s="2" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="178" spans="3:7">
       <c r="C178" s="3">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D178" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E178" s="5">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="179" spans="3:7">
-      <c r="C179" s="3">
-        <v>203</v>
-      </c>
-      <c r="D179" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E179" s="5">
-        <v>203</v>
-      </c>
-      <c r="F179" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="G179" s="2" t="s">
         <v>342</v>
       </c>
     </row>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -1301,12 +1301,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4861,7 +4861,7 @@
       <c r="G152" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="H152" s="11"/>
+      <c r="H152" s="10"/>
     </row>
     <row r="153" spans="3:8">
       <c r="C153" s="3">
@@ -4879,7 +4879,7 @@
       <c r="G153" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="H153" s="11"/>
+      <c r="H153" s="10"/>
     </row>
     <row r="154" spans="3:8">
       <c r="C154" s="3">
@@ -4897,7 +4897,7 @@
       <c r="G154" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="H154" s="11"/>
+      <c r="H154" s="10"/>
     </row>
     <row r="155" spans="3:8">
       <c r="C155" s="3">
@@ -4915,7 +4915,7 @@
       <c r="G155" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="H155" s="11"/>
+      <c r="H155" s="10"/>
     </row>
     <row r="156" spans="3:8">
       <c r="C156" s="3">
@@ -4925,7 +4925,7 @@
         <v>9</v>
       </c>
       <c r="E156" s="5">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F156" s="5" t="s">
         <v>298</v>
@@ -4933,7 +4933,7 @@
       <c r="G156" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="H156" s="6"/>
+      <c r="H156" s="10"/>
     </row>
     <row r="157" spans="3:8">
       <c r="C157" s="3">
@@ -4943,7 +4943,7 @@
         <v>9</v>
       </c>
       <c r="E157" s="5">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F157" s="5" t="s">
         <v>300</v>
@@ -4951,7 +4951,7 @@
       <c r="G157" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="H157" s="6"/>
+      <c r="H157" s="10"/>
     </row>
     <row r="158" spans="3:8">
       <c r="C158" s="3">
@@ -4961,7 +4961,7 @@
         <v>9</v>
       </c>
       <c r="E158" s="5">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F158" s="5" t="s">
         <v>302</v>
@@ -4969,7 +4969,7 @@
       <c r="G158" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="H158" s="6"/>
+      <c r="H158" s="10"/>
     </row>
     <row r="159" spans="3:8">
       <c r="C159" s="3">
@@ -4979,7 +4979,7 @@
         <v>9</v>
       </c>
       <c r="E159" s="5">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F159" s="5" t="s">
         <v>304</v>
@@ -4987,7 +4987,7 @@
       <c r="G159" s="12" t="s">
         <v>305</v>
       </c>
-      <c r="H159" s="6"/>
+      <c r="H159" s="10"/>
     </row>
     <row r="160" spans="3:8">
       <c r="C160" s="3">
@@ -5105,7 +5105,7 @@
         <v>9</v>
       </c>
       <c r="E166" s="5">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F166" s="5" t="s">
         <v>318</v>
@@ -5113,7 +5113,7 @@
       <c r="G166" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="H166" s="11"/>
+      <c r="H166" s="10"/>
     </row>
     <row r="167" spans="3:8">
       <c r="C167" s="3">
@@ -5123,7 +5123,7 @@
         <v>9</v>
       </c>
       <c r="E167" s="5">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F167" s="5" t="s">
         <v>320</v>
@@ -5131,9 +5131,9 @@
       <c r="G167" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="H167" s="11"/>
-    </row>
-    <row r="168" spans="3:7">
+      <c r="H167" s="10"/>
+    </row>
+    <row r="168" spans="3:8">
       <c r="C168" s="3">
         <v>163</v>
       </c>
@@ -5149,8 +5149,9 @@
       <c r="G168" s="12" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="169" spans="3:7">
+      <c r="H168" s="11"/>
+    </row>
+    <row r="169" spans="3:8">
       <c r="C169" s="3">
         <v>164</v>
       </c>
@@ -5158,7 +5159,7 @@
         <v>9</v>
       </c>
       <c r="E169" s="5">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F169" s="5" t="s">
         <v>324</v>
@@ -5166,8 +5167,9 @@
       <c r="G169" s="12" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="170" spans="3:7">
+      <c r="H169" s="11"/>
+    </row>
+    <row r="170" spans="3:8">
       <c r="C170" s="3">
         <v>165</v>
       </c>
@@ -5183,8 +5185,9 @@
       <c r="G170" s="12" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="171" spans="3:7">
+      <c r="H170" s="10"/>
+    </row>
+    <row r="171" spans="3:8">
       <c r="C171" s="3">
         <v>166</v>
       </c>
@@ -5192,7 +5195,7 @@
         <v>9</v>
       </c>
       <c r="E171" s="5">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F171" s="5" t="s">
         <v>328</v>
@@ -5200,6 +5203,7 @@
       <c r="G171" s="12" t="s">
         <v>196</v>
       </c>
+      <c r="H171" s="10"/>
     </row>
     <row r="172" spans="3:7">
       <c r="C172" s="3">

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="344">
   <si>
     <t>Id</t>
   </si>
@@ -1093,6 +1093,9 @@
   </si>
   <si>
     <t>星辰殿堂</t>
+  </si>
+  <si>
+    <t>WJBeta173</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1301,12 +1304,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2169,7 +2172,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I178"/>
+  <dimension ref="C3:I179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5292,36 +5295,51 @@
     </row>
     <row r="177" spans="3:7">
       <c r="C177" s="3">
-        <v>202</v>
+        <v>173</v>
       </c>
       <c r="D177" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E177" s="5">
-        <v>202</v>
+        <v>173</v>
       </c>
       <c r="F177" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="G177" s="2" t="s">
-        <v>340</v>
-      </c>
+      <c r="G177" s="12"/>
     </row>
     <row r="178" spans="3:7">
       <c r="C178" s="3">
+        <v>202</v>
+      </c>
+      <c r="D178" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E178" s="5">
+        <v>202</v>
+      </c>
+      <c r="F178" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="G178" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="179" spans="3:7">
+      <c r="C179" s="3">
         <v>203</v>
       </c>
-      <c r="D178" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E178" s="5">
+      <c r="D179" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E179" s="5">
         <v>203</v>
       </c>
-      <c r="F178" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="G178" s="2" t="s">
+      <c r="F179" s="5" t="s">
         <v>342</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>343</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="345">
   <si>
     <t>Id</t>
   </si>
@@ -1096,6 +1096,9 @@
   </si>
   <si>
     <t>WJBeta173</t>
+  </si>
+  <si>
+    <t>童话森林</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1799,7 +1802,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1824,6 +1827,7 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5306,7 +5310,9 @@
       <c r="F177" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="G177" s="12"/>
+      <c r="G177" s="16" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="178" spans="3:7">
       <c r="C178" s="3">
@@ -5319,10 +5325,10 @@
         <v>202</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="179" spans="3:7">
@@ -5336,10 +5342,10 @@
         <v>203</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="346">
   <si>
     <t>Id</t>
   </si>
@@ -1099,6 +1099,9 @@
   </si>
   <si>
     <t>童话森林</t>
+  </si>
+  <si>
+    <t>WJBeta174</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1802,7 +1805,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1827,7 +1830,6 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2176,7 +2178,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I179"/>
+  <dimension ref="C3:I180"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5310,42 +5312,57 @@
       <c r="F177" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="G177" s="16" t="s">
+      <c r="G177" s="12" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="178" spans="3:7">
       <c r="C178" s="3">
-        <v>202</v>
+        <v>174</v>
       </c>
       <c r="D178" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E178" s="5">
-        <v>202</v>
+        <v>174</v>
       </c>
       <c r="F178" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="G178" s="2" t="s">
-        <v>342</v>
-      </c>
+      <c r="G178" s="12"/>
     </row>
     <row r="179" spans="3:7">
       <c r="C179" s="3">
+        <v>202</v>
+      </c>
+      <c r="D179" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E179" s="5">
+        <v>202</v>
+      </c>
+      <c r="F179" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="180" spans="3:7">
+      <c r="C180" s="3">
         <v>203</v>
       </c>
-      <c r="D179" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E179" s="5">
+      <c r="D180" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E180" s="5">
         <v>203</v>
       </c>
-      <c r="F179" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="G179" s="2" t="s">
+      <c r="F180" s="5" t="s">
         <v>344</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>345</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="348">
   <si>
     <t>Id</t>
   </si>
@@ -1102,6 +1102,12 @@
   </si>
   <si>
     <t>WJBeta174</t>
+  </si>
+  <si>
+    <t>龙息之谷</t>
+  </si>
+  <si>
+    <t>WJBeta175</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2178,7 +2184,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I180"/>
+  <dimension ref="C3:I181"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5329,40 +5335,57 @@
       <c r="F178" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="G178" s="12"/>
+      <c r="G178" s="12" t="s">
+        <v>342</v>
+      </c>
     </row>
     <row r="179" spans="3:7">
       <c r="C179" s="3">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="D179" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E179" s="5">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="G179" s="2" t="s">
         <v>343</v>
       </c>
+      <c r="G179" s="12"/>
     </row>
     <row r="180" spans="3:7">
       <c r="C180" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D180" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E180" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F180" s="5" t="s">
         <v>344</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>345</v>
+      </c>
+    </row>
+    <row r="181" spans="3:7">
+      <c r="C181" s="3">
+        <v>203</v>
+      </c>
+      <c r="D181" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E181" s="5">
+        <v>203</v>
+      </c>
+      <c r="F181" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="G181" s="2" t="s">
+        <v>347</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="349">
   <si>
     <t>Id</t>
   </si>
@@ -1108,6 +1108,9 @@
   </si>
   <si>
     <t>WJBeta175</t>
+  </si>
+  <si>
+    <t>星界回廊</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -5220,7 +5223,7 @@
       </c>
       <c r="H171" s="10"/>
     </row>
-    <row r="172" spans="3:7">
+    <row r="172" spans="3:8">
       <c r="C172" s="3">
         <v>167</v>
       </c>
@@ -5236,8 +5239,9 @@
       <c r="G172" s="12" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="173" spans="3:7">
+      <c r="H172" s="6"/>
+    </row>
+    <row r="173" spans="3:8">
       <c r="C173" s="3">
         <v>168</v>
       </c>
@@ -5245,7 +5249,7 @@
         <v>9</v>
       </c>
       <c r="E173" s="5">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F173" s="5" t="s">
         <v>331</v>
@@ -5253,8 +5257,9 @@
       <c r="G173" s="12" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="174" spans="3:7">
+      <c r="H173" s="6"/>
+    </row>
+    <row r="174" spans="3:8">
       <c r="C174" s="3">
         <v>169</v>
       </c>
@@ -5270,8 +5275,9 @@
       <c r="G174" s="12" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="175" spans="3:7">
+      <c r="H174" s="10"/>
+    </row>
+    <row r="175" spans="3:8">
       <c r="C175" s="3">
         <v>170</v>
       </c>
@@ -5279,7 +5285,7 @@
         <v>9</v>
       </c>
       <c r="E175" s="5">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F175" s="5" t="s">
         <v>335</v>
@@ -5287,6 +5293,7 @@
       <c r="G175" s="12" t="s">
         <v>336</v>
       </c>
+      <c r="H175" s="10"/>
     </row>
     <row r="176" spans="3:7">
       <c r="C176" s="3">
@@ -5352,7 +5359,9 @@
       <c r="F179" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="G179" s="12"/>
+      <c r="G179" s="12" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="180" spans="3:7">
       <c r="C180" s="3">
@@ -5365,10 +5374,10 @@
         <v>202</v>
       </c>
       <c r="F180" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="181" spans="3:7">
@@ -5382,10 +5391,10 @@
         <v>203</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="350">
   <si>
     <t>Id</t>
   </si>
@@ -1111,6 +1111,9 @@
   </si>
   <si>
     <t>星界回廊</t>
+  </si>
+  <si>
+    <t>WJBeta176</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2187,7 +2190,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I181"/>
+  <dimension ref="C3:I182"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5365,36 +5368,51 @@
     </row>
     <row r="180" spans="3:7">
       <c r="C180" s="3">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="D180" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E180" s="5">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="F180" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="G180" s="2" t="s">
-        <v>346</v>
-      </c>
+      <c r="G180" s="12"/>
     </row>
     <row r="181" spans="3:7">
       <c r="C181" s="3">
+        <v>202</v>
+      </c>
+      <c r="D181" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E181" s="5">
+        <v>202</v>
+      </c>
+      <c r="F181" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="G181" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="182" spans="3:7">
+      <c r="C182" s="3">
         <v>203</v>
       </c>
-      <c r="D181" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E181" s="5">
+      <c r="D182" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E182" s="5">
         <v>203</v>
       </c>
-      <c r="F181" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="G181" s="2" t="s">
+      <c r="F182" s="5" t="s">
         <v>348</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>349</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="353">
   <si>
     <t>Id</t>
   </si>
@@ -1114,6 +1114,15 @@
   </si>
   <si>
     <t>WJBeta176</t>
+  </si>
+  <si>
+    <t>普天同庆</t>
+  </si>
+  <si>
+    <t>WJBeta177</t>
+  </si>
+  <si>
+    <t>长安旧梦</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2190,7 +2199,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I182"/>
+  <dimension ref="C3:I183"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5379,40 +5388,59 @@
       <c r="F180" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="G180" s="12"/>
+      <c r="G180" s="12" t="s">
+        <v>346</v>
+      </c>
     </row>
     <row r="181" spans="3:7">
       <c r="C181" s="3">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="D181" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E181" s="5">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="G181" s="2" t="s">
         <v>347</v>
+      </c>
+      <c r="G181" s="12" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="182" spans="3:7">
       <c r="C182" s="3">
+        <v>202</v>
+      </c>
+      <c r="D182" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E182" s="5">
+        <v>202</v>
+      </c>
+      <c r="F182" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="183" spans="3:7">
+      <c r="C183" s="3">
         <v>203</v>
       </c>
-      <c r="D182" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E182" s="5">
+      <c r="D183" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E183" s="5">
         <v>203</v>
       </c>
-      <c r="F182" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="G182" s="2" t="s">
-        <v>349</v>
+      <c r="F183" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="G183" s="2" t="s">
+        <v>352</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="355">
   <si>
     <t>Id</t>
   </si>
@@ -1123,6 +1123,12 @@
   </si>
   <si>
     <t>长安旧梦</t>
+  </si>
+  <si>
+    <t>WJBeta178</t>
+  </si>
+  <si>
+    <t>风暴之地</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2199,7 +2205,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I183"/>
+  <dimension ref="C3:I184"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5411,36 +5417,53 @@
     </row>
     <row r="182" spans="3:7">
       <c r="C182" s="3">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="D182" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E182" s="5">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="F182" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="G182" s="2" t="s">
+      <c r="G182" s="12" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="183" spans="3:7">
       <c r="C183" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D183" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E183" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F183" s="5" t="s">
         <v>351</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>352</v>
+      </c>
+    </row>
+    <row r="184" spans="3:7">
+      <c r="C184" s="3">
+        <v>203</v>
+      </c>
+      <c r="D184" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E184" s="5">
+        <v>203</v>
+      </c>
+      <c r="F184" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="G184" s="2" t="s">
+        <v>354</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="357">
   <si>
     <t>Id</t>
   </si>
@@ -1129,6 +1129,12 @@
   </si>
   <si>
     <t>风暴之地</t>
+  </si>
+  <si>
+    <t>WJBeta179</t>
+  </si>
+  <si>
+    <t>巨刃降临</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2205,7 +2211,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I184"/>
+  <dimension ref="C3:I185"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5041,7 +5047,7 @@
       <c r="G160" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="H160" s="11"/>
+      <c r="H160" s="6"/>
     </row>
     <row r="161" spans="3:8">
       <c r="C161" s="3">
@@ -5059,7 +5065,7 @@
       <c r="G161" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="H161" s="11"/>
+      <c r="H161" s="6"/>
     </row>
     <row r="162" spans="3:8">
       <c r="C162" s="3">
@@ -5077,7 +5083,7 @@
       <c r="G162" s="12" t="s">
         <v>311</v>
       </c>
-      <c r="H162" s="11"/>
+      <c r="H162" s="6"/>
     </row>
     <row r="163" spans="3:8">
       <c r="C163" s="3">
@@ -5095,7 +5101,7 @@
       <c r="G163" s="12" t="s">
         <v>313</v>
       </c>
-      <c r="H163" s="11"/>
+      <c r="H163" s="6"/>
     </row>
     <row r="164" spans="3:8">
       <c r="C164" s="3">
@@ -5105,7 +5111,7 @@
         <v>9</v>
       </c>
       <c r="E164" s="5">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F164" s="5" t="s">
         <v>314</v>
@@ -5113,7 +5119,7 @@
       <c r="G164" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="H164" s="10"/>
+      <c r="H164" s="6"/>
     </row>
     <row r="165" spans="3:8">
       <c r="C165" s="3">
@@ -5123,7 +5129,7 @@
         <v>9</v>
       </c>
       <c r="E165" s="5">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F165" s="5" t="s">
         <v>316</v>
@@ -5131,7 +5137,7 @@
       <c r="G165" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="H165" s="10"/>
+      <c r="H165" s="6"/>
     </row>
     <row r="166" spans="3:8">
       <c r="C166" s="3">
@@ -5141,7 +5147,7 @@
         <v>9</v>
       </c>
       <c r="E166" s="5">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F166" s="5" t="s">
         <v>318</v>
@@ -5149,7 +5155,7 @@
       <c r="G166" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="H166" s="10"/>
+      <c r="H166" s="6"/>
     </row>
     <row r="167" spans="3:8">
       <c r="C167" s="3">
@@ -5159,7 +5165,7 @@
         <v>9</v>
       </c>
       <c r="E167" s="5">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F167" s="5" t="s">
         <v>320</v>
@@ -5167,7 +5173,7 @@
       <c r="G167" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="H167" s="10"/>
+      <c r="H167" s="6"/>
     </row>
     <row r="168" spans="3:8">
       <c r="C168" s="3">
@@ -5213,7 +5219,7 @@
         <v>9</v>
       </c>
       <c r="E170" s="5">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F170" s="5" t="s">
         <v>326</v>
@@ -5221,7 +5227,7 @@
       <c r="G170" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="H170" s="10"/>
+      <c r="H170" s="11"/>
     </row>
     <row r="171" spans="3:8">
       <c r="C171" s="3">
@@ -5231,7 +5237,7 @@
         <v>9</v>
       </c>
       <c r="E171" s="5">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F171" s="5" t="s">
         <v>328</v>
@@ -5239,7 +5245,7 @@
       <c r="G171" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="H171" s="10"/>
+      <c r="H171" s="11"/>
     </row>
     <row r="172" spans="3:8">
       <c r="C172" s="3">
@@ -5313,7 +5319,7 @@
       </c>
       <c r="H175" s="10"/>
     </row>
-    <row r="176" spans="3:7">
+    <row r="176" spans="3:8">
       <c r="C176" s="3">
         <v>172</v>
       </c>
@@ -5329,8 +5335,9 @@
       <c r="G176" s="12" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="177" spans="3:7">
+      <c r="H176" s="11"/>
+    </row>
+    <row r="177" spans="3:8">
       <c r="C177" s="3">
         <v>173</v>
       </c>
@@ -5338,7 +5345,7 @@
         <v>9</v>
       </c>
       <c r="E177" s="5">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F177" s="5" t="s">
         <v>339</v>
@@ -5346,6 +5353,7 @@
       <c r="G177" s="12" t="s">
         <v>340</v>
       </c>
+      <c r="H177" s="11"/>
     </row>
     <row r="178" spans="3:7">
       <c r="C178" s="3">
@@ -5434,36 +5442,53 @@
     </row>
     <row r="183" spans="3:7">
       <c r="C183" s="3">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="D183" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E183" s="5">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="F183" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="G183" s="2" t="s">
+      <c r="G183" s="12" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="184" spans="3:7">
       <c r="C184" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D184" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E184" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F184" s="5" t="s">
         <v>353</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>354</v>
+      </c>
+    </row>
+    <row r="185" spans="3:7">
+      <c r="C185" s="3">
+        <v>203</v>
+      </c>
+      <c r="D185" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E185" s="5">
+        <v>203</v>
+      </c>
+      <c r="F185" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="G185" s="2" t="s">
+        <v>356</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="358">
   <si>
     <t>Id</t>
   </si>
@@ -1135,6 +1135,9 @@
   </si>
   <si>
     <t>巨刃降临</t>
+  </si>
+  <si>
+    <t>WJBeta180</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2211,7 +2214,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I185"/>
+  <dimension ref="C3:I186"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5459,36 +5462,51 @@
     </row>
     <row r="184" spans="3:7">
       <c r="C184" s="3">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="D184" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E184" s="5">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="F184" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="G184" s="2" t="s">
-        <v>354</v>
-      </c>
+      <c r="G184" s="12"/>
     </row>
     <row r="185" spans="3:7">
       <c r="C185" s="3">
+        <v>202</v>
+      </c>
+      <c r="D185" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E185" s="5">
+        <v>202</v>
+      </c>
+      <c r="F185" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="G185" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="186" spans="3:7">
+      <c r="C186" s="3">
         <v>203</v>
       </c>
-      <c r="D185" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E185" s="5">
+      <c r="D186" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E186" s="5">
         <v>203</v>
       </c>
-      <c r="F185" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="G185" s="2" t="s">
+      <c r="F186" s="5" t="s">
         <v>356</v>
+      </c>
+      <c r="G186" s="2" t="s">
+        <v>357</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="359">
   <si>
     <t>Id</t>
   </si>
@@ -1138,6 +1138,9 @@
   </si>
   <si>
     <t>WJBeta180</t>
+  </si>
+  <si>
+    <t>生命之树</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -5473,7 +5476,9 @@
       <c r="F184" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="G184" s="12"/>
+      <c r="G184" s="12" t="s">
+        <v>354</v>
+      </c>
     </row>
     <row r="185" spans="3:7">
       <c r="C185" s="3">
@@ -5486,10 +5491,10 @@
         <v>202</v>
       </c>
       <c r="F185" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="186" spans="3:7">
@@ -5503,10 +5508,10 @@
         <v>203</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="361">
   <si>
     <t>Id</t>
   </si>
@@ -1141,6 +1141,12 @@
   </si>
   <si>
     <t>生命之树</t>
+  </si>
+  <si>
+    <t>WJBeta181</t>
+  </si>
+  <si>
+    <t>浮生若梦</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1844,7 +1850,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1869,6 +1875,7 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2217,7 +2224,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I186"/>
+  <dimension ref="C3:I187"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -2231,7 +2238,7 @@
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:6">
+    <row r="3" spans="3:8">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -2245,7 +2252,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="3:6">
+    <row r="4" spans="3:8">
       <c r="C4" s="4" t="s">
         <v>0</v>
       </c>
@@ -2259,7 +2266,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="3:6">
+    <row r="5" spans="3:8">
       <c r="C5" s="4" t="s">
         <v>7</v>
       </c>
@@ -2273,7 +2280,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="3:6">
+    <row r="6" s="1" customFormat="1" spans="3:8">
       <c r="C6" s="5">
         <v>1</v>
       </c>
@@ -2287,7 +2294,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="3:7">
+    <row r="7" spans="3:8">
       <c r="C7" s="3">
         <v>2</v>
       </c>
@@ -2304,7 +2311,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="3:7">
+    <row r="8" spans="3:8">
       <c r="C8" s="3">
         <v>3</v>
       </c>
@@ -2321,7 +2328,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="3:7">
+    <row r="9" spans="3:8">
       <c r="C9" s="3">
         <v>4</v>
       </c>
@@ -2358,7 +2365,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="3:7">
+    <row r="11" spans="3:8">
       <c r="C11" s="3">
         <v>6</v>
       </c>
@@ -2375,7 +2382,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="3:7">
+    <row r="12" spans="3:8">
       <c r="C12" s="5">
         <v>7</v>
       </c>
@@ -2392,7 +2399,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="3:7">
+    <row r="13" spans="3:8">
       <c r="C13" s="3">
         <v>8</v>
       </c>
@@ -2429,7 +2436,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="3:7">
+    <row r="15" spans="3:8">
       <c r="C15" s="3">
         <v>10</v>
       </c>
@@ -2446,7 +2453,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="3:7">
+    <row r="16" spans="3:8">
       <c r="C16" s="5">
         <v>11</v>
       </c>
@@ -3615,7 +3622,7 @@
       </c>
       <c r="H80" s="11"/>
     </row>
-    <row r="81" spans="3:8">
+    <row r="81" spans="3:9">
       <c r="C81" s="3">
         <v>76</v>
       </c>
@@ -3633,7 +3640,7 @@
       </c>
       <c r="H81" s="11"/>
     </row>
-    <row r="82" spans="3:8">
+    <row r="82" spans="3:9">
       <c r="C82" s="3">
         <v>77</v>
       </c>
@@ -3651,7 +3658,7 @@
       </c>
       <c r="H82" s="11"/>
     </row>
-    <row r="83" spans="3:8">
+    <row r="83" spans="3:9">
       <c r="C83" s="3">
         <v>78</v>
       </c>
@@ -3669,7 +3676,7 @@
       </c>
       <c r="H83" s="11"/>
     </row>
-    <row r="84" spans="3:8">
+    <row r="84" spans="3:9">
       <c r="C84" s="3">
         <v>79</v>
       </c>
@@ -3687,7 +3694,7 @@
       </c>
       <c r="H84" s="11"/>
     </row>
-    <row r="85" spans="3:8">
+    <row r="85" spans="3:9">
       <c r="C85" s="3">
         <v>80</v>
       </c>
@@ -3705,7 +3712,7 @@
       </c>
       <c r="H85" s="6"/>
     </row>
-    <row r="86" spans="3:8">
+    <row r="86" spans="3:9">
       <c r="C86" s="3">
         <v>81</v>
       </c>
@@ -3723,7 +3730,7 @@
       </c>
       <c r="H86" s="6"/>
     </row>
-    <row r="87" spans="3:8">
+    <row r="87" spans="3:9">
       <c r="C87" s="3">
         <v>82</v>
       </c>
@@ -3741,7 +3748,7 @@
       </c>
       <c r="H87" s="6"/>
     </row>
-    <row r="88" spans="3:8">
+    <row r="88" spans="3:9">
       <c r="C88" s="3">
         <v>83</v>
       </c>
@@ -3777,7 +3784,7 @@
       </c>
       <c r="I89" s="6"/>
     </row>
-    <row r="90" spans="3:8">
+    <row r="90" spans="3:9">
       <c r="C90" s="3">
         <v>85</v>
       </c>
@@ -3795,7 +3802,7 @@
       </c>
       <c r="H90" s="6"/>
     </row>
-    <row r="91" spans="3:8">
+    <row r="91" spans="3:9">
       <c r="C91" s="3">
         <v>86</v>
       </c>
@@ -3813,7 +3820,7 @@
       </c>
       <c r="H91" s="6"/>
     </row>
-    <row r="92" spans="3:8">
+    <row r="92" spans="3:9">
       <c r="C92" s="3">
         <v>87</v>
       </c>
@@ -3831,7 +3838,7 @@
       </c>
       <c r="H92" s="6"/>
     </row>
-    <row r="93" spans="3:8">
+    <row r="93" spans="3:9">
       <c r="C93" s="3">
         <v>88</v>
       </c>
@@ -3849,7 +3856,7 @@
       </c>
       <c r="H93" s="6"/>
     </row>
-    <row r="94" spans="3:8">
+    <row r="94" spans="3:9">
       <c r="C94" s="3">
         <v>89</v>
       </c>
@@ -3867,7 +3874,7 @@
       </c>
       <c r="H94" s="10"/>
     </row>
-    <row r="95" spans="3:8">
+    <row r="95" spans="3:9">
       <c r="C95" s="3">
         <v>90</v>
       </c>
@@ -3885,7 +3892,7 @@
       </c>
       <c r="H95" s="10"/>
     </row>
-    <row r="96" spans="3:8">
+    <row r="96" spans="3:9">
       <c r="C96" s="3">
         <v>91</v>
       </c>
@@ -4479,7 +4486,7 @@
       </c>
       <c r="H128" s="10"/>
     </row>
-    <row r="129" spans="3:8">
+    <row r="129" spans="3:9">
       <c r="C129" s="3">
         <v>124</v>
       </c>
@@ -4497,7 +4504,7 @@
       </c>
       <c r="H129" s="10"/>
     </row>
-    <row r="130" spans="3:8">
+    <row r="130" spans="3:9">
       <c r="C130" s="3">
         <v>125</v>
       </c>
@@ -4515,7 +4522,7 @@
       </c>
       <c r="H130" s="13"/>
     </row>
-    <row r="131" spans="3:8">
+    <row r="131" spans="3:9">
       <c r="C131" s="3">
         <v>126</v>
       </c>
@@ -4533,7 +4540,7 @@
       </c>
       <c r="H131" s="13"/>
     </row>
-    <row r="132" spans="3:8">
+    <row r="132" spans="3:9">
       <c r="C132" s="3">
         <v>127</v>
       </c>
@@ -4569,7 +4576,7 @@
       </c>
       <c r="I133" s="11"/>
     </row>
-    <row r="134" spans="3:8">
+    <row r="134" spans="3:9">
       <c r="C134" s="3">
         <v>129</v>
       </c>
@@ -4587,7 +4594,7 @@
       </c>
       <c r="H134" s="13"/>
     </row>
-    <row r="135" spans="3:8">
+    <row r="135" spans="3:9">
       <c r="C135" s="3">
         <v>130</v>
       </c>
@@ -4605,7 +4612,7 @@
       </c>
       <c r="H135" s="13"/>
     </row>
-    <row r="136" spans="3:8">
+    <row r="136" spans="3:9">
       <c r="C136" s="3">
         <v>131</v>
       </c>
@@ -4623,7 +4630,7 @@
       </c>
       <c r="H136" s="10"/>
     </row>
-    <row r="137" spans="3:8">
+    <row r="137" spans="3:9">
       <c r="C137" s="3">
         <v>132</v>
       </c>
@@ -4641,7 +4648,7 @@
       </c>
       <c r="H137" s="10"/>
     </row>
-    <row r="138" spans="3:8">
+    <row r="138" spans="3:9">
       <c r="C138" s="3">
         <v>133</v>
       </c>
@@ -4659,7 +4666,7 @@
       </c>
       <c r="H138" s="10"/>
     </row>
-    <row r="139" spans="3:8">
+    <row r="139" spans="3:9">
       <c r="C139" s="3">
         <v>134</v>
       </c>
@@ -4677,7 +4684,7 @@
       </c>
       <c r="H139" s="10"/>
     </row>
-    <row r="140" spans="3:8">
+    <row r="140" spans="3:9">
       <c r="C140" s="3">
         <v>135</v>
       </c>
@@ -4695,7 +4702,7 @@
       </c>
       <c r="H140" s="10"/>
     </row>
-    <row r="141" spans="3:8">
+    <row r="141" spans="3:9">
       <c r="C141" s="3">
         <v>136</v>
       </c>
@@ -4713,7 +4720,7 @@
       </c>
       <c r="H141" s="10"/>
     </row>
-    <row r="142" spans="3:8">
+    <row r="142" spans="3:9">
       <c r="C142" s="3">
         <v>137</v>
       </c>
@@ -4731,7 +4738,7 @@
       </c>
       <c r="H142" s="10"/>
     </row>
-    <row r="143" spans="3:8">
+    <row r="143" spans="3:9">
       <c r="C143" s="3">
         <v>138</v>
       </c>
@@ -4749,7 +4756,7 @@
       </c>
       <c r="H143" s="10"/>
     </row>
-    <row r="144" spans="3:8">
+    <row r="144" spans="3:9">
       <c r="C144" s="3">
         <v>139</v>
       </c>
@@ -5361,7 +5368,7 @@
       </c>
       <c r="H177" s="11"/>
     </row>
-    <row r="178" spans="3:7">
+    <row r="178" spans="3:8">
       <c r="C178" s="3">
         <v>174</v>
       </c>
@@ -5378,7 +5385,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="179" spans="3:7">
+    <row r="179" spans="3:8">
       <c r="C179" s="3">
         <v>175</v>
       </c>
@@ -5395,7 +5402,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="180" spans="3:7">
+    <row r="180" spans="3:8">
       <c r="C180" s="3">
         <v>176</v>
       </c>
@@ -5412,7 +5419,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="181" spans="3:7">
+    <row r="181" spans="3:8">
       <c r="C181" s="3">
         <v>177</v>
       </c>
@@ -5429,7 +5436,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="182" spans="3:7">
+    <row r="182" spans="3:8">
       <c r="C182" s="3">
         <v>178</v>
       </c>
@@ -5446,7 +5453,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="183" spans="3:7">
+    <row r="183" spans="3:8">
       <c r="C183" s="3">
         <v>179</v>
       </c>
@@ -5463,7 +5470,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="184" spans="3:7">
+    <row r="184" spans="3:8">
       <c r="C184" s="3">
         <v>180</v>
       </c>
@@ -5480,38 +5487,55 @@
         <v>354</v>
       </c>
     </row>
-    <row r="185" spans="3:7">
+    <row r="185" spans="3:8">
       <c r="C185" s="3">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="D185" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E185" s="5">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="F185" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="G185" s="2" t="s">
+      <c r="G185" s="16" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="186" spans="3:7">
+    <row r="186" spans="3:8">
       <c r="C186" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D186" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E186" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F186" s="5" t="s">
         <v>357</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>358</v>
+      </c>
+    </row>
+    <row r="187" spans="3:8">
+      <c r="C187" s="3">
+        <v>203</v>
+      </c>
+      <c r="D187" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E187" s="5">
+        <v>203</v>
+      </c>
+      <c r="F187" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>360</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="362">
   <si>
     <t>Id</t>
   </si>
@@ -1147,6 +1147,9 @@
   </si>
   <si>
     <t>浮生若梦</t>
+  </si>
+  <si>
+    <t>WJBeta182</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1355,12 +1358,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1850,7 +1853,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1875,7 +1878,6 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2224,7 +2226,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I187"/>
+  <dimension ref="C3:I188"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5500,42 +5502,57 @@
       <c r="F185" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="G185" s="16" t="s">
+      <c r="G185" s="12" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="186" spans="3:8">
       <c r="C186" s="3">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="D186" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E186" s="5">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="F186" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="G186" s="2" t="s">
-        <v>358</v>
-      </c>
+      <c r="G186" s="12"/>
     </row>
     <row r="187" spans="3:8">
       <c r="C187" s="3">
+        <v>202</v>
+      </c>
+      <c r="D187" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E187" s="5">
+        <v>202</v>
+      </c>
+      <c r="F187" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="188" spans="3:8">
+      <c r="C188" s="3">
         <v>203</v>
       </c>
-      <c r="D187" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E187" s="5">
+      <c r="D188" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E188" s="5">
         <v>203</v>
       </c>
-      <c r="F187" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="G187" s="2" t="s">
+      <c r="F188" s="5" t="s">
         <v>360</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>361</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="363">
   <si>
     <t>Id</t>
   </si>
@@ -1150,6 +1150,9 @@
   </si>
   <si>
     <t>WJBeta182</t>
+  </si>
+  <si>
+    <t>泰坦之锤</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1174,7 +1177,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1211,6 +1214,12 @@
       <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1358,12 +1367,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1723,16 +1732,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1741,119 +1747,122 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1878,6 +1887,7 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5306,7 +5316,7 @@
         <v>9</v>
       </c>
       <c r="E174" s="5">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F174" s="5" t="s">
         <v>333</v>
@@ -5314,7 +5324,7 @@
       <c r="G174" s="12" t="s">
         <v>334</v>
       </c>
-      <c r="H174" s="10"/>
+      <c r="H174" s="6"/>
     </row>
     <row r="175" spans="3:8">
       <c r="C175" s="3">
@@ -5324,7 +5334,7 @@
         <v>9</v>
       </c>
       <c r="E175" s="5">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F175" s="5" t="s">
         <v>335</v>
@@ -5332,7 +5342,7 @@
       <c r="G175" s="12" t="s">
         <v>336</v>
       </c>
-      <c r="H175" s="10"/>
+      <c r="H175" s="6"/>
     </row>
     <row r="176" spans="3:8">
       <c r="C176" s="3">
@@ -5386,6 +5396,7 @@
       <c r="G178" s="12" t="s">
         <v>342</v>
       </c>
+      <c r="H178" s="6"/>
     </row>
     <row r="179" spans="3:8">
       <c r="C179" s="3">
@@ -5395,7 +5406,7 @@
         <v>9</v>
       </c>
       <c r="E179" s="5">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F179" s="5" t="s">
         <v>343</v>
@@ -5403,6 +5414,7 @@
       <c r="G179" s="12" t="s">
         <v>344</v>
       </c>
+      <c r="H179" s="6"/>
     </row>
     <row r="180" spans="3:8">
       <c r="C180" s="3">
@@ -5420,6 +5432,7 @@
       <c r="G180" s="12" t="s">
         <v>346</v>
       </c>
+      <c r="H180" s="10"/>
     </row>
     <row r="181" spans="3:8">
       <c r="C181" s="3">
@@ -5429,7 +5442,7 @@
         <v>9</v>
       </c>
       <c r="E181" s="5">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F181" s="5" t="s">
         <v>347</v>
@@ -5437,6 +5450,7 @@
       <c r="G181" s="12" t="s">
         <v>348</v>
       </c>
+      <c r="H181" s="10"/>
     </row>
     <row r="182" spans="3:8">
       <c r="C182" s="3">
@@ -5519,7 +5533,9 @@
       <c r="F186" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="G186" s="12"/>
+      <c r="G186" s="16" t="s">
+        <v>358</v>
+      </c>
     </row>
     <row r="187" spans="3:8">
       <c r="C187" s="3">
@@ -5532,10 +5548,10 @@
         <v>202</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="188" spans="3:8">
@@ -5549,10 +5565,10 @@
         <v>203</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="364">
   <si>
     <t>Id</t>
   </si>
@@ -1153,6 +1153,9 @@
   </si>
   <si>
     <t>泰坦之锤</t>
+  </si>
+  <si>
+    <t>WJBeta183</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2236,7 +2239,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I188"/>
+  <dimension ref="C3:I189"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5539,36 +5542,51 @@
     </row>
     <row r="187" spans="3:8">
       <c r="C187" s="3">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="D187" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E187" s="5">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="F187" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="G187" s="2" t="s">
-        <v>360</v>
-      </c>
+      <c r="G187" s="12"/>
     </row>
     <row r="188" spans="3:8">
       <c r="C188" s="3">
+        <v>202</v>
+      </c>
+      <c r="D188" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E188" s="5">
+        <v>202</v>
+      </c>
+      <c r="F188" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="189" spans="3:8">
+      <c r="C189" s="3">
         <v>203</v>
       </c>
-      <c r="D188" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E188" s="5">
+      <c r="D189" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E189" s="5">
         <v>203</v>
       </c>
-      <c r="F188" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="G188" s="2" t="s">
+      <c r="F189" s="5" t="s">
         <v>362</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>363</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="365">
   <si>
     <t>Id</t>
   </si>
@@ -1156,6 +1156,9 @@
   </si>
   <si>
     <t>WJBeta183</t>
+  </si>
+  <si>
+    <t>圣光神域</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1370,12 +1373,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1865,7 +1868,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1891,6 +1894,7 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5553,7 +5557,9 @@
       <c r="F187" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="G187" s="12"/>
+      <c r="G187" s="17" t="s">
+        <v>360</v>
+      </c>
     </row>
     <row r="188" spans="3:8">
       <c r="C188" s="3">
@@ -5566,10 +5572,10 @@
         <v>202</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="189" spans="3:8">
@@ -5583,10 +5589,10 @@
         <v>203</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="366">
   <si>
     <t>Id</t>
   </si>
@@ -1159,6 +1159,9 @@
   </si>
   <si>
     <t>圣光神域</t>
+  </si>
+  <si>
+    <t>WJBeta184</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1373,12 +1376,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1868,7 +1871,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1894,7 +1897,6 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2243,7 +2245,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I189"/>
+  <dimension ref="C3:I190"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5557,42 +5559,57 @@
       <c r="F187" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="G187" s="17" t="s">
+      <c r="G187" s="12" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="188" spans="3:8">
       <c r="C188" s="3">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="D188" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E188" s="5">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="F188" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="G188" s="2" t="s">
-        <v>362</v>
-      </c>
+      <c r="G188" s="12"/>
     </row>
     <row r="189" spans="3:8">
       <c r="C189" s="3">
+        <v>202</v>
+      </c>
+      <c r="D189" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E189" s="5">
+        <v>202</v>
+      </c>
+      <c r="F189" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="190" spans="3:8">
+      <c r="C190" s="3">
         <v>203</v>
       </c>
-      <c r="D189" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E189" s="5">
+      <c r="D190" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E190" s="5">
         <v>203</v>
       </c>
-      <c r="F189" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="G189" s="2" t="s">
+      <c r="F190" s="5" t="s">
         <v>364</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>365</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="367">
   <si>
     <t>Id</t>
   </si>
@@ -1162,6 +1162,9 @@
   </si>
   <si>
     <t>WJBeta184</t>
+  </si>
+  <si>
+    <t>炽焰神殿</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1871,7 +1874,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1897,6 +1900,7 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5576,7 +5580,9 @@
       <c r="F188" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="G188" s="12"/>
+      <c r="G188" s="17" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="189" spans="3:8">
       <c r="C189" s="3">
@@ -5589,10 +5595,10 @@
         <v>202</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="190" spans="3:8">
@@ -5606,10 +5612,10 @@
         <v>203</v>
       </c>
       <c r="F190" s="5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="368">
   <si>
     <t>Id</t>
   </si>
@@ -1165,6 +1165,9 @@
   </si>
   <si>
     <t>炽焰神殿</t>
+  </si>
+  <si>
+    <t>WJBeta185</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1874,7 +1877,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1900,7 +1903,6 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2249,7 +2251,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I190"/>
+  <dimension ref="C3:I191"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5580,42 +5582,57 @@
       <c r="F188" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="G188" s="17" t="s">
+      <c r="G188" s="12" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="189" spans="3:8">
       <c r="C189" s="3">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="D189" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E189" s="5">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="F189" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="G189" s="2" t="s">
-        <v>364</v>
-      </c>
+      <c r="G189" s="16"/>
     </row>
     <row r="190" spans="3:8">
       <c r="C190" s="3">
+        <v>202</v>
+      </c>
+      <c r="D190" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E190" s="5">
+        <v>202</v>
+      </c>
+      <c r="F190" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="191" spans="3:8">
+      <c r="C191" s="3">
         <v>203</v>
       </c>
-      <c r="D190" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E190" s="5">
+      <c r="D191" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E191" s="5">
         <v>203</v>
       </c>
-      <c r="F190" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="G190" s="2" t="s">
+      <c r="F191" s="5" t="s">
         <v>366</v>
+      </c>
+      <c r="G191" s="2" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="370">
   <si>
     <t>Id</t>
   </si>
@@ -1168,6 +1168,12 @@
   </si>
   <si>
     <t>WJBeta185</t>
+  </si>
+  <si>
+    <t>山河万里</t>
+  </si>
+  <si>
+    <t>WJBeta186</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2251,7 +2257,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I191"/>
+  <dimension ref="C3:I192"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5599,40 +5605,57 @@
       <c r="F189" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="G189" s="16"/>
+      <c r="G189" s="16" t="s">
+        <v>364</v>
+      </c>
     </row>
     <row r="190" spans="3:8">
       <c r="C190" s="3">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="D190" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E190" s="5">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="F190" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="G190" s="2" t="s">
         <v>365</v>
       </c>
+      <c r="G190" s="16"/>
     </row>
     <row r="191" spans="3:8">
       <c r="C191" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D191" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E191" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F191" s="5" t="s">
         <v>366</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>367</v>
+      </c>
+    </row>
+    <row r="192" spans="3:8">
+      <c r="C192" s="3">
+        <v>203</v>
+      </c>
+      <c r="D192" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E192" s="5">
+        <v>203</v>
+      </c>
+      <c r="F192" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="G192" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="371">
   <si>
     <t>Id</t>
   </si>
@@ -1174,6 +1174,9 @@
   </si>
   <si>
     <t>WJBeta186</t>
+  </si>
+  <si>
+    <t>忘川彼岸</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -5622,7 +5625,9 @@
       <c r="F190" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="G190" s="16"/>
+      <c r="G190" s="16" t="s">
+        <v>366</v>
+      </c>
     </row>
     <row r="191" spans="3:8">
       <c r="C191" s="3">
@@ -5635,10 +5640,10 @@
         <v>202</v>
       </c>
       <c r="F191" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="192" spans="3:8">
@@ -5652,10 +5657,10 @@
         <v>203</v>
       </c>
       <c r="F192" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="373">
   <si>
     <t>Id</t>
   </si>
@@ -1177,6 +1177,12 @@
   </si>
   <si>
     <t>忘川彼岸</t>
+  </si>
+  <si>
+    <t>WJBeta187</t>
+  </si>
+  <si>
+    <t>花涧语</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2260,7 +2266,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I192"/>
+  <dimension ref="C3:I193"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5240,7 +5246,7 @@
       <c r="G168" s="12" t="s">
         <v>323</v>
       </c>
-      <c r="H168" s="11"/>
+      <c r="H168" s="10"/>
     </row>
     <row r="169" spans="3:8">
       <c r="C169" s="3">
@@ -5258,7 +5264,7 @@
       <c r="G169" s="12" t="s">
         <v>325</v>
       </c>
-      <c r="H169" s="11"/>
+      <c r="H169" s="10"/>
     </row>
     <row r="170" spans="3:8">
       <c r="C170" s="3">
@@ -5276,7 +5282,7 @@
       <c r="G170" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="H170" s="11"/>
+      <c r="H170" s="10"/>
     </row>
     <row r="171" spans="3:8">
       <c r="C171" s="3">
@@ -5294,7 +5300,7 @@
       <c r="G171" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="H171" s="11"/>
+      <c r="H171" s="10"/>
     </row>
     <row r="172" spans="3:8">
       <c r="C172" s="3">
@@ -5304,7 +5310,7 @@
         <v>9</v>
       </c>
       <c r="E172" s="5">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F172" s="5" t="s">
         <v>329</v>
@@ -5312,7 +5318,7 @@
       <c r="G172" s="12" t="s">
         <v>330</v>
       </c>
-      <c r="H172" s="6"/>
+      <c r="H172" s="10"/>
     </row>
     <row r="173" spans="3:8">
       <c r="C173" s="3">
@@ -5322,7 +5328,7 @@
         <v>9</v>
       </c>
       <c r="E173" s="5">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F173" s="5" t="s">
         <v>331</v>
@@ -5330,7 +5336,7 @@
       <c r="G173" s="12" t="s">
         <v>332</v>
       </c>
-      <c r="H173" s="6"/>
+      <c r="H173" s="10"/>
     </row>
     <row r="174" spans="3:8">
       <c r="C174" s="3">
@@ -5340,7 +5346,7 @@
         <v>9</v>
       </c>
       <c r="E174" s="5">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F174" s="5" t="s">
         <v>333</v>
@@ -5348,7 +5354,7 @@
       <c r="G174" s="12" t="s">
         <v>334</v>
       </c>
-      <c r="H174" s="6"/>
+      <c r="H174" s="10"/>
     </row>
     <row r="175" spans="3:8">
       <c r="C175" s="3">
@@ -5358,7 +5364,7 @@
         <v>9</v>
       </c>
       <c r="E175" s="5">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F175" s="5" t="s">
         <v>335</v>
@@ -5366,7 +5372,7 @@
       <c r="G175" s="12" t="s">
         <v>336</v>
       </c>
-      <c r="H175" s="6"/>
+      <c r="H175" s="10"/>
     </row>
     <row r="176" spans="3:8">
       <c r="C176" s="3">
@@ -5412,7 +5418,7 @@
         <v>9</v>
       </c>
       <c r="E178" s="5">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F178" s="5" t="s">
         <v>341</v>
@@ -5420,7 +5426,7 @@
       <c r="G178" s="12" t="s">
         <v>342</v>
       </c>
-      <c r="H178" s="6"/>
+      <c r="H178" s="11"/>
     </row>
     <row r="179" spans="3:8">
       <c r="C179" s="3">
@@ -5430,7 +5436,7 @@
         <v>9</v>
       </c>
       <c r="E179" s="5">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F179" s="5" t="s">
         <v>343</v>
@@ -5438,7 +5444,7 @@
       <c r="G179" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="H179" s="6"/>
+      <c r="H179" s="11"/>
     </row>
     <row r="180" spans="3:8">
       <c r="C180" s="3">
@@ -5492,6 +5498,7 @@
       <c r="G182" s="12" t="s">
         <v>350</v>
       </c>
+      <c r="H182" s="11"/>
     </row>
     <row r="183" spans="3:8">
       <c r="C183" s="3">
@@ -5501,7 +5508,7 @@
         <v>9</v>
       </c>
       <c r="E183" s="5">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F183" s="5" t="s">
         <v>351</v>
@@ -5509,6 +5516,7 @@
       <c r="G183" s="12" t="s">
         <v>352</v>
       </c>
+      <c r="H183" s="11"/>
     </row>
     <row r="184" spans="3:8">
       <c r="C184" s="3">
@@ -5526,6 +5534,7 @@
       <c r="G184" s="12" t="s">
         <v>354</v>
       </c>
+      <c r="H184" s="10"/>
     </row>
     <row r="185" spans="3:8">
       <c r="C185" s="3">
@@ -5535,7 +5544,7 @@
         <v>9</v>
       </c>
       <c r="E185" s="5">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F185" s="5" t="s">
         <v>355</v>
@@ -5543,6 +5552,7 @@
       <c r="G185" s="12" t="s">
         <v>356</v>
       </c>
+      <c r="H185" s="10"/>
     </row>
     <row r="186" spans="3:8">
       <c r="C186" s="3">
@@ -5631,36 +5641,53 @@
     </row>
     <row r="191" spans="3:8">
       <c r="C191" s="3">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="D191" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E191" s="5">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="F191" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="G191" s="2" t="s">
+      <c r="G191" s="16" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="192" spans="3:8">
       <c r="C192" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D192" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E192" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F192" s="5" t="s">
         <v>369</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>370</v>
+      </c>
+    </row>
+    <row r="193" spans="3:7">
+      <c r="C193" s="3">
+        <v>203</v>
+      </c>
+      <c r="D193" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E193" s="5">
+        <v>203</v>
+      </c>
+      <c r="F193" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="G193" s="2" t="s">
+        <v>372</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="375">
   <si>
     <t>Id</t>
   </si>
@@ -1183,6 +1183,12 @@
   </si>
   <si>
     <t>花涧语</t>
+  </si>
+  <si>
+    <t>WJBeta188</t>
+  </si>
+  <si>
+    <t>九天境</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1892,7 +1898,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1918,6 +1924,7 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2266,7 +2273,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I193"/>
+  <dimension ref="C3:I194"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5658,36 +5665,53 @@
     </row>
     <row r="192" spans="3:8">
       <c r="C192" s="3">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="D192" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E192" s="5">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="F192" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="G192" s="2" t="s">
+      <c r="G192" s="17" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="193" spans="3:7">
       <c r="C193" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D193" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E193" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F193" s="5" t="s">
         <v>371</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>372</v>
+      </c>
+    </row>
+    <row r="194" spans="3:7">
+      <c r="C194" s="3">
+        <v>203</v>
+      </c>
+      <c r="D194" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E194" s="5">
+        <v>203</v>
+      </c>
+      <c r="F194" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="G194" s="2" t="s">
+        <v>374</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="376">
   <si>
     <t>Id</t>
   </si>
@@ -1189,6 +1189,9 @@
   </si>
   <si>
     <t>九天境</t>
+  </si>
+  <si>
+    <t>WJBeta189</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1898,7 +1901,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1924,7 +1927,6 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2273,7 +2275,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I194"/>
+  <dimension ref="C3:I195"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5676,42 +5678,57 @@
       <c r="F192" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="G192" s="17" t="s">
+      <c r="G192" s="12" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="193" spans="3:7">
       <c r="C193" s="3">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="D193" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E193" s="5">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="F193" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="G193" s="2" t="s">
-        <v>372</v>
-      </c>
+      <c r="G193" s="12"/>
     </row>
     <row r="194" spans="3:7">
       <c r="C194" s="3">
+        <v>202</v>
+      </c>
+      <c r="D194" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E194" s="5">
+        <v>202</v>
+      </c>
+      <c r="F194" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="G194" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="195" spans="3:7">
+      <c r="C195" s="3">
         <v>203</v>
       </c>
-      <c r="D194" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E194" s="5">
+      <c r="D195" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E195" s="5">
         <v>203</v>
       </c>
-      <c r="F194" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="G194" s="2" t="s">
+      <c r="F195" s="5" t="s">
         <v>374</v>
+      </c>
+      <c r="G195" s="2" t="s">
+        <v>375</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="379">
   <si>
     <t>Id</t>
   </si>
@@ -1192,6 +1192,15 @@
   </si>
   <si>
     <t>WJBeta189</t>
+  </si>
+  <si>
+    <t>吉星高照</t>
+  </si>
+  <si>
+    <t>WJBeta190</t>
+  </si>
+  <si>
+    <t>逐月谷</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1406,12 +1415,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2275,7 +2284,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I195"/>
+  <dimension ref="C3:I196"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5695,40 +5704,59 @@
       <c r="F193" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="G193" s="12"/>
+      <c r="G193" s="12" t="s">
+        <v>372</v>
+      </c>
     </row>
     <row r="194" spans="3:7">
       <c r="C194" s="3">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="D194" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E194" s="5">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="F194" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="G194" s="2" t="s">
         <v>373</v>
+      </c>
+      <c r="G194" s="16" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="195" spans="3:7">
       <c r="C195" s="3">
+        <v>202</v>
+      </c>
+      <c r="D195" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E195" s="5">
+        <v>202</v>
+      </c>
+      <c r="F195" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="G195" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="196" spans="3:7">
+      <c r="C196" s="3">
         <v>203</v>
       </c>
-      <c r="D195" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E195" s="5">
+      <c r="D196" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E196" s="5">
         <v>203</v>
       </c>
-      <c r="F195" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="G195" s="2" t="s">
-        <v>375</v>
+      <c r="F196" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="G196" s="2" t="s">
+        <v>378</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="380">
   <si>
     <t>Id</t>
   </si>
@@ -1201,6 +1201,9 @@
   </si>
   <si>
     <t>逐月谷</t>
+  </si>
+  <si>
+    <t>WJBeta191</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1415,12 +1418,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2284,7 +2287,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I196"/>
+  <dimension ref="C3:I197"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5727,36 +5730,51 @@
     </row>
     <row r="195" spans="3:7">
       <c r="C195" s="3">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="D195" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E195" s="5">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="F195" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="G195" s="2" t="s">
-        <v>376</v>
-      </c>
+      <c r="G195" s="12"/>
     </row>
     <row r="196" spans="3:7">
       <c r="C196" s="3">
+        <v>202</v>
+      </c>
+      <c r="D196" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E196" s="5">
+        <v>202</v>
+      </c>
+      <c r="F196" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="G196" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="197" spans="3:7">
+      <c r="C197" s="3">
         <v>203</v>
       </c>
-      <c r="D196" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E196" s="5">
+      <c r="D197" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E197" s="5">
         <v>203</v>
       </c>
-      <c r="F196" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="G196" s="2" t="s">
+      <c r="F197" s="5" t="s">
         <v>378</v>
+      </c>
+      <c r="G197" s="2" t="s">
+        <v>379</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="381">
   <si>
     <t>Id</t>
   </si>
@@ -1204,6 +1204,9 @@
   </si>
   <si>
     <t>WJBeta191</t>
+  </si>
+  <si>
+    <t>沧澜神域</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1429,7 +1432,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1463,12 +1466,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC00000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1789,7 +1786,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1813,16 +1810,16 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1831,89 +1828,89 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1936,8 +1933,7 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -4907,7 +4903,7 @@
       <c r="G148" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="H148" s="15"/>
+      <c r="H148" s="11"/>
     </row>
     <row r="149" spans="3:8">
       <c r="C149" s="3">
@@ -4925,7 +4921,7 @@
       <c r="G149" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="H149" s="15"/>
+      <c r="H149" s="11"/>
     </row>
     <row r="150" spans="3:8">
       <c r="C150" s="3">
@@ -4943,7 +4939,7 @@
       <c r="G150" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="H150" s="15"/>
+      <c r="H150" s="11"/>
     </row>
     <row r="151" spans="3:8">
       <c r="C151" s="3">
@@ -4961,7 +4957,7 @@
       <c r="G151" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="H151" s="15"/>
+      <c r="H151" s="11"/>
     </row>
     <row r="152" spans="3:8">
       <c r="C152" s="3">
@@ -4971,7 +4967,7 @@
         <v>9</v>
       </c>
       <c r="E152" s="5">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F152" s="5" t="s">
         <v>291</v>
@@ -4979,7 +4975,7 @@
       <c r="G152" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="H152" s="10"/>
+      <c r="H152" s="11"/>
     </row>
     <row r="153" spans="3:8">
       <c r="C153" s="3">
@@ -4989,7 +4985,7 @@
         <v>9</v>
       </c>
       <c r="E153" s="5">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>292</v>
@@ -4997,7 +4993,7 @@
       <c r="G153" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="H153" s="10"/>
+      <c r="H153" s="11"/>
     </row>
     <row r="154" spans="3:8">
       <c r="C154" s="3">
@@ -5007,7 +5003,7 @@
         <v>9</v>
       </c>
       <c r="E154" s="5">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F154" s="5" t="s">
         <v>294</v>
@@ -5015,7 +5011,7 @@
       <c r="G154" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="H154" s="10"/>
+      <c r="H154" s="11"/>
     </row>
     <row r="155" spans="3:8">
       <c r="C155" s="3">
@@ -5025,7 +5021,7 @@
         <v>9</v>
       </c>
       <c r="E155" s="5">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F155" s="5" t="s">
         <v>296</v>
@@ -5033,7 +5029,7 @@
       <c r="G155" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="H155" s="10"/>
+      <c r="H155" s="11"/>
     </row>
     <row r="156" spans="3:8">
       <c r="C156" s="3">
@@ -5043,7 +5039,7 @@
         <v>9</v>
       </c>
       <c r="E156" s="5">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F156" s="5" t="s">
         <v>298</v>
@@ -5051,7 +5047,7 @@
       <c r="G156" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="H156" s="10"/>
+      <c r="H156" s="11"/>
     </row>
     <row r="157" spans="3:8">
       <c r="C157" s="3">
@@ -5061,7 +5057,7 @@
         <v>9</v>
       </c>
       <c r="E157" s="5">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F157" s="5" t="s">
         <v>300</v>
@@ -5069,7 +5065,7 @@
       <c r="G157" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="H157" s="10"/>
+      <c r="H157" s="11"/>
     </row>
     <row r="158" spans="3:8">
       <c r="C158" s="3">
@@ -5079,7 +5075,7 @@
         <v>9</v>
       </c>
       <c r="E158" s="5">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F158" s="5" t="s">
         <v>302</v>
@@ -5087,7 +5083,7 @@
       <c r="G158" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="H158" s="10"/>
+      <c r="H158" s="11"/>
     </row>
     <row r="159" spans="3:8">
       <c r="C159" s="3">
@@ -5097,7 +5093,7 @@
         <v>9</v>
       </c>
       <c r="E159" s="5">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F159" s="5" t="s">
         <v>304</v>
@@ -5105,7 +5101,7 @@
       <c r="G159" s="12" t="s">
         <v>305</v>
       </c>
-      <c r="H159" s="10"/>
+      <c r="H159" s="11"/>
     </row>
     <row r="160" spans="3:8">
       <c r="C160" s="3">
@@ -5483,7 +5479,7 @@
       <c r="G180" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="H180" s="10"/>
+      <c r="H180" s="6"/>
     </row>
     <row r="181" spans="3:8">
       <c r="C181" s="3">
@@ -5501,7 +5497,7 @@
       <c r="G181" s="12" t="s">
         <v>348</v>
       </c>
-      <c r="H181" s="10"/>
+      <c r="H181" s="6"/>
     </row>
     <row r="182" spans="3:8">
       <c r="C182" s="3">
@@ -5511,7 +5507,7 @@
         <v>9</v>
       </c>
       <c r="E182" s="5">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F182" s="5" t="s">
         <v>349</v>
@@ -5519,7 +5515,7 @@
       <c r="G182" s="12" t="s">
         <v>350</v>
       </c>
-      <c r="H182" s="11"/>
+      <c r="H182" s="6"/>
     </row>
     <row r="183" spans="3:8">
       <c r="C183" s="3">
@@ -5529,7 +5525,7 @@
         <v>9</v>
       </c>
       <c r="E183" s="5">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F183" s="5" t="s">
         <v>351</v>
@@ -5537,7 +5533,7 @@
       <c r="G183" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="H183" s="11"/>
+      <c r="H183" s="6"/>
     </row>
     <row r="184" spans="3:8">
       <c r="C184" s="3">
@@ -5588,9 +5584,10 @@
       <c r="F186" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="G186" s="16" t="s">
+      <c r="G186" s="15" t="s">
         <v>358</v>
       </c>
+      <c r="H186" s="6"/>
     </row>
     <row r="187" spans="3:8">
       <c r="C187" s="3">
@@ -5600,7 +5597,7 @@
         <v>9</v>
       </c>
       <c r="E187" s="5">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F187" s="5" t="s">
         <v>359</v>
@@ -5608,6 +5605,7 @@
       <c r="G187" s="12" t="s">
         <v>360</v>
       </c>
+      <c r="H187" s="6"/>
     </row>
     <row r="188" spans="3:8">
       <c r="C188" s="3">
@@ -5625,6 +5623,7 @@
       <c r="G188" s="12" t="s">
         <v>362</v>
       </c>
+      <c r="H188" s="10"/>
     </row>
     <row r="189" spans="3:8">
       <c r="C189" s="3">
@@ -5634,14 +5633,15 @@
         <v>9</v>
       </c>
       <c r="E189" s="5">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F189" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="G189" s="16" t="s">
+      <c r="G189" s="15" t="s">
         <v>364</v>
       </c>
+      <c r="H189" s="10"/>
     </row>
     <row r="190" spans="3:8">
       <c r="C190" s="3">
@@ -5656,7 +5656,7 @@
       <c r="F190" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="G190" s="16" t="s">
+      <c r="G190" s="15" t="s">
         <v>366</v>
       </c>
     </row>
@@ -5673,7 +5673,7 @@
       <c r="F191" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="G191" s="16" t="s">
+      <c r="G191" s="15" t="s">
         <v>368</v>
       </c>
     </row>
@@ -5724,7 +5724,7 @@
       <c r="F194" s="5" t="s">
         <v>373</v>
       </c>
-      <c r="G194" s="16" t="s">
+      <c r="G194" s="15" t="s">
         <v>374</v>
       </c>
     </row>
@@ -5741,7 +5741,9 @@
       <c r="F195" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="G195" s="12"/>
+      <c r="G195" s="15" t="s">
+        <v>376</v>
+      </c>
     </row>
     <row r="196" spans="3:7">
       <c r="C196" s="3">
@@ -5754,10 +5756,10 @@
         <v>202</v>
       </c>
       <c r="F196" s="5" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="197" spans="3:7">
@@ -5771,10 +5773,10 @@
         <v>203</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="383">
   <si>
     <t>Id</t>
   </si>
@@ -1207,6 +1207,12 @@
   </si>
   <si>
     <t>沧澜神域</t>
+  </si>
+  <si>
+    <t>WJBeta192</t>
+  </si>
+  <si>
+    <t>剑啸山河</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2283,7 +2289,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I197"/>
+  <dimension ref="C3:I198"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5747,36 +5753,53 @@
     </row>
     <row r="196" spans="3:7">
       <c r="C196" s="3">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="D196" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E196" s="5">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="F196" s="5" t="s">
         <v>377</v>
       </c>
-      <c r="G196" s="2" t="s">
+      <c r="G196" s="12" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="197" spans="3:7">
       <c r="C197" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D197" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E197" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F197" s="5" t="s">
         <v>379</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>380</v>
+      </c>
+    </row>
+    <row r="198" spans="3:7">
+      <c r="C198" s="3">
+        <v>203</v>
+      </c>
+      <c r="D198" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E198" s="5">
+        <v>203</v>
+      </c>
+      <c r="F198" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="G198" s="2" t="s">
+        <v>382</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="385">
   <si>
     <t>Id</t>
   </si>
@@ -1213,6 +1213,12 @@
   </si>
   <si>
     <t>剑啸山河</t>
+  </si>
+  <si>
+    <t>WJBeta193</t>
+  </si>
+  <si>
+    <t>精灵之森</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1427,12 +1433,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2289,7 +2295,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I198"/>
+  <dimension ref="C3:I199"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5770,36 +5776,53 @@
     </row>
     <row r="197" spans="3:7">
       <c r="C197" s="3">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="D197" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E197" s="5">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="F197" s="5" t="s">
         <v>379</v>
       </c>
-      <c r="G197" s="2" t="s">
+      <c r="G197" s="15" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="198" spans="3:7">
       <c r="C198" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D198" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E198" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F198" s="5" t="s">
         <v>381</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>382</v>
+      </c>
+    </row>
+    <row r="199" spans="3:7">
+      <c r="C199" s="3">
+        <v>203</v>
+      </c>
+      <c r="D199" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E199" s="5">
+        <v>203</v>
+      </c>
+      <c r="F199" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="G199" s="2" t="s">
+        <v>384</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="386">
   <si>
     <t>Id</t>
   </si>
@@ -1219,6 +1219,9 @@
   </si>
   <si>
     <t>精灵之森</t>
+  </si>
+  <si>
+    <t>WJBeta194</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1433,12 +1436,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2295,7 +2298,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I199"/>
+  <dimension ref="C3:I200"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5793,36 +5796,51 @@
     </row>
     <row r="198" spans="3:7">
       <c r="C198" s="3">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D198" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E198" s="5">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="F198" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="G198" s="2" t="s">
-        <v>382</v>
-      </c>
+      <c r="G198" s="12"/>
     </row>
     <row r="199" spans="3:7">
       <c r="C199" s="3">
+        <v>202</v>
+      </c>
+      <c r="D199" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E199" s="5">
+        <v>202</v>
+      </c>
+      <c r="F199" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="G199" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="200" spans="3:7">
+      <c r="C200" s="3">
         <v>203</v>
       </c>
-      <c r="D199" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E199" s="5">
+      <c r="D200" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E200" s="5">
         <v>203</v>
       </c>
-      <c r="F199" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="G199" s="2" t="s">
+      <c r="F200" s="5" t="s">
         <v>384</v>
+      </c>
+      <c r="G200" s="2" t="s">
+        <v>385</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="387">
   <si>
     <t>Id</t>
   </si>
@@ -1222,6 +1222,9 @@
   </si>
   <si>
     <t>WJBeta194</t>
+  </si>
+  <si>
+    <t>龙焰王座</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -5807,7 +5810,9 @@
       <c r="F198" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="G198" s="12"/>
+      <c r="G198" s="15" t="s">
+        <v>382</v>
+      </c>
     </row>
     <row r="199" spans="3:7">
       <c r="C199" s="3">
@@ -5820,10 +5825,10 @@
         <v>202</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="200" spans="3:7">
@@ -5837,10 +5842,10 @@
         <v>203</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="388">
   <si>
     <t>Id</t>
   </si>
@@ -1225,6 +1225,9 @@
   </si>
   <si>
     <t>龙焰王座</t>
+  </si>
+  <si>
+    <t>WJBeta195</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2301,7 +2304,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I200"/>
+  <dimension ref="C3:I201"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5816,36 +5819,51 @@
     </row>
     <row r="199" spans="3:7">
       <c r="C199" s="3">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D199" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E199" s="5">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="F199" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="G199" s="2" t="s">
-        <v>384</v>
-      </c>
+      <c r="G199" s="12"/>
     </row>
     <row r="200" spans="3:7">
       <c r="C200" s="3">
+        <v>202</v>
+      </c>
+      <c r="D200" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E200" s="5">
+        <v>202</v>
+      </c>
+      <c r="F200" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="G200" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="201" spans="3:7">
+      <c r="C201" s="3">
         <v>203</v>
       </c>
-      <c r="D200" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E200" s="5">
+      <c r="D201" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E201" s="5">
         <v>203</v>
       </c>
-      <c r="F200" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="G200" s="2" t="s">
+      <c r="F201" s="5" t="s">
         <v>386</v>
+      </c>
+      <c r="G201" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="16785" windowHeight="4560"/>
   </bookViews>
   <sheets>
     <sheet name="StartZoneConfig" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="389">
   <si>
     <t>Id</t>
   </si>
@@ -1228,6 +1228,9 @@
   </si>
   <si>
     <t>WJBeta195</t>
+  </si>
+  <si>
+    <t>逐鹿天下</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -5830,7 +5833,9 @@
       <c r="F199" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="G199" s="12"/>
+      <c r="G199" s="15" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="200" spans="3:7">
       <c r="C200" s="3">
@@ -5843,10 +5848,10 @@
         <v>202</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="201" spans="3:7">
@@ -5860,10 +5865,10 @@
         <v>203</v>
       </c>
       <c r="F201" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16785" windowHeight="4560"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="StartZoneConfig" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="390">
   <si>
     <t>Id</t>
   </si>
@@ -1231,6 +1231,9 @@
   </si>
   <si>
     <t>逐鹿天下</t>
+  </si>
+  <si>
+    <t>WJBeta196</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2307,7 +2310,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I201"/>
+  <dimension ref="C3:I202"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5839,36 +5842,51 @@
     </row>
     <row r="200" spans="3:7">
       <c r="C200" s="3">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D200" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E200" s="5">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="F200" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="G200" s="2" t="s">
-        <v>386</v>
-      </c>
+      <c r="G200" s="12"/>
     </row>
     <row r="201" spans="3:7">
       <c r="C201" s="3">
+        <v>202</v>
+      </c>
+      <c r="D201" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E201" s="5">
+        <v>202</v>
+      </c>
+      <c r="F201" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="G201" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="202" spans="3:7">
+      <c r="C202" s="3">
         <v>203</v>
       </c>
-      <c r="D201" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E201" s="5">
+      <c r="D202" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E202" s="5">
         <v>203</v>
       </c>
-      <c r="F201" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="G201" s="2" t="s">
+      <c r="F202" s="5" t="s">
         <v>388</v>
+      </c>
+      <c r="G202" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="391">
   <si>
     <t>Id</t>
   </si>
@@ -1234,6 +1234,9 @@
   </si>
   <si>
     <t>WJBeta196</t>
+  </si>
+  <si>
+    <t>金马迎春</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -5853,7 +5856,9 @@
       <c r="F200" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="G200" s="12"/>
+      <c r="G200" s="15" t="s">
+        <v>386</v>
+      </c>
     </row>
     <row r="201" spans="3:7">
       <c r="C201" s="3">
@@ -5866,10 +5871,10 @@
         <v>202</v>
       </c>
       <c r="F201" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="202" spans="3:7">
@@ -5883,10 +5888,10 @@
         <v>203</v>
       </c>
       <c r="F202" s="5" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="393">
   <si>
     <t>Id</t>
   </si>
@@ -1237,6 +1237,12 @@
   </si>
   <si>
     <t>金马迎春</t>
+  </si>
+  <si>
+    <t>WJBeta197</t>
+  </si>
+  <si>
+    <t>御剑天涯</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2313,7 +2319,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I202"/>
+  <dimension ref="C3:I203"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5862,36 +5868,53 @@
     </row>
     <row r="201" spans="3:7">
       <c r="C201" s="3">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D201" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E201" s="5">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F201" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="G201" s="2" t="s">
+      <c r="G201" s="15" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="202" spans="3:7">
       <c r="C202" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D202" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E202" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F202" s="5" t="s">
         <v>389</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>390</v>
+      </c>
+    </row>
+    <row r="203" spans="3:7">
+      <c r="C203" s="3">
+        <v>203</v>
+      </c>
+      <c r="D203" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E203" s="5">
+        <v>203</v>
+      </c>
+      <c r="F203" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="G203" s="2" t="s">
+        <v>392</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="395">
   <si>
     <t>Id</t>
   </si>
@@ -1243,6 +1243,12 @@
   </si>
   <si>
     <t>御剑天涯</t>
+  </si>
+  <si>
+    <t>WJBeta198</t>
+  </si>
+  <si>
+    <t>马踏山河</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2319,7 +2325,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I203"/>
+  <dimension ref="C3:I204"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5587,7 +5593,7 @@
       <c r="G184" s="12" t="s">
         <v>354</v>
       </c>
-      <c r="H184" s="10"/>
+      <c r="H184" s="8"/>
     </row>
     <row r="185" spans="3:8">
       <c r="C185" s="3">
@@ -5605,7 +5611,7 @@
       <c r="G185" s="12" t="s">
         <v>356</v>
       </c>
-      <c r="H185" s="10"/>
+      <c r="H185" s="8"/>
     </row>
     <row r="186" spans="3:8">
       <c r="C186" s="3">
@@ -5615,7 +5621,7 @@
         <v>9</v>
       </c>
       <c r="E186" s="5">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F186" s="5" t="s">
         <v>357</v>
@@ -5623,7 +5629,7 @@
       <c r="G186" s="15" t="s">
         <v>358</v>
       </c>
-      <c r="H186" s="6"/>
+      <c r="H186" s="8"/>
     </row>
     <row r="187" spans="3:8">
       <c r="C187" s="3">
@@ -5633,7 +5639,7 @@
         <v>9</v>
       </c>
       <c r="E187" s="5">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F187" s="5" t="s">
         <v>359</v>
@@ -5641,7 +5647,7 @@
       <c r="G187" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="H187" s="6"/>
+      <c r="H187" s="8"/>
     </row>
     <row r="188" spans="3:8">
       <c r="C188" s="3">
@@ -5695,6 +5701,7 @@
       <c r="G190" s="15" t="s">
         <v>366</v>
       </c>
+      <c r="H190" s="8"/>
     </row>
     <row r="191" spans="3:8">
       <c r="C191" s="3">
@@ -5704,7 +5711,7 @@
         <v>9</v>
       </c>
       <c r="E191" s="5">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F191" s="5" t="s">
         <v>367</v>
@@ -5712,6 +5719,7 @@
       <c r="G191" s="15" t="s">
         <v>368</v>
       </c>
+      <c r="H191" s="8"/>
     </row>
     <row r="192" spans="3:8">
       <c r="C192" s="3">
@@ -5729,8 +5737,9 @@
       <c r="G192" s="12" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="193" spans="3:7">
+      <c r="H192" s="10"/>
+    </row>
+    <row r="193" spans="3:8">
       <c r="C193" s="3">
         <v>189</v>
       </c>
@@ -5738,7 +5747,7 @@
         <v>9</v>
       </c>
       <c r="E193" s="5">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F193" s="5" t="s">
         <v>371</v>
@@ -5746,8 +5755,9 @@
       <c r="G193" s="12" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="194" spans="3:7">
+      <c r="H193" s="10"/>
+    </row>
+    <row r="194" spans="3:8">
       <c r="C194" s="3">
         <v>190</v>
       </c>
@@ -5763,8 +5773,9 @@
       <c r="G194" s="15" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="195" spans="3:7">
+      <c r="H194" s="11"/>
+    </row>
+    <row r="195" spans="3:8">
       <c r="C195" s="3">
         <v>191</v>
       </c>
@@ -5772,7 +5783,7 @@
         <v>9</v>
       </c>
       <c r="E195" s="5">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F195" s="5" t="s">
         <v>375</v>
@@ -5780,8 +5791,9 @@
       <c r="G195" s="15" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="196" spans="3:7">
+      <c r="H195" s="11"/>
+    </row>
+    <row r="196" spans="3:8">
       <c r="C196" s="3">
         <v>192</v>
       </c>
@@ -5797,8 +5809,9 @@
       <c r="G196" s="12" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="197" spans="3:7">
+      <c r="H196" s="10"/>
+    </row>
+    <row r="197" spans="3:8">
       <c r="C197" s="3">
         <v>193</v>
       </c>
@@ -5806,7 +5819,7 @@
         <v>9</v>
       </c>
       <c r="E197" s="5">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F197" s="5" t="s">
         <v>379</v>
@@ -5814,8 +5827,9 @@
       <c r="G197" s="15" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="198" spans="3:7">
+      <c r="H197" s="10"/>
+    </row>
+    <row r="198" spans="3:8">
       <c r="C198" s="3">
         <v>194</v>
       </c>
@@ -5832,7 +5846,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="199" spans="3:7">
+    <row r="199" spans="3:8">
       <c r="C199" s="3">
         <v>195</v>
       </c>
@@ -5849,7 +5863,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="200" spans="3:7">
+    <row r="200" spans="3:8">
       <c r="C200" s="3">
         <v>196</v>
       </c>
@@ -5866,7 +5880,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="201" spans="3:7">
+    <row r="201" spans="3:8">
       <c r="C201" s="3">
         <v>197</v>
       </c>
@@ -5883,38 +5897,55 @@
         <v>388</v>
       </c>
     </row>
-    <row r="202" spans="3:7">
+    <row r="202" spans="3:8">
       <c r="C202" s="3">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D202" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E202" s="5">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F202" s="5" t="s">
         <v>389</v>
       </c>
-      <c r="G202" s="2" t="s">
+      <c r="G202" s="15" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="203" spans="3:7">
+    <row r="203" spans="3:8">
       <c r="C203" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D203" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E203" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F203" s="5" t="s">
         <v>391</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>392</v>
+      </c>
+    </row>
+    <row r="204" spans="3:8">
+      <c r="C204" s="3">
+        <v>203</v>
+      </c>
+      <c r="D204" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E204" s="5">
+        <v>203</v>
+      </c>
+      <c r="F204" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="G204" s="2" t="s">
+        <v>394</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="396">
   <si>
     <t>Id</t>
   </si>
@@ -1249,6 +1249,9 @@
   </si>
   <si>
     <t>马踏山河</t>
+  </si>
+  <si>
+    <t>WJBeta199</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2325,7 +2328,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I204"/>
+  <dimension ref="C3:I205"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5916,36 +5919,51 @@
     </row>
     <row r="203" spans="3:8">
       <c r="C203" s="3">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D203" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E203" s="5">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F203" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="G203" s="2" t="s">
-        <v>392</v>
-      </c>
+      <c r="G203" s="15"/>
     </row>
     <row r="204" spans="3:8">
       <c r="C204" s="3">
+        <v>202</v>
+      </c>
+      <c r="D204" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E204" s="5">
+        <v>202</v>
+      </c>
+      <c r="F204" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="G204" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="205" spans="3:8">
+      <c r="C205" s="3">
         <v>203</v>
       </c>
-      <c r="D204" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E204" s="5">
+      <c r="D205" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E205" s="5">
         <v>203</v>
       </c>
-      <c r="F204" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="G204" s="2" t="s">
+      <c r="F205" s="5" t="s">
         <v>394</v>
+      </c>
+      <c r="G205" s="2" t="s">
+        <v>395</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="397">
   <si>
     <t>Id</t>
   </si>
@@ -1252,6 +1252,9 @@
   </si>
   <si>
     <t>WJBeta199</t>
+  </si>
+  <si>
+    <t>烽火逐鹿</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -5930,7 +5933,9 @@
       <c r="F203" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="G203" s="15"/>
+      <c r="G203" s="15" t="s">
+        <v>392</v>
+      </c>
     </row>
     <row r="204" spans="3:8">
       <c r="C204" s="3">
@@ -5943,10 +5948,10 @@
         <v>202</v>
       </c>
       <c r="F204" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="205" spans="3:8">
@@ -5960,10 +5965,10 @@
         <v>203</v>
       </c>
       <c r="F205" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="398">
   <si>
     <t>Id</t>
   </si>
@@ -1255,6 +1255,9 @@
   </si>
   <si>
     <t>烽火逐鹿</t>
+  </si>
+  <si>
+    <t>WJBeta200</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2331,7 +2334,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I205"/>
+  <dimension ref="C3:I206"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5939,36 +5942,51 @@
     </row>
     <row r="204" spans="3:8">
       <c r="C204" s="3">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D204" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E204" s="5">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F204" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="G204" s="2" t="s">
-        <v>394</v>
-      </c>
+      <c r="G204" s="15"/>
     </row>
     <row r="205" spans="3:8">
       <c r="C205" s="3">
+        <v>202</v>
+      </c>
+      <c r="D205" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E205" s="5">
+        <v>202</v>
+      </c>
+      <c r="F205" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="G205" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="206" spans="3:8">
+      <c r="C206" s="3">
         <v>203</v>
       </c>
-      <c r="D205" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E205" s="5">
+      <c r="D206" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E206" s="5">
         <v>203</v>
       </c>
-      <c r="F205" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="G205" s="2" t="s">
+      <c r="F206" s="5" t="s">
         <v>396</v>
+      </c>
+      <c r="G206" s="2" t="s">
+        <v>397</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="400">
   <si>
     <t>Id</t>
   </si>
@@ -1258,6 +1258,9 @@
   </si>
   <si>
     <t>WJBeta200</t>
+  </si>
+  <si>
+    <t>梦幻湖畔</t>
   </si>
   <si>
     <t>WJBeta211</t>
@@ -5956,7 +5959,9 @@
       <c r="F204" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="G204" s="15"/>
+      <c r="G204" s="15" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="205" spans="3:8">
       <c r="C205" s="3">
@@ -5969,7 +5974,7 @@
         <v>211</v>
       </c>
       <c r="F205" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G205" s="15"/>
     </row>
@@ -5984,10 +5989,10 @@
         <v>202</v>
       </c>
       <c r="F206" s="5" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="207" spans="3:8">
@@ -6001,10 +6006,10 @@
         <v>203</v>
       </c>
       <c r="F207" s="5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="401">
   <si>
     <t>Id</t>
   </si>
@@ -1263,19 +1263,22 @@
     <t>梦幻湖畔</t>
   </si>
   <si>
+    <t>WJBeta202(center)</t>
+  </si>
+  <si>
+    <t>#中心服</t>
+  </si>
+  <si>
+    <t>WJBeta203(robot)</t>
+  </si>
+  <si>
+    <t>#机器人</t>
+  </si>
+  <si>
+    <t>201-210是特殊区服</t>
+  </si>
+  <si>
     <t>WJBeta211</t>
-  </si>
-  <si>
-    <t>WJBeta202(center)</t>
-  </si>
-  <si>
-    <t>#中心服</t>
-  </si>
-  <si>
-    <t>WJBeta203(robot)</t>
-  </si>
-  <si>
-    <t>#机器人</t>
   </si>
 </sst>
 </file>
@@ -1498,6 +1501,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1517,12 +1526,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF7030A0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1967,31 +1970,37 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2340,2297 +2349,2297 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I207"/>
+  <dimension ref="A3:I207"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="41.125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="33.375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="21" style="3" customWidth="1"/>
-    <col min="7" max="7" width="9" style="2"/>
-    <col min="8" max="8" width="23.75" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="12.75" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="41.125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="33.375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="21" style="4" customWidth="1"/>
+    <col min="7" max="7" width="9" style="3"/>
+    <col min="8" max="8" width="23.75" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="3" spans="3:8">
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="3:8">
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="3:8">
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="3:8">
-      <c r="C6" s="5">
+      <c r="C6" s="6">
         <v>1</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="5">
+      <c r="D6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="6">
         <v>1</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="3:8">
-      <c r="C7" s="3">
+      <c r="C7" s="4">
         <v>2</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="5">
+      <c r="D7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="6">
         <v>3</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="3:8">
-      <c r="C8" s="3">
+      <c r="C8" s="4">
         <v>3</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="5">
+      <c r="D8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="6">
         <v>3</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="3:8">
-      <c r="C9" s="3">
+      <c r="C9" s="4">
         <v>4</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="5">
+      <c r="D9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="6">
         <v>3</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="3:8">
-      <c r="C10" s="3">
+      <c r="C10" s="4">
         <v>5</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="5">
+      <c r="D10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="6">
         <v>5</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="3" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="11" spans="3:8">
-      <c r="C11" s="3">
+      <c r="C11" s="4">
         <v>6</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="5">
+      <c r="D11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="6">
         <v>5</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" spans="3:8">
-      <c r="C12" s="5">
+      <c r="C12" s="6">
         <v>7</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="5">
+      <c r="D12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="6">
         <v>5</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" spans="3:8">
-      <c r="C13" s="3">
+      <c r="C13" s="4">
         <v>8</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="5">
+      <c r="D13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="6">
         <v>5</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="3:8">
-      <c r="C14" s="3">
-        <v>9</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="3">
-        <v>9</v>
-      </c>
-      <c r="F14" s="5" t="s">
+      <c r="C14" s="4">
+        <v>9</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="4">
+        <v>9</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="15" spans="3:8">
-      <c r="C15" s="3">
+      <c r="C15" s="4">
         <v>10</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="5">
-        <v>9</v>
-      </c>
-      <c r="F15" s="5" t="s">
+      <c r="D15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="6">
+        <v>9</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="3" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="16" spans="3:8">
-      <c r="C16" s="5">
+      <c r="C16" s="6">
         <v>11</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="3">
-        <v>9</v>
-      </c>
-      <c r="F16" s="5" t="s">
+      <c r="D16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="4">
+        <v>9</v>
+      </c>
+      <c r="F16" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" spans="3:8">
-      <c r="C17" s="3">
+      <c r="C17" s="4">
         <v>12</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="3">
+      <c r="D17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="4">
         <v>12</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H17" s="6"/>
+      <c r="H17" s="7"/>
     </row>
     <row r="18" spans="3:8">
-      <c r="C18" s="3">
+      <c r="C18" s="4">
         <v>13</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="5">
+      <c r="D18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="6">
         <v>12</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="6"/>
+      <c r="H18" s="7"/>
     </row>
     <row r="19" spans="3:8">
-      <c r="C19" s="3">
+      <c r="C19" s="4">
         <v>14</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="5">
+      <c r="D19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="6">
         <v>12</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H19" s="6"/>
+      <c r="H19" s="7"/>
     </row>
     <row r="20" spans="3:8">
-      <c r="C20" s="5">
+      <c r="C20" s="6">
         <v>15</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20" s="5">
+      <c r="D20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="6">
         <v>12</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H20" s="6"/>
+      <c r="H20" s="7"/>
     </row>
     <row r="21" spans="3:8">
-      <c r="C21" s="3">
+      <c r="C21" s="4">
         <v>16</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" s="5">
+      <c r="D21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="6">
         <v>12</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H21" s="6"/>
+      <c r="H21" s="7"/>
     </row>
     <row r="22" spans="3:8">
-      <c r="C22" s="3">
+      <c r="C22" s="4">
         <v>17</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" s="5">
+      <c r="D22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="6">
         <v>12</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H22" s="6"/>
+      <c r="H22" s="7"/>
     </row>
     <row r="23" spans="3:8">
-      <c r="C23" s="3">
+      <c r="C23" s="4">
         <v>18</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23" s="5">
+      <c r="D23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="6">
         <v>12</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="H23" s="7"/>
+      <c r="H23" s="8"/>
     </row>
     <row r="24" spans="3:8">
-      <c r="C24" s="3">
+      <c r="C24" s="4">
         <v>19</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E24" s="5">
+      <c r="D24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="6">
         <v>12</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="H24" s="7"/>
+      <c r="H24" s="8"/>
     </row>
     <row r="25" spans="3:8">
-      <c r="C25" s="3">
+      <c r="C25" s="4">
         <v>20</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E25" s="5">
+      <c r="D25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="6">
         <v>12</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H25" s="6"/>
+      <c r="H25" s="7"/>
     </row>
     <row r="26" spans="3:8">
-      <c r="C26" s="3">
+      <c r="C26" s="4">
         <v>21</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26" s="5">
+      <c r="D26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="6">
         <v>12</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G26" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H26" s="6"/>
+      <c r="H26" s="7"/>
     </row>
     <row r="27" spans="3:8">
-      <c r="C27" s="3">
+      <c r="C27" s="4">
         <v>22</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E27" s="3">
+      <c r="D27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="4">
         <v>12</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="F27" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H27" s="7"/>
+      <c r="H27" s="8"/>
     </row>
     <row r="28" spans="3:8">
-      <c r="C28" s="3">
+      <c r="C28" s="4">
         <v>23</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E28" s="5">
+      <c r="D28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="6">
         <v>12</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="F28" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H28" s="7"/>
+      <c r="H28" s="8"/>
     </row>
     <row r="29" spans="3:8">
-      <c r="C29" s="3">
+      <c r="C29" s="4">
         <v>24</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E29" s="5">
+      <c r="D29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="6">
         <v>12</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="F29" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="G29" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H29" s="7"/>
+      <c r="H29" s="8"/>
     </row>
     <row r="30" spans="3:8">
-      <c r="C30" s="3">
+      <c r="C30" s="4">
         <v>25</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E30" s="5">
+      <c r="D30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="6">
         <v>12</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="F30" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G30" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="H30" s="7"/>
+      <c r="H30" s="8"/>
     </row>
     <row r="31" spans="3:8">
-      <c r="C31" s="3">
+      <c r="C31" s="4">
         <v>26</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E31" s="5">
+      <c r="D31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="6">
         <v>12</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="F31" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="G31" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="H31" s="6"/>
+      <c r="H31" s="7"/>
     </row>
     <row r="32" spans="3:8">
-      <c r="C32" s="3">
+      <c r="C32" s="4">
         <v>27</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E32" s="5">
+      <c r="D32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="6">
         <v>12</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="F32" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="G32" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="H32" s="6"/>
+      <c r="H32" s="7"/>
     </row>
     <row r="33" spans="3:8">
-      <c r="C33" s="3">
+      <c r="C33" s="4">
         <v>28</v>
       </c>
-      <c r="D33" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E33" s="5">
+      <c r="D33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33" s="6">
         <v>12</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="F33" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G33" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="H33" s="6"/>
+      <c r="H33" s="7"/>
     </row>
     <row r="34" spans="3:8">
-      <c r="C34" s="3">
+      <c r="C34" s="4">
         <v>29</v>
       </c>
-      <c r="D34" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" s="5">
+      <c r="D34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="6">
         <v>12</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="F34" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G34" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H34" s="7"/>
+      <c r="H34" s="8"/>
     </row>
     <row r="35" spans="3:8">
-      <c r="C35" s="3">
+      <c r="C35" s="4">
         <v>30</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" s="5">
+      <c r="D35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" s="6">
         <v>12</v>
       </c>
-      <c r="F35" s="5" t="s">
+      <c r="F35" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G35" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H35" s="6"/>
+      <c r="H35" s="7"/>
     </row>
     <row r="36" spans="3:8">
-      <c r="C36" s="3">
+      <c r="C36" s="4">
         <v>31</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E36" s="5">
+      <c r="D36" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" s="6">
         <v>12</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="F36" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G36" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H36" s="6"/>
+      <c r="H36" s="7"/>
     </row>
     <row r="37" spans="3:8">
-      <c r="C37" s="3">
+      <c r="C37" s="4">
         <v>32</v>
       </c>
-      <c r="D37" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E37" s="5">
+      <c r="D37" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" s="6">
         <v>32</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="F37" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G37" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H37" s="8"/>
+      <c r="H37" s="9"/>
     </row>
     <row r="38" spans="3:8">
-      <c r="C38" s="3">
+      <c r="C38" s="4">
         <v>33</v>
       </c>
-      <c r="D38" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E38" s="5">
+      <c r="D38" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" s="6">
         <v>32</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="F38" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="G38" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="H38" s="8"/>
+      <c r="H38" s="9"/>
     </row>
     <row r="39" spans="3:8">
-      <c r="C39" s="3">
+      <c r="C39" s="4">
         <v>34</v>
       </c>
-      <c r="D39" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E39" s="5">
+      <c r="D39" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" s="6">
         <v>32</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="F39" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="G39" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="H39" s="8"/>
+      <c r="H39" s="9"/>
     </row>
     <row r="40" spans="3:8">
-      <c r="C40" s="3">
+      <c r="C40" s="4">
         <v>35</v>
       </c>
-      <c r="D40" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E40" s="5">
+      <c r="D40" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" s="6">
         <v>32</v>
       </c>
-      <c r="F40" s="5" t="s">
+      <c r="F40" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="G40" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="H40" s="8"/>
+      <c r="H40" s="9"/>
     </row>
     <row r="41" spans="3:8">
-      <c r="C41" s="3">
+      <c r="C41" s="4">
         <v>36</v>
       </c>
-      <c r="D41" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E41" s="5">
+      <c r="D41" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="6">
         <v>32</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="F41" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="G41" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="H41" s="8"/>
+      <c r="H41" s="9"/>
     </row>
     <row r="42" spans="3:8">
-      <c r="C42" s="3">
+      <c r="C42" s="4">
         <v>37</v>
       </c>
-      <c r="D42" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E42" s="5">
+      <c r="D42" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="6">
         <v>32</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="F42" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="G42" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H42" s="8"/>
+      <c r="H42" s="9"/>
     </row>
     <row r="43" spans="3:8">
-      <c r="C43" s="3">
+      <c r="C43" s="4">
         <v>38</v>
       </c>
-      <c r="D43" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E43" s="5">
+      <c r="D43" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43" s="6">
         <v>32</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="F43" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="G43" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="H43" s="9"/>
+      <c r="H43" s="10"/>
     </row>
     <row r="44" spans="3:8">
-      <c r="C44" s="3">
+      <c r="C44" s="4">
         <v>39</v>
       </c>
-      <c r="D44" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E44" s="5">
+      <c r="D44" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" s="6">
         <v>32</v>
       </c>
-      <c r="F44" s="5" t="s">
+      <c r="F44" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="G44" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H44" s="9"/>
+      <c r="H44" s="10"/>
     </row>
     <row r="45" spans="3:8">
-      <c r="C45" s="3">
+      <c r="C45" s="4">
         <v>40</v>
       </c>
-      <c r="D45" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E45" s="5">
+      <c r="D45" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45" s="6">
         <v>32</v>
       </c>
-      <c r="F45" s="5" t="s">
+      <c r="F45" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="G45" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="H45" s="8"/>
+      <c r="H45" s="9"/>
     </row>
     <row r="46" spans="3:8">
-      <c r="C46" s="3">
+      <c r="C46" s="4">
         <v>41</v>
       </c>
-      <c r="D46" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E46" s="5">
+      <c r="D46" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E46" s="6">
         <v>32</v>
       </c>
-      <c r="F46" s="5" t="s">
+      <c r="F46" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="G46" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="H46" s="8"/>
+      <c r="H46" s="9"/>
     </row>
     <row r="47" spans="3:8">
-      <c r="C47" s="3">
+      <c r="C47" s="4">
         <v>42</v>
       </c>
-      <c r="D47" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E47" s="5">
+      <c r="D47" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" s="6">
         <v>32</v>
       </c>
-      <c r="F47" s="5" t="s">
+      <c r="F47" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="G47" s="2" t="s">
+      <c r="G47" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="H47" s="8"/>
+      <c r="H47" s="9"/>
     </row>
     <row r="48" spans="3:8">
-      <c r="C48" s="3">
+      <c r="C48" s="4">
         <v>43</v>
       </c>
-      <c r="D48" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E48" s="5">
+      <c r="D48" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48" s="6">
         <v>32</v>
       </c>
-      <c r="F48" s="5" t="s">
+      <c r="F48" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="G48" s="2" t="s">
+      <c r="G48" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="H48" s="8"/>
+      <c r="H48" s="9"/>
     </row>
     <row r="49" spans="3:8">
-      <c r="C49" s="3">
+      <c r="C49" s="4">
         <v>44</v>
       </c>
-      <c r="D49" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E49" s="5">
+      <c r="D49" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" s="6">
         <v>32</v>
       </c>
-      <c r="F49" s="5" t="s">
+      <c r="F49" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="G49" s="2" t="s">
+      <c r="G49" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="H49" s="8"/>
+      <c r="H49" s="9"/>
     </row>
     <row r="50" spans="3:8">
-      <c r="C50" s="3">
+      <c r="C50" s="4">
         <v>45</v>
       </c>
-      <c r="D50" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E50" s="5">
+      <c r="D50" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" s="6">
         <v>32</v>
       </c>
-      <c r="F50" s="5" t="s">
+      <c r="F50" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="G50" s="2" t="s">
+      <c r="G50" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="H50" s="8"/>
+      <c r="H50" s="9"/>
     </row>
     <row r="51" spans="3:8">
-      <c r="C51" s="3">
+      <c r="C51" s="4">
         <v>46</v>
       </c>
-      <c r="D51" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E51" s="5">
+      <c r="D51" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" s="6">
         <v>32</v>
       </c>
-      <c r="F51" s="5" t="s">
+      <c r="F51" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="G51" s="2" t="s">
+      <c r="G51" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="H51" s="8"/>
+      <c r="H51" s="9"/>
     </row>
     <row r="52" ht="13" customHeight="1" spans="3:8">
-      <c r="C52" s="3">
+      <c r="C52" s="4">
         <v>47</v>
       </c>
-      <c r="D52" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E52" s="5">
+      <c r="D52" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E52" s="6">
         <v>32</v>
       </c>
-      <c r="F52" s="5" t="s">
+      <c r="F52" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="G52" s="2" t="s">
+      <c r="G52" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="H52" s="8"/>
+      <c r="H52" s="9"/>
     </row>
     <row r="53" spans="3:8">
-      <c r="C53" s="3">
+      <c r="C53" s="4">
         <v>48</v>
       </c>
-      <c r="D53" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E53" s="5">
+      <c r="D53" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" s="6">
         <v>48</v>
       </c>
-      <c r="F53" s="5" t="s">
+      <c r="F53" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="G53" s="2" t="s">
+      <c r="G53" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="H53" s="10"/>
+      <c r="H53" s="11"/>
     </row>
     <row r="54" spans="3:8">
-      <c r="C54" s="3">
+      <c r="C54" s="4">
         <v>49</v>
       </c>
-      <c r="D54" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E54" s="5">
+      <c r="D54" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54" s="6">
         <v>48</v>
       </c>
-      <c r="F54" s="5" t="s">
+      <c r="F54" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="G54" s="2" t="s">
+      <c r="G54" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="H54" s="10"/>
+      <c r="H54" s="11"/>
     </row>
     <row r="55" spans="3:8">
-      <c r="C55" s="3">
+      <c r="C55" s="4">
         <v>50</v>
       </c>
-      <c r="D55" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E55" s="5">
+      <c r="D55" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55" s="6">
         <v>48</v>
       </c>
-      <c r="F55" s="5" t="s">
+      <c r="F55" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="G55" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H55" s="10"/>
+      <c r="H55" s="11"/>
     </row>
     <row r="56" spans="3:8">
-      <c r="C56" s="3">
+      <c r="C56" s="4">
         <v>51</v>
       </c>
-      <c r="D56" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E56" s="5">
+      <c r="D56" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56" s="6">
         <v>48</v>
       </c>
-      <c r="F56" s="5" t="s">
+      <c r="F56" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="G56" s="2" t="s">
+      <c r="G56" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H56" s="10"/>
+      <c r="H56" s="11"/>
     </row>
     <row r="57" spans="3:8">
-      <c r="C57" s="3">
+      <c r="C57" s="4">
         <v>52</v>
       </c>
-      <c r="D57" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E57" s="5">
+      <c r="D57" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" s="6">
         <v>48</v>
       </c>
-      <c r="F57" s="5" t="s">
+      <c r="F57" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="G57" s="2" t="s">
+      <c r="G57" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="H57" s="10"/>
+      <c r="H57" s="11"/>
     </row>
     <row r="58" spans="3:8">
-      <c r="C58" s="3">
+      <c r="C58" s="4">
         <v>53</v>
       </c>
-      <c r="D58" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E58" s="5">
+      <c r="D58" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58" s="6">
         <v>48</v>
       </c>
-      <c r="F58" s="5" t="s">
+      <c r="F58" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="G58" s="2" t="s">
+      <c r="G58" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="H58" s="10"/>
+      <c r="H58" s="11"/>
     </row>
     <row r="59" spans="3:8">
-      <c r="C59" s="3">
+      <c r="C59" s="4">
         <v>54</v>
       </c>
-      <c r="D59" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E59" s="5">
+      <c r="D59" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E59" s="6">
         <v>48</v>
       </c>
-      <c r="F59" s="5" t="s">
+      <c r="F59" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="G59" s="2" t="s">
+      <c r="G59" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="H59" s="10"/>
+      <c r="H59" s="11"/>
     </row>
     <row r="60" spans="3:8">
-      <c r="C60" s="3">
+      <c r="C60" s="4">
         <v>55</v>
       </c>
-      <c r="D60" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E60" s="5">
+      <c r="D60" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E60" s="6">
         <v>48</v>
       </c>
-      <c r="F60" s="5" t="s">
+      <c r="F60" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G60" s="2" t="s">
+      <c r="G60" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="H60" s="10"/>
+      <c r="H60" s="11"/>
     </row>
     <row r="61" spans="3:8">
-      <c r="C61" s="3">
+      <c r="C61" s="4">
         <v>56</v>
       </c>
-      <c r="D61" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E61" s="5">
+      <c r="D61" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E61" s="6">
         <v>48</v>
       </c>
-      <c r="F61" s="5" t="s">
+      <c r="F61" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="G61" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="H61" s="10"/>
+      <c r="H61" s="11"/>
     </row>
     <row r="62" spans="3:8">
-      <c r="C62" s="3">
+      <c r="C62" s="4">
         <v>57</v>
       </c>
-      <c r="D62" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E62" s="5">
+      <c r="D62" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E62" s="6">
         <v>48</v>
       </c>
-      <c r="F62" s="5" t="s">
+      <c r="F62" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="G62" s="2" t="s">
+      <c r="G62" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="H62" s="10"/>
+      <c r="H62" s="11"/>
     </row>
     <row r="63" spans="3:8">
-      <c r="C63" s="3">
+      <c r="C63" s="4">
         <v>58</v>
       </c>
-      <c r="D63" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E63" s="5">
+      <c r="D63" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E63" s="6">
         <v>48</v>
       </c>
-      <c r="F63" s="5" t="s">
+      <c r="F63" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="G63" s="2" t="s">
+      <c r="G63" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="H63" s="10"/>
+      <c r="H63" s="11"/>
     </row>
     <row r="64" spans="3:8">
-      <c r="C64" s="3">
+      <c r="C64" s="4">
         <v>59</v>
       </c>
-      <c r="D64" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E64" s="5">
+      <c r="D64" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E64" s="6">
         <v>48</v>
       </c>
-      <c r="F64" s="5" t="s">
+      <c r="F64" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="G64" s="2" t="s">
+      <c r="G64" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="H64" s="10"/>
+      <c r="H64" s="11"/>
     </row>
     <row r="65" spans="3:8">
-      <c r="C65" s="3">
+      <c r="C65" s="4">
         <v>60</v>
       </c>
-      <c r="D65" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E65" s="5">
+      <c r="D65" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E65" s="6">
         <v>48</v>
       </c>
-      <c r="F65" s="5" t="s">
+      <c r="F65" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="G65" s="2" t="s">
+      <c r="G65" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="H65" s="10"/>
+      <c r="H65" s="11"/>
     </row>
     <row r="66" spans="3:8">
-      <c r="C66" s="3">
+      <c r="C66" s="4">
         <v>61</v>
       </c>
-      <c r="D66" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E66" s="5">
+      <c r="D66" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E66" s="6">
         <v>48</v>
       </c>
-      <c r="F66" s="5" t="s">
+      <c r="F66" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="G66" s="2" t="s">
+      <c r="G66" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="H66" s="10"/>
+      <c r="H66" s="11"/>
     </row>
     <row r="67" spans="3:8">
-      <c r="C67" s="3">
+      <c r="C67" s="4">
         <v>62</v>
       </c>
-      <c r="D67" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E67" s="5">
+      <c r="D67" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E67" s="6">
         <v>48</v>
       </c>
-      <c r="F67" s="5" t="s">
+      <c r="F67" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="G67" s="2" t="s">
+      <c r="G67" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="H67" s="10"/>
+      <c r="H67" s="11"/>
     </row>
     <row r="68" spans="3:8">
-      <c r="C68" s="3">
+      <c r="C68" s="4">
         <v>63</v>
       </c>
-      <c r="D68" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E68" s="5">
+      <c r="D68" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E68" s="6">
         <v>48</v>
       </c>
-      <c r="F68" s="5" t="s">
+      <c r="F68" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="G68" s="2" t="s">
+      <c r="G68" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="H68" s="10"/>
+      <c r="H68" s="11"/>
     </row>
     <row r="69" spans="3:8">
-      <c r="C69" s="3">
+      <c r="C69" s="4">
         <v>64</v>
       </c>
-      <c r="D69" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E69" s="5">
+      <c r="D69" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E69" s="6">
         <v>64</v>
       </c>
-      <c r="F69" s="5" t="s">
+      <c r="F69" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="G69" s="2" t="s">
+      <c r="G69" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H69" s="11"/>
+      <c r="H69" s="2"/>
     </row>
     <row r="70" spans="3:8">
-      <c r="C70" s="3">
+      <c r="C70" s="4">
         <v>65</v>
       </c>
-      <c r="D70" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E70" s="5">
+      <c r="D70" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70" s="6">
         <v>64</v>
       </c>
-      <c r="F70" s="5" t="s">
+      <c r="F70" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="G70" s="2" t="s">
+      <c r="G70" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="H70" s="11"/>
+      <c r="H70" s="2"/>
     </row>
     <row r="71" spans="3:8">
-      <c r="C71" s="3">
+      <c r="C71" s="4">
         <v>66</v>
       </c>
-      <c r="D71" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E71" s="5">
+      <c r="D71" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E71" s="6">
         <v>64</v>
       </c>
-      <c r="F71" s="5" t="s">
+      <c r="F71" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="G71" s="2" t="s">
+      <c r="G71" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="H71" s="11"/>
+      <c r="H71" s="2"/>
     </row>
     <row r="72" spans="3:8">
-      <c r="C72" s="3">
+      <c r="C72" s="4">
         <v>67</v>
       </c>
-      <c r="D72" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E72" s="5">
+      <c r="D72" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E72" s="6">
         <v>64</v>
       </c>
-      <c r="F72" s="5" t="s">
+      <c r="F72" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="G72" s="2" t="s">
+      <c r="G72" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H72" s="11"/>
+      <c r="H72" s="2"/>
     </row>
     <row r="73" spans="3:8">
-      <c r="C73" s="3">
+      <c r="C73" s="4">
         <v>68</v>
       </c>
-      <c r="D73" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E73" s="5">
+      <c r="D73" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E73" s="6">
         <v>64</v>
       </c>
-      <c r="F73" s="5" t="s">
+      <c r="F73" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="G73" s="2" t="s">
+      <c r="G73" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="H73" s="11"/>
+      <c r="H73" s="2"/>
     </row>
     <row r="74" spans="3:8">
-      <c r="C74" s="3">
+      <c r="C74" s="4">
         <v>69</v>
       </c>
-      <c r="D74" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E74" s="5">
+      <c r="D74" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E74" s="6">
         <v>64</v>
       </c>
-      <c r="F74" s="5" t="s">
+      <c r="F74" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="G74" s="2" t="s">
+      <c r="G74" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="H74" s="11"/>
+      <c r="H74" s="2"/>
     </row>
     <row r="75" spans="3:8">
-      <c r="C75" s="3">
+      <c r="C75" s="4">
         <v>70</v>
       </c>
-      <c r="D75" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E75" s="5">
+      <c r="D75" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E75" s="6">
         <v>64</v>
       </c>
-      <c r="F75" s="5" t="s">
+      <c r="F75" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="G75" s="2" t="s">
+      <c r="G75" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H75" s="11"/>
+      <c r="H75" s="2"/>
     </row>
     <row r="76" spans="3:8">
-      <c r="C76" s="3">
+      <c r="C76" s="4">
         <v>71</v>
       </c>
-      <c r="D76" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E76" s="5">
+      <c r="D76" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E76" s="6">
         <v>64</v>
       </c>
-      <c r="F76" s="5" t="s">
+      <c r="F76" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="G76" s="2" t="s">
+      <c r="G76" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="H76" s="11"/>
+      <c r="H76" s="2"/>
     </row>
     <row r="77" spans="3:8">
-      <c r="C77" s="3">
+      <c r="C77" s="4">
         <v>72</v>
       </c>
-      <c r="D77" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E77" s="5">
+      <c r="D77" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E77" s="6">
         <v>64</v>
       </c>
-      <c r="F77" s="5" t="s">
+      <c r="F77" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="G77" s="2" t="s">
+      <c r="G77" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="H77" s="11"/>
+      <c r="H77" s="2"/>
     </row>
     <row r="78" spans="3:8">
-      <c r="C78" s="3">
+      <c r="C78" s="4">
         <v>73</v>
       </c>
-      <c r="D78" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E78" s="5">
+      <c r="D78" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E78" s="6">
         <v>64</v>
       </c>
-      <c r="F78" s="5" t="s">
+      <c r="F78" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="G78" s="2" t="s">
+      <c r="G78" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="H78" s="11"/>
+      <c r="H78" s="2"/>
     </row>
     <row r="79" spans="3:8">
-      <c r="C79" s="3">
+      <c r="C79" s="4">
         <v>74</v>
       </c>
-      <c r="D79" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E79" s="5">
+      <c r="D79" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E79" s="6">
         <v>64</v>
       </c>
-      <c r="F79" s="5" t="s">
+      <c r="F79" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="G79" s="2" t="s">
+      <c r="G79" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="H79" s="11"/>
+      <c r="H79" s="2"/>
     </row>
     <row r="80" spans="3:8">
-      <c r="C80" s="3">
+      <c r="C80" s="4">
         <v>75</v>
       </c>
-      <c r="D80" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E80" s="5">
+      <c r="D80" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E80" s="6">
         <v>64</v>
       </c>
-      <c r="F80" s="5" t="s">
+      <c r="F80" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="G80" s="2" t="s">
+      <c r="G80" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="H80" s="11"/>
+      <c r="H80" s="2"/>
     </row>
     <row r="81" spans="3:9">
-      <c r="C81" s="3">
+      <c r="C81" s="4">
         <v>76</v>
       </c>
-      <c r="D81" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E81" s="5">
+      <c r="D81" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E81" s="6">
         <v>64</v>
       </c>
-      <c r="F81" s="5" t="s">
+      <c r="F81" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="G81" s="2" t="s">
+      <c r="G81" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="H81" s="11"/>
+      <c r="H81" s="2"/>
     </row>
     <row r="82" spans="3:9">
-      <c r="C82" s="3">
+      <c r="C82" s="4">
         <v>77</v>
       </c>
-      <c r="D82" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E82" s="5">
+      <c r="D82" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E82" s="6">
         <v>64</v>
       </c>
-      <c r="F82" s="5" t="s">
+      <c r="F82" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="G82" s="2" t="s">
+      <c r="G82" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H82" s="11"/>
+      <c r="H82" s="2"/>
     </row>
     <row r="83" spans="3:9">
-      <c r="C83" s="3">
+      <c r="C83" s="4">
         <v>78</v>
       </c>
-      <c r="D83" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E83" s="5">
+      <c r="D83" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E83" s="6">
         <v>64</v>
       </c>
-      <c r="F83" s="5" t="s">
+      <c r="F83" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="G83" s="2" t="s">
+      <c r="G83" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H83" s="11"/>
+      <c r="H83" s="2"/>
     </row>
     <row r="84" spans="3:9">
-      <c r="C84" s="3">
+      <c r="C84" s="4">
         <v>79</v>
       </c>
-      <c r="D84" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E84" s="5">
+      <c r="D84" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E84" s="6">
         <v>64</v>
       </c>
-      <c r="F84" s="5" t="s">
+      <c r="F84" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G84" s="2" t="s">
+      <c r="G84" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="H84" s="11"/>
+      <c r="H84" s="2"/>
     </row>
     <row r="85" spans="3:9">
-      <c r="C85" s="3">
+      <c r="C85" s="4">
         <v>80</v>
       </c>
-      <c r="D85" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E85" s="5">
+      <c r="D85" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E85" s="6">
         <v>80</v>
       </c>
-      <c r="F85" s="5" t="s">
+      <c r="F85" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="G85" s="2" t="s">
+      <c r="G85" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="H85" s="6"/>
+      <c r="H85" s="7"/>
     </row>
     <row r="86" spans="3:9">
-      <c r="C86" s="3">
+      <c r="C86" s="4">
         <v>81</v>
       </c>
-      <c r="D86" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E86" s="5">
+      <c r="D86" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E86" s="6">
         <v>80</v>
       </c>
-      <c r="F86" s="5" t="s">
+      <c r="F86" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="G86" s="2" t="s">
+      <c r="G86" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="H86" s="6"/>
+      <c r="H86" s="7"/>
     </row>
     <row r="87" spans="3:9">
-      <c r="C87" s="3">
+      <c r="C87" s="4">
         <v>82</v>
       </c>
-      <c r="D87" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E87" s="5">
+      <c r="D87" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E87" s="6">
         <v>80</v>
       </c>
-      <c r="F87" s="5" t="s">
+      <c r="F87" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="G87" s="2" t="s">
+      <c r="G87" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="H87" s="6"/>
+      <c r="H87" s="7"/>
     </row>
     <row r="88" spans="3:9">
-      <c r="C88" s="3">
+      <c r="C88" s="4">
         <v>83</v>
       </c>
-      <c r="D88" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E88" s="5">
+      <c r="D88" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E88" s="6">
         <v>80</v>
       </c>
-      <c r="F88" s="5" t="s">
+      <c r="F88" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G88" s="2" t="s">
+      <c r="G88" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="H88" s="6"/>
+      <c r="H88" s="7"/>
     </row>
     <row r="89" spans="3:9">
-      <c r="C89" s="3">
+      <c r="C89" s="4">
         <v>84</v>
       </c>
-      <c r="D89" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E89" s="5">
+      <c r="D89" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89" s="6">
         <v>84</v>
       </c>
-      <c r="F89" s="5" t="s">
+      <c r="F89" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G89" s="2" t="s">
+      <c r="G89" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="I89" s="6"/>
+      <c r="I89" s="7"/>
     </row>
     <row r="90" spans="3:9">
-      <c r="C90" s="3">
+      <c r="C90" s="4">
         <v>85</v>
       </c>
-      <c r="D90" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E90" s="5">
+      <c r="D90" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E90" s="6">
         <v>80</v>
       </c>
-      <c r="F90" s="5" t="s">
+      <c r="F90" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="G90" s="2" t="s">
+      <c r="G90" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="H90" s="6"/>
+      <c r="H90" s="7"/>
     </row>
     <row r="91" spans="3:9">
-      <c r="C91" s="3">
+      <c r="C91" s="4">
         <v>86</v>
       </c>
-      <c r="D91" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E91" s="5">
+      <c r="D91" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E91" s="6">
         <v>80</v>
       </c>
-      <c r="F91" s="5" t="s">
+      <c r="F91" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="G91" s="2" t="s">
+      <c r="G91" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="H91" s="6"/>
+      <c r="H91" s="7"/>
     </row>
     <row r="92" spans="3:9">
-      <c r="C92" s="3">
+      <c r="C92" s="4">
         <v>87</v>
       </c>
-      <c r="D92" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E92" s="5">
+      <c r="D92" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E92" s="6">
         <v>80</v>
       </c>
-      <c r="F92" s="5" t="s">
+      <c r="F92" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="G92" s="2" t="s">
+      <c r="G92" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="H92" s="6"/>
+      <c r="H92" s="7"/>
     </row>
     <row r="93" spans="3:9">
-      <c r="C93" s="3">
+      <c r="C93" s="4">
         <v>88</v>
       </c>
-      <c r="D93" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E93" s="5">
+      <c r="D93" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E93" s="6">
         <v>80</v>
       </c>
-      <c r="F93" s="5" t="s">
+      <c r="F93" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="G93" s="2" t="s">
+      <c r="G93" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="H93" s="6"/>
+      <c r="H93" s="7"/>
     </row>
     <row r="94" spans="3:9">
-      <c r="C94" s="3">
+      <c r="C94" s="4">
         <v>89</v>
       </c>
-      <c r="D94" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E94" s="5">
+      <c r="D94" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E94" s="6">
         <v>89</v>
       </c>
-      <c r="F94" s="5" t="s">
+      <c r="F94" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="G94" s="2" t="s">
+      <c r="G94" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="H94" s="10"/>
+      <c r="H94" s="11"/>
     </row>
     <row r="95" spans="3:9">
-      <c r="C95" s="3">
+      <c r="C95" s="4">
         <v>90</v>
       </c>
-      <c r="D95" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E95" s="5">
+      <c r="D95" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95" s="6">
         <v>89</v>
       </c>
-      <c r="F95" s="5" t="s">
+      <c r="F95" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="G95" s="2" t="s">
+      <c r="G95" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="H95" s="10"/>
+      <c r="H95" s="11"/>
     </row>
     <row r="96" spans="3:9">
-      <c r="C96" s="3">
+      <c r="C96" s="4">
         <v>91</v>
       </c>
-      <c r="D96" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E96" s="5">
+      <c r="D96" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E96" s="6">
         <v>89</v>
       </c>
-      <c r="F96" s="5" t="s">
+      <c r="F96" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="G96" s="2" t="s">
+      <c r="G96" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="H96" s="10"/>
+      <c r="H96" s="11"/>
     </row>
     <row r="97" spans="3:8">
-      <c r="C97" s="3">
+      <c r="C97" s="4">
         <v>92</v>
       </c>
-      <c r="D97" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E97" s="5">
+      <c r="D97" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E97" s="6">
         <v>89</v>
       </c>
-      <c r="F97" s="5" t="s">
+      <c r="F97" s="6" t="s">
         <v>185</v>
       </c>
       <c r="G97" t="s">
         <v>186</v>
       </c>
-      <c r="H97" s="10"/>
+      <c r="H97" s="11"/>
     </row>
     <row r="98" spans="3:8">
-      <c r="C98" s="3">
+      <c r="C98" s="4">
         <v>93</v>
       </c>
-      <c r="D98" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E98" s="5">
+      <c r="D98" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E98" s="6">
         <v>89</v>
       </c>
-      <c r="F98" s="5" t="s">
+      <c r="F98" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="G98" s="2" t="s">
+      <c r="G98" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="H98" s="10"/>
+      <c r="H98" s="11"/>
     </row>
     <row r="99" spans="3:8">
-      <c r="C99" s="3">
+      <c r="C99" s="4">
         <v>94</v>
       </c>
-      <c r="D99" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E99" s="5">
+      <c r="D99" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E99" s="6">
         <v>89</v>
       </c>
-      <c r="F99" s="5" t="s">
+      <c r="F99" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="G99" s="2" t="s">
+      <c r="G99" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="H99" s="10"/>
+      <c r="H99" s="11"/>
     </row>
     <row r="100" spans="3:8">
-      <c r="C100" s="3">
+      <c r="C100" s="4">
         <v>95</v>
       </c>
-      <c r="D100" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E100" s="5">
+      <c r="D100" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E100" s="6">
         <v>89</v>
       </c>
-      <c r="F100" s="5" t="s">
+      <c r="F100" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="G100" s="2" t="s">
+      <c r="G100" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H100" s="10"/>
+      <c r="H100" s="11"/>
     </row>
     <row r="101" spans="3:8">
-      <c r="C101" s="3">
+      <c r="C101" s="4">
         <v>96</v>
       </c>
-      <c r="D101" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E101" s="5">
+      <c r="D101" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E101" s="6">
         <v>89</v>
       </c>
-      <c r="F101" s="5" t="s">
+      <c r="F101" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="G101" s="2" t="s">
+      <c r="G101" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="H101" s="10"/>
+      <c r="H101" s="11"/>
     </row>
     <row r="102" spans="3:8">
-      <c r="C102" s="3">
+      <c r="C102" s="4">
         <v>97</v>
       </c>
-      <c r="D102" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E102" s="5">
+      <c r="D102" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E102" s="6">
         <v>89</v>
       </c>
-      <c r="F102" s="5" t="s">
+      <c r="F102" s="6" t="s">
         <v>195</v>
       </c>
       <c r="G102" t="s">
         <v>196</v>
       </c>
-      <c r="H102" s="10"/>
+      <c r="H102" s="11"/>
     </row>
     <row r="103" spans="3:8">
-      <c r="C103" s="3">
+      <c r="C103" s="4">
         <v>98</v>
       </c>
-      <c r="D103" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E103" s="5">
+      <c r="D103" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E103" s="6">
         <v>89</v>
       </c>
-      <c r="F103" s="5" t="s">
+      <c r="F103" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="G103" s="2" t="s">
+      <c r="G103" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="H103" s="10"/>
+      <c r="H103" s="11"/>
     </row>
     <row r="104" spans="3:8">
-      <c r="C104" s="3">
+      <c r="C104" s="4">
         <v>99</v>
       </c>
-      <c r="D104" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E104" s="5">
+      <c r="D104" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E104" s="6">
         <v>89</v>
       </c>
-      <c r="F104" s="5" t="s">
+      <c r="F104" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="G104" s="2" t="s">
+      <c r="G104" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="H104" s="10"/>
+      <c r="H104" s="11"/>
     </row>
     <row r="105" spans="3:8">
-      <c r="C105" s="3">
+      <c r="C105" s="4">
         <v>100</v>
       </c>
-      <c r="D105" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E105" s="5">
+      <c r="D105" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E105" s="6">
         <v>89</v>
       </c>
-      <c r="F105" s="5" t="s">
+      <c r="F105" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="G105" s="2" t="s">
+      <c r="G105" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="H105" s="10"/>
+      <c r="H105" s="11"/>
     </row>
     <row r="106" spans="3:8">
-      <c r="C106" s="3">
+      <c r="C106" s="4">
         <v>101</v>
       </c>
-      <c r="D106" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E106" s="5">
+      <c r="D106" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E106" s="6">
         <v>89</v>
       </c>
-      <c r="F106" s="5" t="s">
+      <c r="F106" s="6" t="s">
         <v>203</v>
       </c>
       <c r="G106" t="s">
         <v>204</v>
       </c>
-      <c r="H106" s="10"/>
+      <c r="H106" s="11"/>
     </row>
     <row r="107" spans="3:8">
-      <c r="C107" s="3">
+      <c r="C107" s="4">
         <v>102</v>
       </c>
-      <c r="D107" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E107" s="5">
+      <c r="D107" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E107" s="6">
         <v>89</v>
       </c>
-      <c r="F107" s="5" t="s">
+      <c r="F107" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="G107" s="2" t="s">
+      <c r="G107" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="H107" s="10"/>
+      <c r="H107" s="11"/>
     </row>
     <row r="108" spans="3:8">
-      <c r="C108" s="3">
+      <c r="C108" s="4">
         <v>103</v>
       </c>
-      <c r="D108" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E108" s="5">
+      <c r="D108" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E108" s="6">
         <v>89</v>
       </c>
-      <c r="F108" s="5" t="s">
+      <c r="F108" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="G108" s="2" t="s">
+      <c r="G108" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="H108" s="10"/>
+      <c r="H108" s="11"/>
     </row>
     <row r="109" spans="3:8">
-      <c r="C109" s="3">
+      <c r="C109" s="4">
         <v>104</v>
       </c>
-      <c r="D109" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E109" s="5">
+      <c r="D109" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E109" s="6">
         <v>89</v>
       </c>
-      <c r="F109" s="5" t="s">
+      <c r="F109" s="6" t="s">
         <v>209</v>
       </c>
       <c r="G109" t="s">
         <v>210</v>
       </c>
-      <c r="H109" s="10"/>
+      <c r="H109" s="11"/>
     </row>
     <row r="110" spans="3:8">
-      <c r="C110" s="3">
+      <c r="C110" s="4">
         <v>105</v>
       </c>
-      <c r="D110" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E110" s="5">
+      <c r="D110" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E110" s="6">
         <v>105</v>
       </c>
-      <c r="F110" s="5" t="s">
+      <c r="F110" s="6" t="s">
         <v>211</v>
       </c>
       <c r="G110" t="s">
         <v>212</v>
       </c>
-      <c r="H110" s="11"/>
+      <c r="H110" s="2"/>
     </row>
     <row r="111" spans="3:8">
-      <c r="C111" s="3">
+      <c r="C111" s="4">
         <v>106</v>
       </c>
-      <c r="D111" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E111" s="5">
+      <c r="D111" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E111" s="6">
         <v>105</v>
       </c>
-      <c r="F111" s="5" t="s">
+      <c r="F111" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="G111" s="2" t="s">
+      <c r="G111" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="H111" s="11"/>
+      <c r="H111" s="2"/>
     </row>
     <row r="112" spans="3:8">
-      <c r="C112" s="3">
+      <c r="C112" s="4">
         <v>107</v>
       </c>
-      <c r="D112" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E112" s="5">
+      <c r="D112" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E112" s="6">
         <v>105</v>
       </c>
-      <c r="F112" s="5" t="s">
+      <c r="F112" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="G112" s="2" t="s">
+      <c r="G112" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="H112" s="11"/>
+      <c r="H112" s="2"/>
     </row>
     <row r="113" spans="3:8">
-      <c r="C113" s="3">
+      <c r="C113" s="4">
         <v>108</v>
       </c>
-      <c r="D113" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E113" s="5">
+      <c r="D113" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E113" s="6">
         <v>105</v>
       </c>
-      <c r="F113" s="5" t="s">
+      <c r="F113" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="G113" s="2" t="s">
+      <c r="G113" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="H113" s="11"/>
+      <c r="H113" s="2"/>
     </row>
     <row r="114" spans="3:8">
-      <c r="C114" s="3">
+      <c r="C114" s="4">
         <v>109</v>
       </c>
-      <c r="D114" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E114" s="5">
+      <c r="D114" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E114" s="6">
         <v>105</v>
       </c>
-      <c r="F114" s="5" t="s">
+      <c r="F114" s="6" t="s">
         <v>219</v>
       </c>
       <c r="G114" t="s">
         <v>220</v>
       </c>
-      <c r="H114" s="11"/>
+      <c r="H114" s="2"/>
     </row>
     <row r="115" spans="3:8">
-      <c r="C115" s="3">
+      <c r="C115" s="4">
         <v>110</v>
       </c>
-      <c r="D115" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E115" s="5">
+      <c r="D115" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E115" s="6">
         <v>105</v>
       </c>
-      <c r="F115" s="5" t="s">
+      <c r="F115" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="G115" s="2" t="s">
+      <c r="G115" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="H115" s="11"/>
+      <c r="H115" s="2"/>
     </row>
     <row r="116" spans="3:8">
-      <c r="C116" s="3">
+      <c r="C116" s="4">
         <v>111</v>
       </c>
-      <c r="D116" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E116" s="5">
+      <c r="D116" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E116" s="6">
         <v>105</v>
       </c>
-      <c r="F116" s="5" t="s">
+      <c r="F116" s="6" t="s">
         <v>223</v>
       </c>
       <c r="G116" t="s">
         <v>224</v>
       </c>
-      <c r="H116" s="11"/>
+      <c r="H116" s="2"/>
     </row>
     <row r="117" spans="3:8">
-      <c r="C117" s="3">
+      <c r="C117" s="4">
         <v>112</v>
       </c>
-      <c r="D117" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E117" s="5">
+      <c r="D117" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E117" s="6">
         <v>105</v>
       </c>
-      <c r="F117" s="5" t="s">
+      <c r="F117" s="6" t="s">
         <v>225</v>
       </c>
       <c r="G117" t="s">
         <v>226</v>
       </c>
-      <c r="H117" s="11"/>
+      <c r="H117" s="2"/>
     </row>
     <row r="118" spans="3:8">
-      <c r="C118" s="3">
+      <c r="C118" s="4">
         <v>113</v>
       </c>
-      <c r="D118" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E118" s="5">
+      <c r="D118" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E118" s="6">
         <v>105</v>
       </c>
-      <c r="F118" s="5" t="s">
+      <c r="F118" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="G118" s="2" t="s">
+      <c r="G118" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="H118" s="11"/>
+      <c r="H118" s="2"/>
     </row>
     <row r="119" spans="3:8">
-      <c r="C119" s="3">
+      <c r="C119" s="4">
         <v>114</v>
       </c>
-      <c r="D119" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E119" s="5">
+      <c r="D119" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E119" s="6">
         <v>105</v>
       </c>
-      <c r="F119" s="5" t="s">
+      <c r="F119" s="6" t="s">
         <v>229</v>
       </c>
       <c r="G119" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="H119" s="11"/>
+      <c r="H119" s="2"/>
     </row>
     <row r="120" spans="3:8">
-      <c r="C120" s="3">
+      <c r="C120" s="4">
         <v>115</v>
       </c>
-      <c r="D120" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E120" s="5">
+      <c r="D120" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E120" s="6">
         <v>105</v>
       </c>
-      <c r="F120" s="5" t="s">
+      <c r="F120" s="6" t="s">
         <v>231</v>
       </c>
       <c r="G120" t="s">
         <v>232</v>
       </c>
-      <c r="H120" s="11"/>
+      <c r="H120" s="2"/>
     </row>
     <row r="121" spans="3:8">
-      <c r="C121" s="3">
+      <c r="C121" s="4">
         <v>116</v>
       </c>
-      <c r="D121" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E121" s="5">
+      <c r="D121" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E121" s="6">
         <v>105</v>
       </c>
-      <c r="F121" s="5" t="s">
+      <c r="F121" s="6" t="s">
         <v>233</v>
       </c>
       <c r="G121" t="s">
         <v>234</v>
       </c>
-      <c r="H121" s="11"/>
+      <c r="H121" s="2"/>
     </row>
     <row r="122" spans="3:8">
-      <c r="C122" s="3">
+      <c r="C122" s="4">
         <v>117</v>
       </c>
-      <c r="D122" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E122" s="5">
+      <c r="D122" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E122" s="6">
         <v>105</v>
       </c>
-      <c r="F122" s="5" t="s">
+      <c r="F122" s="6" t="s">
         <v>235</v>
       </c>
       <c r="G122" t="s">
         <v>236</v>
       </c>
-      <c r="H122" s="11"/>
+      <c r="H122" s="2"/>
     </row>
     <row r="123" spans="3:8">
-      <c r="C123" s="3">
+      <c r="C123" s="4">
         <v>118</v>
       </c>
-      <c r="D123" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E123" s="5">
+      <c r="D123" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E123" s="6">
         <v>105</v>
       </c>
-      <c r="F123" s="5" t="s">
+      <c r="F123" s="6" t="s">
         <v>237</v>
       </c>
       <c r="G123" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="H123" s="11"/>
+      <c r="H123" s="2"/>
     </row>
     <row r="124" spans="3:8">
-      <c r="C124" s="3">
+      <c r="C124" s="4">
         <v>119</v>
       </c>
-      <c r="D124" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E124" s="5">
+      <c r="D124" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E124" s="6">
         <v>105</v>
       </c>
-      <c r="F124" s="5" t="s">
+      <c r="F124" s="6" t="s">
         <v>239</v>
       </c>
       <c r="G124" t="s">
         <v>240</v>
       </c>
-      <c r="H124" s="11"/>
+      <c r="H124" s="2"/>
     </row>
     <row r="125" spans="3:8">
-      <c r="C125" s="3">
+      <c r="C125" s="4">
         <v>120</v>
       </c>
-      <c r="D125" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E125" s="5">
+      <c r="D125" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E125" s="6">
         <v>105</v>
       </c>
-      <c r="F125" s="5" t="s">
+      <c r="F125" s="6" t="s">
         <v>241</v>
       </c>
       <c r="G125" t="s">
         <v>242</v>
       </c>
-      <c r="H125" s="11"/>
+      <c r="H125" s="2"/>
     </row>
     <row r="126" spans="3:8">
-      <c r="C126" s="3">
+      <c r="C126" s="4">
         <v>121</v>
       </c>
-      <c r="D126" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E126" s="5">
+      <c r="D126" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E126" s="6">
         <v>121</v>
       </c>
-      <c r="F126" s="5" t="s">
+      <c r="F126" s="6" t="s">
         <v>243</v>
       </c>
       <c r="G126" t="s">
         <v>244</v>
       </c>
-      <c r="H126" s="10"/>
+      <c r="H126" s="11"/>
     </row>
     <row r="127" spans="3:8">
-      <c r="C127" s="3">
+      <c r="C127" s="4">
         <v>122</v>
       </c>
-      <c r="D127" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E127" s="5">
+      <c r="D127" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E127" s="6">
         <v>121</v>
       </c>
-      <c r="F127" s="5" t="s">
+      <c r="F127" s="6" t="s">
         <v>245</v>
       </c>
       <c r="G127" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="H127" s="10"/>
+      <c r="H127" s="11"/>
     </row>
     <row r="128" spans="3:8">
-      <c r="C128" s="3">
+      <c r="C128" s="4">
         <v>123</v>
       </c>
-      <c r="D128" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E128" s="5">
+      <c r="D128" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E128" s="6">
         <v>121</v>
       </c>
-      <c r="F128" s="5" t="s">
+      <c r="F128" s="6" t="s">
         <v>246</v>
       </c>
       <c r="G128" t="s">
         <v>247</v>
       </c>
-      <c r="H128" s="10"/>
+      <c r="H128" s="11"/>
     </row>
     <row r="129" spans="3:9">
-      <c r="C129" s="3">
+      <c r="C129" s="4">
         <v>124</v>
       </c>
-      <c r="D129" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E129" s="5">
+      <c r="D129" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E129" s="6">
         <v>121</v>
       </c>
-      <c r="F129" s="5" t="s">
+      <c r="F129" s="6" t="s">
         <v>248</v>
       </c>
       <c r="G129" t="s">
         <v>249</v>
       </c>
-      <c r="H129" s="10"/>
+      <c r="H129" s="11"/>
     </row>
     <row r="130" spans="3:9">
-      <c r="C130" s="3">
+      <c r="C130" s="4">
         <v>125</v>
       </c>
-      <c r="D130" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E130" s="5">
+      <c r="D130" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E130" s="6">
         <v>121</v>
       </c>
-      <c r="F130" s="5" t="s">
+      <c r="F130" s="6" t="s">
         <v>250</v>
       </c>
       <c r="G130" t="s">
@@ -4639,16 +4648,16 @@
       <c r="H130" s="13"/>
     </row>
     <row r="131" spans="3:9">
-      <c r="C131" s="3">
+      <c r="C131" s="4">
         <v>126</v>
       </c>
-      <c r="D131" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E131" s="5">
+      <c r="D131" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E131" s="6">
         <v>121</v>
       </c>
-      <c r="F131" s="5" t="s">
+      <c r="F131" s="6" t="s">
         <v>252</v>
       </c>
       <c r="G131" t="s">
@@ -4657,16 +4666,16 @@
       <c r="H131" s="13"/>
     </row>
     <row r="132" spans="3:9">
-      <c r="C132" s="3">
+      <c r="C132" s="4">
         <v>127</v>
       </c>
-      <c r="D132" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E132" s="5">
+      <c r="D132" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E132" s="6">
         <v>121</v>
       </c>
-      <c r="F132" s="5" t="s">
+      <c r="F132" s="6" t="s">
         <v>254</v>
       </c>
       <c r="G132" t="s">
@@ -4675,34 +4684,34 @@
       <c r="H132" s="13"/>
     </row>
     <row r="133" spans="3:9">
-      <c r="C133" s="3">
+      <c r="C133" s="4">
         <v>128</v>
       </c>
-      <c r="D133" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E133" s="5">
+      <c r="D133" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E133" s="6">
         <v>128</v>
       </c>
-      <c r="F133" s="5" t="s">
+      <c r="F133" s="6" t="s">
         <v>256</v>
       </c>
       <c r="G133" t="s">
         <v>257</v>
       </c>
-      <c r="I133" s="11"/>
+      <c r="I133" s="2"/>
     </row>
     <row r="134" spans="3:9">
-      <c r="C134" s="3">
+      <c r="C134" s="4">
         <v>129</v>
       </c>
-      <c r="D134" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E134" s="5">
+      <c r="D134" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E134" s="6">
         <v>121</v>
       </c>
-      <c r="F134" s="5" t="s">
+      <c r="F134" s="6" t="s">
         <v>258</v>
       </c>
       <c r="G134" s="12" t="s">
@@ -4711,16 +4720,16 @@
       <c r="H134" s="13"/>
     </row>
     <row r="135" spans="3:9">
-      <c r="C135" s="3">
+      <c r="C135" s="4">
         <v>130</v>
       </c>
-      <c r="D135" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E135" s="5">
+      <c r="D135" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E135" s="6">
         <v>121</v>
       </c>
-      <c r="F135" s="5" t="s">
+      <c r="F135" s="6" t="s">
         <v>260</v>
       </c>
       <c r="G135" t="s">
@@ -4729,160 +4738,160 @@
       <c r="H135" s="13"/>
     </row>
     <row r="136" spans="3:9">
-      <c r="C136" s="3">
+      <c r="C136" s="4">
         <v>131</v>
       </c>
-      <c r="D136" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E136" s="5">
+      <c r="D136" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E136" s="6">
         <v>121</v>
       </c>
-      <c r="F136" s="5" t="s">
+      <c r="F136" s="6" t="s">
         <v>262</v>
       </c>
       <c r="G136" t="s">
         <v>263</v>
       </c>
-      <c r="H136" s="10"/>
+      <c r="H136" s="11"/>
     </row>
     <row r="137" spans="3:9">
-      <c r="C137" s="3">
+      <c r="C137" s="4">
         <v>132</v>
       </c>
-      <c r="D137" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E137" s="5">
+      <c r="D137" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E137" s="6">
         <v>121</v>
       </c>
-      <c r="F137" s="5" t="s">
+      <c r="F137" s="6" t="s">
         <v>264</v>
       </c>
       <c r="G137" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="H137" s="10"/>
+      <c r="H137" s="11"/>
     </row>
     <row r="138" spans="3:9">
-      <c r="C138" s="3">
+      <c r="C138" s="4">
         <v>133</v>
       </c>
-      <c r="D138" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E138" s="5">
+      <c r="D138" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E138" s="6">
         <v>121</v>
       </c>
-      <c r="F138" s="5" t="s">
+      <c r="F138" s="6" t="s">
         <v>266</v>
       </c>
       <c r="G138" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="H138" s="10"/>
+      <c r="H138" s="11"/>
     </row>
     <row r="139" spans="3:9">
-      <c r="C139" s="3">
+      <c r="C139" s="4">
         <v>134</v>
       </c>
-      <c r="D139" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E139" s="5">
+      <c r="D139" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E139" s="6">
         <v>121</v>
       </c>
-      <c r="F139" s="5" t="s">
+      <c r="F139" s="6" t="s">
         <v>268</v>
       </c>
       <c r="G139" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="H139" s="10"/>
+      <c r="H139" s="11"/>
     </row>
     <row r="140" spans="3:9">
-      <c r="C140" s="3">
+      <c r="C140" s="4">
         <v>135</v>
       </c>
-      <c r="D140" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E140" s="5">
+      <c r="D140" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E140" s="6">
         <v>121</v>
       </c>
-      <c r="F140" s="5" t="s">
+      <c r="F140" s="6" t="s">
         <v>270</v>
       </c>
       <c r="G140" t="s">
         <v>271</v>
       </c>
-      <c r="H140" s="10"/>
+      <c r="H140" s="11"/>
     </row>
     <row r="141" spans="3:9">
-      <c r="C141" s="3">
+      <c r="C141" s="4">
         <v>136</v>
       </c>
-      <c r="D141" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E141" s="5">
+      <c r="D141" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E141" s="6">
         <v>121</v>
       </c>
-      <c r="F141" s="5" t="s">
+      <c r="F141" s="6" t="s">
         <v>272</v>
       </c>
       <c r="G141" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="H141" s="10"/>
+      <c r="H141" s="11"/>
     </row>
     <row r="142" spans="3:9">
-      <c r="C142" s="3">
+      <c r="C142" s="4">
         <v>137</v>
       </c>
-      <c r="D142" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E142" s="5">
+      <c r="D142" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E142" s="6">
         <v>121</v>
       </c>
-      <c r="F142" s="5" t="s">
+      <c r="F142" s="6" t="s">
         <v>274</v>
       </c>
       <c r="G142" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="H142" s="10"/>
+      <c r="H142" s="11"/>
     </row>
     <row r="143" spans="3:9">
-      <c r="C143" s="3">
+      <c r="C143" s="4">
         <v>138</v>
       </c>
-      <c r="D143" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E143" s="5">
+      <c r="D143" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E143" s="6">
         <v>121</v>
       </c>
-      <c r="F143" s="5" t="s">
+      <c r="F143" s="6" t="s">
         <v>276</v>
       </c>
       <c r="G143" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="H143" s="10"/>
+      <c r="H143" s="11"/>
     </row>
     <row r="144" spans="3:9">
-      <c r="C144" s="3">
+      <c r="C144" s="4">
         <v>139</v>
       </c>
-      <c r="D144" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E144" s="5">
+      <c r="D144" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E144" s="6">
         <v>139</v>
       </c>
-      <c r="F144" s="5" t="s">
+      <c r="F144" s="6" t="s">
         <v>278</v>
       </c>
       <c r="G144" s="12" t="s">
@@ -4891,16 +4900,16 @@
       <c r="H144" s="14"/>
     </row>
     <row r="145" spans="3:8">
-      <c r="C145" s="3">
+      <c r="C145" s="4">
         <v>140</v>
       </c>
-      <c r="D145" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E145" s="5">
+      <c r="D145" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E145" s="6">
         <v>139</v>
       </c>
-      <c r="F145" s="5" t="s">
+      <c r="F145" s="6" t="s">
         <v>280</v>
       </c>
       <c r="G145" s="12" t="s">
@@ -4909,16 +4918,16 @@
       <c r="H145" s="14"/>
     </row>
     <row r="146" spans="3:8">
-      <c r="C146" s="3">
+      <c r="C146" s="4">
         <v>141</v>
       </c>
-      <c r="D146" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E146" s="5">
+      <c r="D146" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E146" s="6">
         <v>139</v>
       </c>
-      <c r="F146" s="5" t="s">
+      <c r="F146" s="6" t="s">
         <v>281</v>
       </c>
       <c r="G146" s="12" t="s">
@@ -4927,16 +4936,16 @@
       <c r="H146" s="14"/>
     </row>
     <row r="147" spans="3:8">
-      <c r="C147" s="3">
+      <c r="C147" s="4">
         <v>142</v>
       </c>
-      <c r="D147" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E147" s="5">
+      <c r="D147" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E147" s="6">
         <v>139</v>
       </c>
-      <c r="F147" s="5" t="s">
+      <c r="F147" s="6" t="s">
         <v>282</v>
       </c>
       <c r="G147" s="12" t="s">
@@ -4945,1072 +4954,1075 @@
       <c r="H147" s="14"/>
     </row>
     <row r="148" spans="3:8">
-      <c r="C148" s="3">
+      <c r="C148" s="4">
         <v>143</v>
       </c>
-      <c r="D148" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E148" s="5">
+      <c r="D148" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E148" s="6">
         <v>139</v>
       </c>
-      <c r="F148" s="5" t="s">
+      <c r="F148" s="6" t="s">
         <v>283</v>
       </c>
       <c r="G148" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="H148" s="11"/>
+      <c r="H148" s="2"/>
     </row>
     <row r="149" spans="3:8">
-      <c r="C149" s="3">
+      <c r="C149" s="4">
         <v>144</v>
       </c>
-      <c r="D149" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E149" s="5">
+      <c r="D149" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E149" s="6">
         <v>139</v>
       </c>
-      <c r="F149" s="5" t="s">
+      <c r="F149" s="6" t="s">
         <v>285</v>
       </c>
       <c r="G149" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="H149" s="11"/>
+      <c r="H149" s="2"/>
     </row>
     <row r="150" spans="3:8">
-      <c r="C150" s="3">
+      <c r="C150" s="4">
         <v>145</v>
       </c>
-      <c r="D150" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E150" s="5">
+      <c r="D150" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E150" s="6">
         <v>139</v>
       </c>
-      <c r="F150" s="5" t="s">
+      <c r="F150" s="6" t="s">
         <v>287</v>
       </c>
       <c r="G150" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="H150" s="11"/>
+      <c r="H150" s="2"/>
     </row>
     <row r="151" spans="3:8">
-      <c r="C151" s="3">
+      <c r="C151" s="4">
         <v>146</v>
       </c>
-      <c r="D151" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E151" s="5">
+      <c r="D151" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E151" s="6">
         <v>139</v>
       </c>
-      <c r="F151" s="5" t="s">
+      <c r="F151" s="6" t="s">
         <v>289</v>
       </c>
       <c r="G151" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="H151" s="11"/>
+      <c r="H151" s="2"/>
     </row>
     <row r="152" spans="3:8">
-      <c r="C152" s="3">
+      <c r="C152" s="4">
         <v>147</v>
       </c>
-      <c r="D152" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E152" s="5">
+      <c r="D152" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E152" s="6">
         <v>139</v>
       </c>
-      <c r="F152" s="5" t="s">
+      <c r="F152" s="6" t="s">
         <v>291</v>
       </c>
       <c r="G152" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="H152" s="11"/>
+      <c r="H152" s="2"/>
     </row>
     <row r="153" spans="3:8">
-      <c r="C153" s="3">
+      <c r="C153" s="4">
         <v>148</v>
       </c>
-      <c r="D153" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E153" s="5">
+      <c r="D153" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E153" s="6">
         <v>139</v>
       </c>
-      <c r="F153" s="5" t="s">
+      <c r="F153" s="6" t="s">
         <v>292</v>
       </c>
       <c r="G153" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="H153" s="11"/>
+      <c r="H153" s="2"/>
     </row>
     <row r="154" spans="3:8">
-      <c r="C154" s="3">
+      <c r="C154" s="4">
         <v>149</v>
       </c>
-      <c r="D154" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E154" s="5">
+      <c r="D154" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E154" s="6">
         <v>139</v>
       </c>
-      <c r="F154" s="5" t="s">
+      <c r="F154" s="6" t="s">
         <v>294</v>
       </c>
       <c r="G154" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="H154" s="11"/>
+      <c r="H154" s="2"/>
     </row>
     <row r="155" spans="3:8">
-      <c r="C155" s="3">
+      <c r="C155" s="4">
         <v>150</v>
       </c>
-      <c r="D155" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E155" s="5">
+      <c r="D155" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E155" s="6">
         <v>139</v>
       </c>
-      <c r="F155" s="5" t="s">
+      <c r="F155" s="6" t="s">
         <v>296</v>
       </c>
       <c r="G155" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="H155" s="11"/>
+      <c r="H155" s="2"/>
     </row>
     <row r="156" spans="3:8">
-      <c r="C156" s="3">
+      <c r="C156" s="4">
         <v>151</v>
       </c>
-      <c r="D156" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E156" s="5">
+      <c r="D156" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E156" s="6">
         <v>139</v>
       </c>
-      <c r="F156" s="5" t="s">
+      <c r="F156" s="6" t="s">
         <v>298</v>
       </c>
       <c r="G156" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="H156" s="11"/>
+      <c r="H156" s="2"/>
     </row>
     <row r="157" spans="3:8">
-      <c r="C157" s="3">
+      <c r="C157" s="4">
         <v>152</v>
       </c>
-      <c r="D157" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E157" s="5">
+      <c r="D157" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E157" s="6">
         <v>139</v>
       </c>
-      <c r="F157" s="5" t="s">
+      <c r="F157" s="6" t="s">
         <v>300</v>
       </c>
       <c r="G157" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="H157" s="11"/>
+      <c r="H157" s="2"/>
     </row>
     <row r="158" spans="3:8">
-      <c r="C158" s="3">
+      <c r="C158" s="4">
         <v>153</v>
       </c>
-      <c r="D158" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E158" s="5">
+      <c r="D158" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E158" s="6">
         <v>139</v>
       </c>
-      <c r="F158" s="5" t="s">
+      <c r="F158" s="6" t="s">
         <v>302</v>
       </c>
       <c r="G158" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="H158" s="11"/>
+      <c r="H158" s="2"/>
     </row>
     <row r="159" spans="3:8">
-      <c r="C159" s="3">
+      <c r="C159" s="4">
         <v>154</v>
       </c>
-      <c r="D159" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E159" s="5">
+      <c r="D159" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E159" s="6">
         <v>139</v>
       </c>
-      <c r="F159" s="5" t="s">
+      <c r="F159" s="6" t="s">
         <v>304</v>
       </c>
       <c r="G159" s="12" t="s">
         <v>305</v>
       </c>
-      <c r="H159" s="11"/>
+      <c r="H159" s="2"/>
     </row>
     <row r="160" spans="3:8">
-      <c r="C160" s="3">
+      <c r="C160" s="4">
         <v>155</v>
       </c>
-      <c r="D160" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E160" s="5">
+      <c r="D160" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E160" s="6">
         <v>155</v>
       </c>
-      <c r="F160" s="5" t="s">
+      <c r="F160" s="6" t="s">
         <v>306</v>
       </c>
       <c r="G160" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="H160" s="6"/>
+      <c r="H160" s="7"/>
     </row>
     <row r="161" spans="3:8">
-      <c r="C161" s="3">
+      <c r="C161" s="4">
         <v>156</v>
       </c>
-      <c r="D161" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E161" s="5">
+      <c r="D161" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E161" s="6">
         <v>155</v>
       </c>
-      <c r="F161" s="5" t="s">
+      <c r="F161" s="6" t="s">
         <v>308</v>
       </c>
       <c r="G161" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="H161" s="6"/>
+      <c r="H161" s="7"/>
     </row>
     <row r="162" spans="3:8">
-      <c r="C162" s="3">
+      <c r="C162" s="4">
         <v>157</v>
       </c>
-      <c r="D162" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E162" s="5">
+      <c r="D162" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E162" s="6">
         <v>155</v>
       </c>
-      <c r="F162" s="5" t="s">
+      <c r="F162" s="6" t="s">
         <v>310</v>
       </c>
       <c r="G162" s="12" t="s">
         <v>311</v>
       </c>
-      <c r="H162" s="6"/>
+      <c r="H162" s="7"/>
     </row>
     <row r="163" spans="3:8">
-      <c r="C163" s="3">
+      <c r="C163" s="4">
         <v>158</v>
       </c>
-      <c r="D163" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E163" s="5">
+      <c r="D163" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E163" s="6">
         <v>155</v>
       </c>
-      <c r="F163" s="5" t="s">
+      <c r="F163" s="6" t="s">
         <v>312</v>
       </c>
       <c r="G163" s="12" t="s">
         <v>313</v>
       </c>
-      <c r="H163" s="6"/>
+      <c r="H163" s="7"/>
     </row>
     <row r="164" spans="3:8">
-      <c r="C164" s="3">
+      <c r="C164" s="4">
         <v>159</v>
       </c>
-      <c r="D164" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E164" s="5">
+      <c r="D164" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E164" s="6">
         <v>155</v>
       </c>
-      <c r="F164" s="5" t="s">
+      <c r="F164" s="6" t="s">
         <v>314</v>
       </c>
       <c r="G164" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="H164" s="6"/>
+      <c r="H164" s="7"/>
     </row>
     <row r="165" spans="3:8">
-      <c r="C165" s="3">
+      <c r="C165" s="4">
         <v>160</v>
       </c>
-      <c r="D165" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E165" s="5">
+      <c r="D165" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E165" s="6">
         <v>155</v>
       </c>
-      <c r="F165" s="5" t="s">
+      <c r="F165" s="6" t="s">
         <v>316</v>
       </c>
       <c r="G165" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="H165" s="6"/>
+      <c r="H165" s="7"/>
     </row>
     <row r="166" spans="3:8">
-      <c r="C166" s="3">
+      <c r="C166" s="4">
         <v>161</v>
       </c>
-      <c r="D166" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E166" s="5">
+      <c r="D166" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E166" s="6">
         <v>155</v>
       </c>
-      <c r="F166" s="5" t="s">
+      <c r="F166" s="6" t="s">
         <v>318</v>
       </c>
       <c r="G166" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="H166" s="6"/>
+      <c r="H166" s="7"/>
     </row>
     <row r="167" spans="3:8">
-      <c r="C167" s="3">
+      <c r="C167" s="4">
         <v>162</v>
       </c>
-      <c r="D167" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E167" s="5">
+      <c r="D167" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E167" s="6">
         <v>155</v>
       </c>
-      <c r="F167" s="5" t="s">
+      <c r="F167" s="6" t="s">
         <v>320</v>
       </c>
       <c r="G167" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="H167" s="6"/>
+      <c r="H167" s="7"/>
     </row>
     <row r="168" spans="3:8">
-      <c r="C168" s="3">
+      <c r="C168" s="4">
         <v>163</v>
       </c>
-      <c r="D168" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E168" s="5">
+      <c r="D168" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E168" s="6">
         <v>163</v>
       </c>
-      <c r="F168" s="5" t="s">
+      <c r="F168" s="6" t="s">
         <v>322</v>
       </c>
       <c r="G168" s="12" t="s">
         <v>323</v>
       </c>
-      <c r="H168" s="10"/>
+      <c r="H168" s="11"/>
     </row>
     <row r="169" spans="3:8">
-      <c r="C169" s="3">
+      <c r="C169" s="4">
         <v>164</v>
       </c>
-      <c r="D169" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E169" s="5">
+      <c r="D169" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E169" s="6">
         <v>163</v>
       </c>
-      <c r="F169" s="5" t="s">
+      <c r="F169" s="6" t="s">
         <v>324</v>
       </c>
       <c r="G169" s="12" t="s">
         <v>325</v>
       </c>
-      <c r="H169" s="10"/>
+      <c r="H169" s="11"/>
     </row>
     <row r="170" spans="3:8">
-      <c r="C170" s="3">
+      <c r="C170" s="4">
         <v>165</v>
       </c>
-      <c r="D170" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E170" s="5">
+      <c r="D170" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E170" s="6">
         <v>163</v>
       </c>
-      <c r="F170" s="5" t="s">
+      <c r="F170" s="6" t="s">
         <v>326</v>
       </c>
       <c r="G170" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="H170" s="10"/>
+      <c r="H170" s="11"/>
     </row>
     <row r="171" spans="3:8">
-      <c r="C171" s="3">
+      <c r="C171" s="4">
         <v>166</v>
       </c>
-      <c r="D171" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E171" s="5">
+      <c r="D171" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E171" s="6">
         <v>163</v>
       </c>
-      <c r="F171" s="5" t="s">
+      <c r="F171" s="6" t="s">
         <v>328</v>
       </c>
       <c r="G171" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="H171" s="10"/>
+      <c r="H171" s="11"/>
     </row>
     <row r="172" spans="3:8">
-      <c r="C172" s="3">
+      <c r="C172" s="4">
         <v>167</v>
       </c>
-      <c r="D172" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E172" s="5">
+      <c r="D172" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E172" s="6">
         <v>163</v>
       </c>
-      <c r="F172" s="5" t="s">
+      <c r="F172" s="6" t="s">
         <v>329</v>
       </c>
       <c r="G172" s="12" t="s">
         <v>330</v>
       </c>
-      <c r="H172" s="10"/>
+      <c r="H172" s="11"/>
     </row>
     <row r="173" spans="3:8">
-      <c r="C173" s="3">
+      <c r="C173" s="4">
         <v>168</v>
       </c>
-      <c r="D173" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E173" s="5">
+      <c r="D173" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E173" s="6">
         <v>163</v>
       </c>
-      <c r="F173" s="5" t="s">
+      <c r="F173" s="6" t="s">
         <v>331</v>
       </c>
       <c r="G173" s="12" t="s">
         <v>332</v>
       </c>
-      <c r="H173" s="10"/>
+      <c r="H173" s="11"/>
     </row>
     <row r="174" spans="3:8">
-      <c r="C174" s="3">
+      <c r="C174" s="4">
         <v>169</v>
       </c>
-      <c r="D174" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E174" s="5">
+      <c r="D174" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E174" s="6">
         <v>163</v>
       </c>
-      <c r="F174" s="5" t="s">
+      <c r="F174" s="6" t="s">
         <v>333</v>
       </c>
       <c r="G174" s="12" t="s">
         <v>334</v>
       </c>
-      <c r="H174" s="10"/>
+      <c r="H174" s="11"/>
     </row>
     <row r="175" spans="3:8">
-      <c r="C175" s="3">
+      <c r="C175" s="4">
         <v>170</v>
       </c>
-      <c r="D175" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E175" s="5">
+      <c r="D175" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E175" s="6">
         <v>163</v>
       </c>
-      <c r="F175" s="5" t="s">
+      <c r="F175" s="6" t="s">
         <v>335</v>
       </c>
       <c r="G175" s="12" t="s">
         <v>336</v>
       </c>
-      <c r="H175" s="10"/>
+      <c r="H175" s="11"/>
     </row>
     <row r="176" spans="3:8">
-      <c r="C176" s="3">
+      <c r="C176" s="4">
         <v>172</v>
       </c>
-      <c r="D176" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E176" s="5">
+      <c r="D176" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E176" s="6">
         <v>172</v>
       </c>
-      <c r="F176" s="5" t="s">
+      <c r="F176" s="6" t="s">
         <v>337</v>
       </c>
       <c r="G176" s="12" t="s">
         <v>338</v>
       </c>
-      <c r="H176" s="11"/>
+      <c r="H176" s="2"/>
     </row>
     <row r="177" spans="3:8">
-      <c r="C177" s="3">
+      <c r="C177" s="4">
         <v>173</v>
       </c>
-      <c r="D177" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E177" s="5">
+      <c r="D177" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E177" s="6">
         <v>172</v>
       </c>
-      <c r="F177" s="5" t="s">
+      <c r="F177" s="6" t="s">
         <v>339</v>
       </c>
       <c r="G177" s="12" t="s">
         <v>340</v>
       </c>
-      <c r="H177" s="11"/>
+      <c r="H177" s="2"/>
     </row>
     <row r="178" spans="3:8">
-      <c r="C178" s="3">
+      <c r="C178" s="4">
         <v>174</v>
       </c>
-      <c r="D178" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E178" s="5">
+      <c r="D178" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E178" s="6">
         <v>172</v>
       </c>
-      <c r="F178" s="5" t="s">
+      <c r="F178" s="6" t="s">
         <v>341</v>
       </c>
       <c r="G178" s="12" t="s">
         <v>342</v>
       </c>
-      <c r="H178" s="11"/>
+      <c r="H178" s="2"/>
     </row>
     <row r="179" spans="3:8">
-      <c r="C179" s="3">
+      <c r="C179" s="4">
         <v>175</v>
       </c>
-      <c r="D179" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E179" s="5">
+      <c r="D179" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E179" s="6">
         <v>172</v>
       </c>
-      <c r="F179" s="5" t="s">
+      <c r="F179" s="6" t="s">
         <v>343</v>
       </c>
       <c r="G179" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="H179" s="11"/>
+      <c r="H179" s="2"/>
     </row>
     <row r="180" spans="3:8">
-      <c r="C180" s="3">
+      <c r="C180" s="4">
         <v>176</v>
       </c>
-      <c r="D180" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E180" s="5">
+      <c r="D180" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E180" s="6">
         <v>176</v>
       </c>
-      <c r="F180" s="5" t="s">
+      <c r="F180" s="6" t="s">
         <v>345</v>
       </c>
       <c r="G180" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="H180" s="6"/>
+      <c r="H180" s="7"/>
     </row>
     <row r="181" spans="3:8">
-      <c r="C181" s="3">
+      <c r="C181" s="4">
         <v>177</v>
       </c>
-      <c r="D181" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E181" s="5">
+      <c r="D181" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E181" s="6">
         <v>176</v>
       </c>
-      <c r="F181" s="5" t="s">
+      <c r="F181" s="6" t="s">
         <v>347</v>
       </c>
       <c r="G181" s="12" t="s">
         <v>348</v>
       </c>
-      <c r="H181" s="6"/>
+      <c r="H181" s="7"/>
     </row>
     <row r="182" spans="3:8">
-      <c r="C182" s="3">
+      <c r="C182" s="4">
         <v>178</v>
       </c>
-      <c r="D182" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E182" s="5">
+      <c r="D182" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E182" s="6">
         <v>176</v>
       </c>
-      <c r="F182" s="5" t="s">
+      <c r="F182" s="6" t="s">
         <v>349</v>
       </c>
       <c r="G182" s="12" t="s">
         <v>350</v>
       </c>
-      <c r="H182" s="6"/>
+      <c r="H182" s="7"/>
     </row>
     <row r="183" spans="3:8">
-      <c r="C183" s="3">
+      <c r="C183" s="4">
         <v>179</v>
       </c>
-      <c r="D183" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E183" s="5">
+      <c r="D183" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E183" s="6">
         <v>176</v>
       </c>
-      <c r="F183" s="5" t="s">
+      <c r="F183" s="6" t="s">
         <v>351</v>
       </c>
       <c r="G183" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="H183" s="6"/>
+      <c r="H183" s="7"/>
     </row>
     <row r="184" spans="3:8">
-      <c r="C184" s="3">
+      <c r="C184" s="4">
         <v>180</v>
       </c>
-      <c r="D184" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E184" s="5">
+      <c r="D184" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E184" s="6">
         <v>180</v>
       </c>
-      <c r="F184" s="5" t="s">
+      <c r="F184" s="6" t="s">
         <v>353</v>
       </c>
       <c r="G184" s="12" t="s">
         <v>354</v>
       </c>
-      <c r="H184" s="8"/>
+      <c r="H184" s="9"/>
     </row>
     <row r="185" spans="3:8">
-      <c r="C185" s="3">
+      <c r="C185" s="4">
         <v>181</v>
       </c>
-      <c r="D185" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E185" s="5">
+      <c r="D185" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E185" s="6">
         <v>180</v>
       </c>
-      <c r="F185" s="5" t="s">
+      <c r="F185" s="6" t="s">
         <v>355</v>
       </c>
       <c r="G185" s="12" t="s">
         <v>356</v>
       </c>
-      <c r="H185" s="8"/>
+      <c r="H185" s="9"/>
     </row>
     <row r="186" spans="3:8">
-      <c r="C186" s="3">
+      <c r="C186" s="4">
         <v>182</v>
       </c>
-      <c r="D186" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E186" s="5">
+      <c r="D186" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E186" s="6">
         <v>180</v>
       </c>
-      <c r="F186" s="5" t="s">
+      <c r="F186" s="6" t="s">
         <v>357</v>
       </c>
       <c r="G186" s="15" t="s">
         <v>358</v>
       </c>
-      <c r="H186" s="8"/>
+      <c r="H186" s="9"/>
     </row>
     <row r="187" spans="3:8">
-      <c r="C187" s="3">
+      <c r="C187" s="4">
         <v>183</v>
       </c>
-      <c r="D187" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E187" s="5">
+      <c r="D187" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E187" s="6">
         <v>180</v>
       </c>
-      <c r="F187" s="5" t="s">
+      <c r="F187" s="6" t="s">
         <v>359</v>
       </c>
       <c r="G187" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="H187" s="8"/>
+      <c r="H187" s="9"/>
     </row>
     <row r="188" spans="3:8">
-      <c r="C188" s="3">
+      <c r="C188" s="4">
         <v>184</v>
       </c>
-      <c r="D188" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E188" s="5">
+      <c r="D188" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E188" s="6">
         <v>184</v>
       </c>
-      <c r="F188" s="5" t="s">
+      <c r="F188" s="6" t="s">
         <v>361</v>
       </c>
       <c r="G188" s="12" t="s">
         <v>362</v>
       </c>
-      <c r="H188" s="10"/>
+      <c r="H188" s="11"/>
     </row>
     <row r="189" spans="3:8">
-      <c r="C189" s="3">
+      <c r="C189" s="4">
         <v>185</v>
       </c>
-      <c r="D189" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E189" s="5">
+      <c r="D189" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E189" s="6">
         <v>184</v>
       </c>
-      <c r="F189" s="5" t="s">
+      <c r="F189" s="6" t="s">
         <v>363</v>
       </c>
       <c r="G189" s="15" t="s">
         <v>364</v>
       </c>
-      <c r="H189" s="10"/>
+      <c r="H189" s="11"/>
     </row>
     <row r="190" spans="3:8">
-      <c r="C190" s="3">
+      <c r="C190" s="4">
         <v>186</v>
       </c>
-      <c r="D190" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E190" s="5">
+      <c r="D190" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E190" s="6">
         <v>186</v>
       </c>
-      <c r="F190" s="5" t="s">
+      <c r="F190" s="6" t="s">
         <v>365</v>
       </c>
       <c r="G190" s="15" t="s">
         <v>366</v>
       </c>
-      <c r="H190" s="8"/>
+      <c r="H190" s="9"/>
     </row>
     <row r="191" spans="3:8">
-      <c r="C191" s="3">
+      <c r="C191" s="4">
         <v>187</v>
       </c>
-      <c r="D191" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E191" s="5">
+      <c r="D191" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E191" s="6">
         <v>186</v>
       </c>
-      <c r="F191" s="5" t="s">
+      <c r="F191" s="6" t="s">
         <v>367</v>
       </c>
       <c r="G191" s="15" t="s">
         <v>368</v>
       </c>
-      <c r="H191" s="8"/>
+      <c r="H191" s="9"/>
     </row>
     <row r="192" spans="3:8">
-      <c r="C192" s="3">
+      <c r="C192" s="4">
         <v>188</v>
       </c>
-      <c r="D192" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E192" s="5">
+      <c r="D192" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E192" s="6">
         <v>188</v>
       </c>
-      <c r="F192" s="5" t="s">
+      <c r="F192" s="6" t="s">
         <v>369</v>
       </c>
       <c r="G192" s="12" t="s">
         <v>370</v>
       </c>
-      <c r="H192" s="10"/>
-    </row>
-    <row r="193" spans="3:8">
-      <c r="C193" s="3">
+      <c r="H192" s="11"/>
+    </row>
+    <row r="193" spans="1:8">
+      <c r="C193" s="4">
         <v>189</v>
       </c>
-      <c r="D193" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E193" s="5">
+      <c r="D193" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E193" s="6">
         <v>188</v>
       </c>
-      <c r="F193" s="5" t="s">
+      <c r="F193" s="6" t="s">
         <v>371</v>
       </c>
       <c r="G193" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="H193" s="10"/>
-    </row>
-    <row r="194" spans="3:8">
-      <c r="C194" s="3">
+      <c r="H193" s="11"/>
+    </row>
+    <row r="194" spans="1:8">
+      <c r="C194" s="4">
         <v>190</v>
       </c>
-      <c r="D194" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E194" s="5">
+      <c r="D194" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E194" s="6">
         <v>190</v>
       </c>
-      <c r="F194" s="5" t="s">
+      <c r="F194" s="6" t="s">
         <v>373</v>
       </c>
       <c r="G194" s="15" t="s">
         <v>374</v>
       </c>
-      <c r="H194" s="11"/>
-    </row>
-    <row r="195" spans="3:8">
-      <c r="C195" s="3">
+      <c r="H194" s="2"/>
+    </row>
+    <row r="195" spans="1:8">
+      <c r="C195" s="4">
         <v>191</v>
       </c>
-      <c r="D195" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E195" s="5">
+      <c r="D195" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E195" s="6">
         <v>190</v>
       </c>
-      <c r="F195" s="5" t="s">
+      <c r="F195" s="6" t="s">
         <v>375</v>
       </c>
       <c r="G195" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="H195" s="11"/>
-    </row>
-    <row r="196" spans="3:8">
-      <c r="C196" s="3">
+      <c r="H195" s="2"/>
+    </row>
+    <row r="196" spans="1:8">
+      <c r="C196" s="4">
         <v>192</v>
       </c>
-      <c r="D196" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E196" s="5">
+      <c r="D196" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E196" s="6">
         <v>192</v>
       </c>
-      <c r="F196" s="5" t="s">
+      <c r="F196" s="6" t="s">
         <v>377</v>
       </c>
       <c r="G196" s="12" t="s">
         <v>378</v>
       </c>
-      <c r="H196" s="10"/>
-    </row>
-    <row r="197" spans="3:8">
-      <c r="C197" s="3">
+      <c r="H196" s="11"/>
+    </row>
+    <row r="197" spans="1:8">
+      <c r="C197" s="4">
         <v>193</v>
       </c>
-      <c r="D197" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E197" s="5">
+      <c r="D197" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E197" s="6">
         <v>192</v>
       </c>
-      <c r="F197" s="5" t="s">
+      <c r="F197" s="6" t="s">
         <v>379</v>
       </c>
       <c r="G197" s="15" t="s">
         <v>380</v>
       </c>
-      <c r="H197" s="10"/>
-    </row>
-    <row r="198" spans="3:8">
-      <c r="C198" s="3">
+      <c r="H197" s="11"/>
+    </row>
+    <row r="198" spans="1:8">
+      <c r="C198" s="4">
         <v>194</v>
       </c>
-      <c r="D198" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E198" s="5">
+      <c r="D198" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E198" s="6">
         <v>194</v>
       </c>
-      <c r="F198" s="5" t="s">
+      <c r="F198" s="6" t="s">
         <v>381</v>
       </c>
       <c r="G198" s="15" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="199" spans="3:8">
-      <c r="C199" s="3">
+    <row r="199" spans="1:8">
+      <c r="C199" s="4">
         <v>195</v>
       </c>
-      <c r="D199" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E199" s="5">
+      <c r="D199" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E199" s="6">
         <v>195</v>
       </c>
-      <c r="F199" s="5" t="s">
+      <c r="F199" s="6" t="s">
         <v>383</v>
       </c>
       <c r="G199" s="15" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="200" spans="3:8">
-      <c r="C200" s="3">
+    <row r="200" spans="1:8">
+      <c r="C200" s="4">
         <v>196</v>
       </c>
-      <c r="D200" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E200" s="5">
+      <c r="D200" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E200" s="6">
         <v>196</v>
       </c>
-      <c r="F200" s="5" t="s">
+      <c r="F200" s="6" t="s">
         <v>385</v>
       </c>
       <c r="G200" s="15" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="201" spans="3:8">
-      <c r="C201" s="3">
+    <row r="201" spans="1:8">
+      <c r="C201" s="4">
         <v>197</v>
       </c>
-      <c r="D201" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E201" s="5">
+      <c r="D201" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E201" s="6">
         <v>197</v>
       </c>
-      <c r="F201" s="5" t="s">
+      <c r="F201" s="6" t="s">
         <v>387</v>
       </c>
       <c r="G201" s="15" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="202" spans="3:8">
-      <c r="C202" s="3">
+    <row r="202" spans="1:8">
+      <c r="C202" s="4">
         <v>198</v>
       </c>
-      <c r="D202" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E202" s="5">
+      <c r="D202" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E202" s="6">
         <v>198</v>
       </c>
-      <c r="F202" s="5" t="s">
+      <c r="F202" s="6" t="s">
         <v>389</v>
       </c>
       <c r="G202" s="15" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="203" ht="20" customHeight="1" spans="3:8">
-      <c r="C203" s="3">
+    <row r="203" ht="20" customHeight="1" spans="1:8">
+      <c r="C203" s="4">
         <v>199</v>
       </c>
-      <c r="D203" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E203" s="5">
+      <c r="D203" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E203" s="6">
         <v>199</v>
       </c>
-      <c r="F203" s="5" t="s">
+      <c r="F203" s="6" t="s">
         <v>391</v>
       </c>
       <c r="G203" s="15" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="204" spans="3:8">
-      <c r="C204" s="3">
+    <row r="204" spans="1:8">
+      <c r="C204" s="4">
         <v>200</v>
       </c>
-      <c r="D204" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E204" s="5">
+      <c r="D204" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E204" s="6">
         <v>200</v>
       </c>
-      <c r="F204" s="5" t="s">
+      <c r="F204" s="6" t="s">
         <v>393</v>
       </c>
       <c r="G204" s="15" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="205" spans="3:8">
-      <c r="C205" s="3">
+    <row r="205" s="2" customFormat="1" spans="1:8">
+      <c r="C205" s="16">
+        <v>202</v>
+      </c>
+      <c r="D205" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E205" s="17">
+        <v>202</v>
+      </c>
+      <c r="F205" s="17" t="s">
+        <v>395</v>
+      </c>
+      <c r="G205" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="206" s="2" customFormat="1" spans="1:8">
+      <c r="C206" s="16">
+        <v>203</v>
+      </c>
+      <c r="D206" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E206" s="17">
+        <v>203</v>
+      </c>
+      <c r="F206" s="17" t="s">
+        <v>397</v>
+      </c>
+      <c r="G206" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8">
+      <c r="A207" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C207" s="4">
         <v>211</v>
       </c>
-      <c r="D205" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E205" s="5">
+      <c r="D207" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E207" s="6">
         <v>211</v>
       </c>
-      <c r="F205" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="G205" s="15"/>
-    </row>
-    <row r="206" spans="3:8">
-      <c r="C206" s="3">
-        <v>202</v>
-      </c>
-      <c r="D206" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E206" s="5">
-        <v>202</v>
-      </c>
-      <c r="F206" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="G206" s="2" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="207" spans="3:8">
-      <c r="C207" s="3">
-        <v>203</v>
-      </c>
-      <c r="D207" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E207" s="5">
-        <v>203</v>
-      </c>
-      <c r="F207" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="G207" s="2" t="s">
-        <v>399</v>
-      </c>
+      <c r="F207" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="G207" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -5185,7 +5185,7 @@
       <c r="G160" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="H160" s="7"/>
+      <c r="H160" s="11"/>
     </row>
     <row r="161" spans="3:8">
       <c r="C161" s="4">
@@ -5203,7 +5203,7 @@
       <c r="G161" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="H161" s="7"/>
+      <c r="H161" s="11"/>
     </row>
     <row r="162" spans="3:8">
       <c r="C162" s="4">
@@ -5221,7 +5221,7 @@
       <c r="G162" s="12" t="s">
         <v>311</v>
       </c>
-      <c r="H162" s="7"/>
+      <c r="H162" s="11"/>
     </row>
     <row r="163" spans="3:8">
       <c r="C163" s="4">
@@ -5239,7 +5239,7 @@
       <c r="G163" s="12" t="s">
         <v>313</v>
       </c>
-      <c r="H163" s="7"/>
+      <c r="H163" s="11"/>
     </row>
     <row r="164" spans="3:8">
       <c r="C164" s="4">
@@ -5257,7 +5257,7 @@
       <c r="G164" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="H164" s="7"/>
+      <c r="H164" s="11"/>
     </row>
     <row r="165" spans="3:8">
       <c r="C165" s="4">
@@ -5275,7 +5275,7 @@
       <c r="G165" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="H165" s="7"/>
+      <c r="H165" s="11"/>
     </row>
     <row r="166" spans="3:8">
       <c r="C166" s="4">
@@ -5293,7 +5293,7 @@
       <c r="G166" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="H166" s="7"/>
+      <c r="H166" s="11"/>
     </row>
     <row r="167" spans="3:8">
       <c r="C167" s="4">
@@ -5311,7 +5311,7 @@
       <c r="G167" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="H167" s="7"/>
+      <c r="H167" s="11"/>
     </row>
     <row r="168" spans="3:8">
       <c r="C168" s="4">
@@ -5321,7 +5321,7 @@
         <v>9</v>
       </c>
       <c r="E168" s="6">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>322</v>
@@ -5339,7 +5339,7 @@
         <v>9</v>
       </c>
       <c r="E169" s="6">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F169" s="6" t="s">
         <v>324</v>
@@ -5357,7 +5357,7 @@
         <v>9</v>
       </c>
       <c r="E170" s="6">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>326</v>
@@ -5375,7 +5375,7 @@
         <v>9</v>
       </c>
       <c r="E171" s="6">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F171" s="6" t="s">
         <v>328</v>
@@ -5393,7 +5393,7 @@
         <v>9</v>
       </c>
       <c r="E172" s="6">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>329</v>
@@ -5411,7 +5411,7 @@
         <v>9</v>
       </c>
       <c r="E173" s="6">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F173" s="6" t="s">
         <v>331</v>
@@ -5429,7 +5429,7 @@
         <v>9</v>
       </c>
       <c r="E174" s="6">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>333</v>
@@ -5447,7 +5447,7 @@
         <v>9</v>
       </c>
       <c r="E175" s="6">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F175" s="6" t="s">
         <v>335</v>
@@ -5473,7 +5473,7 @@
       <c r="G176" s="12" t="s">
         <v>338</v>
       </c>
-      <c r="H176" s="2"/>
+      <c r="H176" s="7"/>
     </row>
     <row r="177" spans="3:8">
       <c r="C177" s="4">
@@ -5491,7 +5491,7 @@
       <c r="G177" s="12" t="s">
         <v>340</v>
       </c>
-      <c r="H177" s="2"/>
+      <c r="H177" s="7"/>
     </row>
     <row r="178" spans="3:8">
       <c r="C178" s="4">
@@ -5509,7 +5509,7 @@
       <c r="G178" s="12" t="s">
         <v>342</v>
       </c>
-      <c r="H178" s="2"/>
+      <c r="H178" s="7"/>
     </row>
     <row r="179" spans="3:8">
       <c r="C179" s="4">
@@ -5527,7 +5527,7 @@
       <c r="G179" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="H179" s="2"/>
+      <c r="H179" s="7"/>
     </row>
     <row r="180" spans="3:8">
       <c r="C180" s="4">
@@ -5537,7 +5537,7 @@
         <v>9</v>
       </c>
       <c r="E180" s="6">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>345</v>
@@ -5555,7 +5555,7 @@
         <v>9</v>
       </c>
       <c r="E181" s="6">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F181" s="6" t="s">
         <v>347</v>
@@ -5573,7 +5573,7 @@
         <v>9</v>
       </c>
       <c r="E182" s="6">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>349</v>
@@ -5591,7 +5591,7 @@
         <v>9</v>
       </c>
       <c r="E183" s="6">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F183" s="6" t="s">
         <v>351</v>
@@ -5869,6 +5869,7 @@
       <c r="G198" s="15" t="s">
         <v>382</v>
       </c>
+      <c r="H198" s="7"/>
     </row>
     <row r="199" spans="1:8">
       <c r="C199" s="4">
@@ -5878,7 +5879,7 @@
         <v>9</v>
       </c>
       <c r="E199" s="6">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F199" s="6" t="s">
         <v>383</v>
@@ -5886,6 +5887,7 @@
       <c r="G199" s="15" t="s">
         <v>384</v>
       </c>
+      <c r="H199" s="7"/>
     </row>
     <row r="200" spans="1:8">
       <c r="C200" s="4">
@@ -5903,6 +5905,7 @@
       <c r="G200" s="15" t="s">
         <v>386</v>
       </c>
+      <c r="H200" s="11"/>
     </row>
     <row r="201" spans="1:8">
       <c r="C201" s="4">
@@ -5912,7 +5915,7 @@
         <v>9</v>
       </c>
       <c r="E201" s="6">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F201" s="6" t="s">
         <v>387</v>
@@ -5920,6 +5923,7 @@
       <c r="G201" s="15" t="s">
         <v>388</v>
       </c>
+      <c r="H201" s="11"/>
     </row>
     <row r="202" spans="1:8">
       <c r="C202" s="4">

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="399">
   <si>
     <t>Id</t>
   </si>
@@ -1258,6 +1258,9 @@
   </si>
   <si>
     <t>WJBeta200</t>
+  </si>
+  <si>
+    <t>WJBeta211</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2334,7 +2337,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I206"/>
+  <dimension ref="C3:I207"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5923,7 +5926,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="203" spans="3:8">
+    <row r="203" ht="20" customHeight="1" spans="3:8">
       <c r="C203" s="3">
         <v>199</v>
       </c>
@@ -5957,36 +5960,51 @@
     </row>
     <row r="205" spans="3:8">
       <c r="C205" s="3">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="D205" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E205" s="5">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="F205" s="5" t="s">
         <v>394</v>
       </c>
-      <c r="G205" s="2" t="s">
-        <v>395</v>
-      </c>
+      <c r="G205" s="15"/>
     </row>
     <row r="206" spans="3:8">
       <c r="C206" s="3">
+        <v>202</v>
+      </c>
+      <c r="D206" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E206" s="5">
+        <v>202</v>
+      </c>
+      <c r="F206" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="G206" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="207" spans="3:8">
+      <c r="C207" s="3">
         <v>203</v>
       </c>
-      <c r="D206" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E206" s="5">
+      <c r="D207" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E207" s="5">
         <v>203</v>
       </c>
-      <c r="F206" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="G206" s="2" t="s">
+      <c r="F207" s="5" t="s">
         <v>397</v>
+      </c>
+      <c r="G207" s="2" t="s">
+        <v>398</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="403">
   <si>
     <t>Id</t>
   </si>
@@ -1279,6 +1279,12 @@
   </si>
   <si>
     <t>WJBeta211</t>
+  </si>
+  <si>
+    <t>月见之森</t>
+  </si>
+  <si>
+    <t>WJBeta212</t>
   </si>
 </sst>
 </file>
@@ -2349,7 +2355,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I207"/>
+  <dimension ref="A3:I208"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6026,7 +6032,24 @@
       <c r="F207" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="G207" s="15"/>
+      <c r="G207" s="15" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8">
+      <c r="C208" s="4">
+        <v>212</v>
+      </c>
+      <c r="D208" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E208" s="6">
+        <v>212</v>
+      </c>
+      <c r="F208" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="G208" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="20145" windowHeight="4560"/>
   </bookViews>
   <sheets>
     <sheet name="StartZoneConfig" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="404">
   <si>
     <t>Id</t>
   </si>
@@ -1285,6 +1285,9 @@
   </si>
   <si>
     <t>WJBeta212</t>
+  </si>
+  <si>
+    <t>天地同归</t>
   </si>
 </sst>
 </file>
@@ -6049,7 +6052,9 @@
       <c r="F208" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="G208" s="15"/>
+      <c r="G208" s="15" t="s">
+        <v>403</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20145" windowHeight="4560"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="StartZoneConfig" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="405">
   <si>
     <t>Id</t>
   </si>
@@ -1288,6 +1288,9 @@
   </si>
   <si>
     <t>天地同归</t>
+  </si>
+  <si>
+    <t>WJBeta213</t>
   </si>
 </sst>
 </file>
@@ -2358,7 +2361,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I208"/>
+  <dimension ref="A3:I209"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6056,6 +6059,21 @@
         <v>403</v>
       </c>
     </row>
+    <row r="209" spans="3:7">
+      <c r="C209" s="4">
+        <v>213</v>
+      </c>
+      <c r="D209" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E209" s="6">
+        <v>213</v>
+      </c>
+      <c r="F209" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="G209" s="15"/>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="407">
   <si>
     <t>Id</t>
   </si>
@@ -1291,6 +1291,12 @@
   </si>
   <si>
     <t>WJBeta213</t>
+  </si>
+  <si>
+    <t>盛世华章</t>
+  </si>
+  <si>
+    <t>WJBeta214</t>
   </si>
 </sst>
 </file>
@@ -2361,7 +2367,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I209"/>
+  <dimension ref="A3:I210"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6072,7 +6078,24 @@
       <c r="F209" s="6" t="s">
         <v>404</v>
       </c>
-      <c r="G209" s="15"/>
+      <c r="G209" s="15" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="210" spans="3:7">
+      <c r="C210" s="4">
+        <v>214</v>
+      </c>
+      <c r="D210" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E210" s="6">
+        <v>214</v>
+      </c>
+      <c r="F210" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="G210" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="408">
   <si>
     <t>Id</t>
   </si>
@@ -1297,6 +1297,9 @@
   </si>
   <si>
     <t>WJBeta214</t>
+  </si>
+  <si>
+    <t>烽火王座</t>
   </si>
 </sst>
 </file>
@@ -6095,7 +6098,9 @@
       <c r="F210" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="G210" s="15"/>
+      <c r="G210" s="15" t="s">
+        <v>407</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="409">
   <si>
     <t>Id</t>
   </si>
@@ -1300,6 +1300,9 @@
   </si>
   <si>
     <t>烽火王座</t>
+  </si>
+  <si>
+    <t>WJBeta215</t>
   </si>
 </sst>
 </file>
@@ -1502,12 +1505,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2370,7 +2373,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I210"/>
+  <dimension ref="A3:I211"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6102,6 +6105,21 @@
         <v>407</v>
       </c>
     </row>
+    <row r="211" spans="3:7">
+      <c r="C211" s="4">
+        <v>215</v>
+      </c>
+      <c r="D211" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E211" s="6">
+        <v>215</v>
+      </c>
+      <c r="F211" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="G211" s="15"/>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="410">
   <si>
     <t>Id</t>
   </si>
@@ -1303,6 +1303,9 @@
   </si>
   <si>
     <t>WJBeta215</t>
+  </si>
+  <si>
+    <t>凌云九霄</t>
   </si>
 </sst>
 </file>
@@ -1505,12 +1508,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -6118,7 +6121,9 @@
       <c r="F211" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="G211" s="15"/>
+      <c r="G211" s="15" t="s">
+        <v>409</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="411">
   <si>
     <t>Id</t>
   </si>
@@ -1306,6 +1306,9 @@
   </si>
   <si>
     <t>凌云九霄</t>
+  </si>
+  <si>
+    <t>WJBeta216</t>
   </si>
 </sst>
 </file>
@@ -2376,7 +2379,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I211"/>
+  <dimension ref="A3:I212"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6125,6 +6128,21 @@
         <v>409</v>
       </c>
     </row>
+    <row r="212" spans="3:7">
+      <c r="C212" s="4">
+        <v>216</v>
+      </c>
+      <c r="D212" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E212" s="6">
+        <v>216</v>
+      </c>
+      <c r="F212" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="G212" s="15"/>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="412">
   <si>
     <t>Id</t>
   </si>
@@ -1309,6 +1309,9 @@
   </si>
   <si>
     <t>WJBeta216</t>
+  </si>
+  <si>
+    <t>沧澜城</t>
   </si>
 </sst>
 </file>
@@ -6141,7 +6144,9 @@
       <c r="F212" s="6" t="s">
         <v>410</v>
       </c>
-      <c r="G212" s="15"/>
+      <c r="G212" s="15" t="s">
+        <v>411</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="413">
   <si>
     <t>Id</t>
   </si>
@@ -1312,6 +1312,9 @@
   </si>
   <si>
     <t>沧澜城</t>
+  </si>
+  <si>
+    <t>WJBeta217</t>
   </si>
 </sst>
 </file>
@@ -1514,12 +1517,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2382,7 +2385,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I212"/>
+  <dimension ref="A3:I213"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6148,6 +6151,21 @@
         <v>411</v>
       </c>
     </row>
+    <row r="213" spans="3:7">
+      <c r="C213" s="4">
+        <v>217</v>
+      </c>
+      <c r="D213" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E213" s="6">
+        <v>217</v>
+      </c>
+      <c r="F213" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="G213" s="15"/>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="414">
   <si>
     <t>Id</t>
   </si>
@@ -1315,6 +1315,9 @@
   </si>
   <si>
     <t>WJBeta217</t>
+  </si>
+  <si>
+    <t>惊鸿</t>
   </si>
 </sst>
 </file>
@@ -1517,18 +1520,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1537,7 +1540,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1562,6 +1565,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1882,7 +1891,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1906,16 +1915,16 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1924,89 +1933,89 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2027,9 +2036,10 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3583,7 +3593,7 @@
       <c r="G69" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H69" s="2"/>
+      <c r="H69" s="12"/>
     </row>
     <row r="70" spans="3:8">
       <c r="C70" s="4">
@@ -3601,7 +3611,7 @@
       <c r="G70" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="H70" s="2"/>
+      <c r="H70" s="12"/>
     </row>
     <row r="71" spans="3:8">
       <c r="C71" s="4">
@@ -3619,7 +3629,7 @@
       <c r="G71" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="H71" s="2"/>
+      <c r="H71" s="12"/>
     </row>
     <row r="72" spans="3:8">
       <c r="C72" s="4">
@@ -3637,7 +3647,7 @@
       <c r="G72" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H72" s="2"/>
+      <c r="H72" s="12"/>
     </row>
     <row r="73" spans="3:8">
       <c r="C73" s="4">
@@ -3655,7 +3665,7 @@
       <c r="G73" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="H73" s="2"/>
+      <c r="H73" s="12"/>
     </row>
     <row r="74" spans="3:8">
       <c r="C74" s="4">
@@ -3673,7 +3683,7 @@
       <c r="G74" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="H74" s="2"/>
+      <c r="H74" s="12"/>
     </row>
     <row r="75" spans="3:8">
       <c r="C75" s="4">
@@ -3691,7 +3701,7 @@
       <c r="G75" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H75" s="2"/>
+      <c r="H75" s="12"/>
     </row>
     <row r="76" spans="3:8">
       <c r="C76" s="4">
@@ -3709,7 +3719,7 @@
       <c r="G76" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="H76" s="2"/>
+      <c r="H76" s="12"/>
     </row>
     <row r="77" spans="3:8">
       <c r="C77" s="4">
@@ -3727,7 +3737,7 @@
       <c r="G77" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="H77" s="2"/>
+      <c r="H77" s="12"/>
     </row>
     <row r="78" spans="3:8">
       <c r="C78" s="4">
@@ -3745,7 +3755,7 @@
       <c r="G78" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="H78" s="2"/>
+      <c r="H78" s="12"/>
     </row>
     <row r="79" spans="3:8">
       <c r="C79" s="4">
@@ -3763,7 +3773,7 @@
       <c r="G79" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="H79" s="2"/>
+      <c r="H79" s="12"/>
     </row>
     <row r="80" spans="3:8">
       <c r="C80" s="4">
@@ -3781,7 +3791,7 @@
       <c r="G80" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="H80" s="2"/>
+      <c r="H80" s="12"/>
     </row>
     <row r="81" spans="3:9">
       <c r="C81" s="4">
@@ -3799,7 +3809,7 @@
       <c r="G81" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="H81" s="2"/>
+      <c r="H81" s="12"/>
     </row>
     <row r="82" spans="3:9">
       <c r="C82" s="4">
@@ -3817,7 +3827,7 @@
       <c r="G82" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H82" s="2"/>
+      <c r="H82" s="12"/>
     </row>
     <row r="83" spans="3:9">
       <c r="C83" s="4">
@@ -3835,7 +3845,7 @@
       <c r="G83" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H83" s="2"/>
+      <c r="H83" s="12"/>
     </row>
     <row r="84" spans="3:9">
       <c r="C84" s="4">
@@ -3853,7 +3863,7 @@
       <c r="G84" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="H84" s="2"/>
+      <c r="H84" s="12"/>
     </row>
     <row r="85" spans="3:9">
       <c r="C85" s="4">
@@ -4321,7 +4331,7 @@
       <c r="G110" t="s">
         <v>212</v>
       </c>
-      <c r="H110" s="2"/>
+      <c r="H110" s="12"/>
     </row>
     <row r="111" spans="3:8">
       <c r="C111" s="4">
@@ -4339,7 +4349,7 @@
       <c r="G111" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="H111" s="2"/>
+      <c r="H111" s="12"/>
     </row>
     <row r="112" spans="3:8">
       <c r="C112" s="4">
@@ -4357,7 +4367,7 @@
       <c r="G112" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="H112" s="2"/>
+      <c r="H112" s="12"/>
     </row>
     <row r="113" spans="3:8">
       <c r="C113" s="4">
@@ -4375,7 +4385,7 @@
       <c r="G113" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="H113" s="2"/>
+      <c r="H113" s="12"/>
     </row>
     <row r="114" spans="3:8">
       <c r="C114" s="4">
@@ -4393,7 +4403,7 @@
       <c r="G114" t="s">
         <v>220</v>
       </c>
-      <c r="H114" s="2"/>
+      <c r="H114" s="12"/>
     </row>
     <row r="115" spans="3:8">
       <c r="C115" s="4">
@@ -4411,7 +4421,7 @@
       <c r="G115" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="H115" s="2"/>
+      <c r="H115" s="12"/>
     </row>
     <row r="116" spans="3:8">
       <c r="C116" s="4">
@@ -4429,7 +4439,7 @@
       <c r="G116" t="s">
         <v>224</v>
       </c>
-      <c r="H116" s="2"/>
+      <c r="H116" s="12"/>
     </row>
     <row r="117" spans="3:8">
       <c r="C117" s="4">
@@ -4447,7 +4457,7 @@
       <c r="G117" t="s">
         <v>226</v>
       </c>
-      <c r="H117" s="2"/>
+      <c r="H117" s="12"/>
     </row>
     <row r="118" spans="3:8">
       <c r="C118" s="4">
@@ -4465,7 +4475,7 @@
       <c r="G118" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="H118" s="2"/>
+      <c r="H118" s="12"/>
     </row>
     <row r="119" spans="3:8">
       <c r="C119" s="4">
@@ -4480,10 +4490,10 @@
       <c r="F119" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="G119" s="12" t="s">
+      <c r="G119" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="H119" s="2"/>
+      <c r="H119" s="12"/>
     </row>
     <row r="120" spans="3:8">
       <c r="C120" s="4">
@@ -4501,7 +4511,7 @@
       <c r="G120" t="s">
         <v>232</v>
       </c>
-      <c r="H120" s="2"/>
+      <c r="H120" s="12"/>
     </row>
     <row r="121" spans="3:8">
       <c r="C121" s="4">
@@ -4519,7 +4529,7 @@
       <c r="G121" t="s">
         <v>234</v>
       </c>
-      <c r="H121" s="2"/>
+      <c r="H121" s="12"/>
     </row>
     <row r="122" spans="3:8">
       <c r="C122" s="4">
@@ -4537,7 +4547,7 @@
       <c r="G122" t="s">
         <v>236</v>
       </c>
-      <c r="H122" s="2"/>
+      <c r="H122" s="12"/>
     </row>
     <row r="123" spans="3:8">
       <c r="C123" s="4">
@@ -4552,10 +4562,10 @@
       <c r="F123" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="G123" s="12" t="s">
+      <c r="G123" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="H123" s="2"/>
+      <c r="H123" s="12"/>
     </row>
     <row r="124" spans="3:8">
       <c r="C124" s="4">
@@ -4573,7 +4583,7 @@
       <c r="G124" t="s">
         <v>240</v>
       </c>
-      <c r="H124" s="2"/>
+      <c r="H124" s="12"/>
     </row>
     <row r="125" spans="3:8">
       <c r="C125" s="4">
@@ -4591,7 +4601,7 @@
       <c r="G125" t="s">
         <v>242</v>
       </c>
-      <c r="H125" s="2"/>
+      <c r="H125" s="12"/>
     </row>
     <row r="126" spans="3:8">
       <c r="C126" s="4">
@@ -4624,7 +4634,7 @@
       <c r="F127" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="G127" s="12" t="s">
+      <c r="G127" s="13" t="s">
         <v>106</v>
       </c>
       <c r="H127" s="11"/>
@@ -4681,7 +4691,7 @@
       <c r="G130" t="s">
         <v>251</v>
       </c>
-      <c r="H130" s="13"/>
+      <c r="H130" s="14"/>
     </row>
     <row r="131" spans="3:9">
       <c r="C131" s="4">
@@ -4699,7 +4709,7 @@
       <c r="G131" t="s">
         <v>253</v>
       </c>
-      <c r="H131" s="13"/>
+      <c r="H131" s="14"/>
     </row>
     <row r="132" spans="3:9">
       <c r="C132" s="4">
@@ -4717,7 +4727,7 @@
       <c r="G132" t="s">
         <v>255</v>
       </c>
-      <c r="H132" s="13"/>
+      <c r="H132" s="14"/>
     </row>
     <row r="133" spans="3:9">
       <c r="C133" s="4">
@@ -4735,7 +4745,7 @@
       <c r="G133" t="s">
         <v>257</v>
       </c>
-      <c r="I133" s="2"/>
+      <c r="I133" s="12"/>
     </row>
     <row r="134" spans="3:9">
       <c r="C134" s="4">
@@ -4750,10 +4760,10 @@
       <c r="F134" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="G134" s="12" t="s">
+      <c r="G134" s="13" t="s">
         <v>259</v>
       </c>
-      <c r="H134" s="13"/>
+      <c r="H134" s="14"/>
     </row>
     <row r="135" spans="3:9">
       <c r="C135" s="4">
@@ -4771,7 +4781,7 @@
       <c r="G135" t="s">
         <v>261</v>
       </c>
-      <c r="H135" s="13"/>
+      <c r="H135" s="14"/>
     </row>
     <row r="136" spans="3:9">
       <c r="C136" s="4">
@@ -4804,7 +4814,7 @@
       <c r="F137" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="G137" s="12" t="s">
+      <c r="G137" s="13" t="s">
         <v>265</v>
       </c>
       <c r="H137" s="11"/>
@@ -4822,7 +4832,7 @@
       <c r="F138" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="G138" s="12" t="s">
+      <c r="G138" s="13" t="s">
         <v>267</v>
       </c>
       <c r="H138" s="11"/>
@@ -4840,7 +4850,7 @@
       <c r="F139" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="G139" s="12" t="s">
+      <c r="G139" s="13" t="s">
         <v>269</v>
       </c>
       <c r="H139" s="11"/>
@@ -4876,7 +4886,7 @@
       <c r="F141" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="G141" s="12" t="s">
+      <c r="G141" s="13" t="s">
         <v>273</v>
       </c>
       <c r="H141" s="11"/>
@@ -4894,7 +4904,7 @@
       <c r="F142" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="G142" s="12" t="s">
+      <c r="G142" s="13" t="s">
         <v>275</v>
       </c>
       <c r="H142" s="11"/>
@@ -4912,7 +4922,7 @@
       <c r="F143" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="G143" s="12" t="s">
+      <c r="G143" s="13" t="s">
         <v>277</v>
       </c>
       <c r="H143" s="11"/>
@@ -4930,10 +4940,10 @@
       <c r="F144" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="G144" s="12" t="s">
+      <c r="G144" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="H144" s="14"/>
+      <c r="H144" s="15"/>
     </row>
     <row r="145" spans="3:8">
       <c r="C145" s="4">
@@ -4948,10 +4958,10 @@
       <c r="F145" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="G145" s="12" t="s">
+      <c r="G145" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="H145" s="14"/>
+      <c r="H145" s="15"/>
     </row>
     <row r="146" spans="3:8">
       <c r="C146" s="4">
@@ -4966,10 +4976,10 @@
       <c r="F146" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="G146" s="12" t="s">
+      <c r="G146" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="H146" s="14"/>
+      <c r="H146" s="15"/>
     </row>
     <row r="147" spans="3:8">
       <c r="C147" s="4">
@@ -4984,10 +4994,10 @@
       <c r="F147" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="G147" s="12" t="s">
+      <c r="G147" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H147" s="14"/>
+      <c r="H147" s="15"/>
     </row>
     <row r="148" spans="3:8">
       <c r="C148" s="4">
@@ -5002,10 +5012,10 @@
       <c r="F148" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="G148" s="12" t="s">
+      <c r="G148" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="H148" s="2"/>
+      <c r="H148" s="12"/>
     </row>
     <row r="149" spans="3:8">
       <c r="C149" s="4">
@@ -5020,10 +5030,10 @@
       <c r="F149" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="G149" s="12" t="s">
+      <c r="G149" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="H149" s="2"/>
+      <c r="H149" s="12"/>
     </row>
     <row r="150" spans="3:8">
       <c r="C150" s="4">
@@ -5038,10 +5048,10 @@
       <c r="F150" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="G150" s="12" t="s">
+      <c r="G150" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="H150" s="2"/>
+      <c r="H150" s="12"/>
     </row>
     <row r="151" spans="3:8">
       <c r="C151" s="4">
@@ -5056,10 +5066,10 @@
       <c r="F151" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="G151" s="12" t="s">
+      <c r="G151" s="13" t="s">
         <v>290</v>
       </c>
-      <c r="H151" s="2"/>
+      <c r="H151" s="12"/>
     </row>
     <row r="152" spans="3:8">
       <c r="C152" s="4">
@@ -5074,10 +5084,10 @@
       <c r="F152" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="G152" s="12" t="s">
+      <c r="G152" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="H152" s="2"/>
+      <c r="H152" s="12"/>
     </row>
     <row r="153" spans="3:8">
       <c r="C153" s="4">
@@ -5092,10 +5102,10 @@
       <c r="F153" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="G153" s="12" t="s">
+      <c r="G153" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="H153" s="2"/>
+      <c r="H153" s="12"/>
     </row>
     <row r="154" spans="3:8">
       <c r="C154" s="4">
@@ -5110,10 +5120,10 @@
       <c r="F154" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="G154" s="12" t="s">
+      <c r="G154" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="H154" s="2"/>
+      <c r="H154" s="12"/>
     </row>
     <row r="155" spans="3:8">
       <c r="C155" s="4">
@@ -5128,10 +5138,10 @@
       <c r="F155" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="G155" s="12" t="s">
+      <c r="G155" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="H155" s="2"/>
+      <c r="H155" s="12"/>
     </row>
     <row r="156" spans="3:8">
       <c r="C156" s="4">
@@ -5146,10 +5156,10 @@
       <c r="F156" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="G156" s="12" t="s">
+      <c r="G156" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="H156" s="2"/>
+      <c r="H156" s="12"/>
     </row>
     <row r="157" spans="3:8">
       <c r="C157" s="4">
@@ -5164,10 +5174,10 @@
       <c r="F157" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="G157" s="12" t="s">
+      <c r="G157" s="13" t="s">
         <v>301</v>
       </c>
-      <c r="H157" s="2"/>
+      <c r="H157" s="12"/>
     </row>
     <row r="158" spans="3:8">
       <c r="C158" s="4">
@@ -5182,10 +5192,10 @@
       <c r="F158" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="G158" s="12" t="s">
+      <c r="G158" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="H158" s="2"/>
+      <c r="H158" s="12"/>
     </row>
     <row r="159" spans="3:8">
       <c r="C159" s="4">
@@ -5200,10 +5210,10 @@
       <c r="F159" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="G159" s="12" t="s">
+      <c r="G159" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="H159" s="2"/>
+      <c r="H159" s="12"/>
     </row>
     <row r="160" spans="3:8">
       <c r="C160" s="4">
@@ -5218,7 +5228,7 @@
       <c r="F160" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="G160" s="12" t="s">
+      <c r="G160" s="13" t="s">
         <v>307</v>
       </c>
       <c r="H160" s="11"/>
@@ -5236,7 +5246,7 @@
       <c r="F161" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="G161" s="12" t="s">
+      <c r="G161" s="13" t="s">
         <v>309</v>
       </c>
       <c r="H161" s="11"/>
@@ -5254,7 +5264,7 @@
       <c r="F162" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="G162" s="12" t="s">
+      <c r="G162" s="13" t="s">
         <v>311</v>
       </c>
       <c r="H162" s="11"/>
@@ -5272,7 +5282,7 @@
       <c r="F163" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="G163" s="12" t="s">
+      <c r="G163" s="13" t="s">
         <v>313</v>
       </c>
       <c r="H163" s="11"/>
@@ -5290,7 +5300,7 @@
       <c r="F164" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="G164" s="12" t="s">
+      <c r="G164" s="13" t="s">
         <v>315</v>
       </c>
       <c r="H164" s="11"/>
@@ -5308,7 +5318,7 @@
       <c r="F165" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G165" s="12" t="s">
+      <c r="G165" s="13" t="s">
         <v>317</v>
       </c>
       <c r="H165" s="11"/>
@@ -5326,7 +5336,7 @@
       <c r="F166" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="G166" s="12" t="s">
+      <c r="G166" s="13" t="s">
         <v>319</v>
       </c>
       <c r="H166" s="11"/>
@@ -5344,7 +5354,7 @@
       <c r="F167" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="G167" s="12" t="s">
+      <c r="G167" s="13" t="s">
         <v>321</v>
       </c>
       <c r="H167" s="11"/>
@@ -5362,7 +5372,7 @@
       <c r="F168" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="G168" s="12" t="s">
+      <c r="G168" s="13" t="s">
         <v>323</v>
       </c>
       <c r="H168" s="11"/>
@@ -5380,7 +5390,7 @@
       <c r="F169" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="G169" s="12" t="s">
+      <c r="G169" s="13" t="s">
         <v>325</v>
       </c>
       <c r="H169" s="11"/>
@@ -5398,7 +5408,7 @@
       <c r="F170" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="G170" s="12" t="s">
+      <c r="G170" s="13" t="s">
         <v>327</v>
       </c>
       <c r="H170" s="11"/>
@@ -5416,7 +5426,7 @@
       <c r="F171" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="G171" s="12" t="s">
+      <c r="G171" s="13" t="s">
         <v>196</v>
       </c>
       <c r="H171" s="11"/>
@@ -5434,7 +5444,7 @@
       <c r="F172" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="G172" s="12" t="s">
+      <c r="G172" s="13" t="s">
         <v>330</v>
       </c>
       <c r="H172" s="11"/>
@@ -5452,7 +5462,7 @@
       <c r="F173" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="G173" s="12" t="s">
+      <c r="G173" s="13" t="s">
         <v>332</v>
       </c>
       <c r="H173" s="11"/>
@@ -5470,7 +5480,7 @@
       <c r="F174" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="G174" s="12" t="s">
+      <c r="G174" s="13" t="s">
         <v>334</v>
       </c>
       <c r="H174" s="11"/>
@@ -5488,7 +5498,7 @@
       <c r="F175" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="G175" s="12" t="s">
+      <c r="G175" s="13" t="s">
         <v>336</v>
       </c>
       <c r="H175" s="11"/>
@@ -5506,7 +5516,7 @@
       <c r="F176" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="G176" s="12" t="s">
+      <c r="G176" s="13" t="s">
         <v>338</v>
       </c>
       <c r="H176" s="7"/>
@@ -5524,7 +5534,7 @@
       <c r="F177" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="G177" s="12" t="s">
+      <c r="G177" s="13" t="s">
         <v>340</v>
       </c>
       <c r="H177" s="7"/>
@@ -5542,7 +5552,7 @@
       <c r="F178" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="G178" s="12" t="s">
+      <c r="G178" s="13" t="s">
         <v>342</v>
       </c>
       <c r="H178" s="7"/>
@@ -5560,7 +5570,7 @@
       <c r="F179" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="G179" s="12" t="s">
+      <c r="G179" s="13" t="s">
         <v>344</v>
       </c>
       <c r="H179" s="7"/>
@@ -5578,7 +5588,7 @@
       <c r="F180" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="G180" s="12" t="s">
+      <c r="G180" s="13" t="s">
         <v>346</v>
       </c>
       <c r="H180" s="7"/>
@@ -5596,7 +5606,7 @@
       <c r="F181" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="G181" s="12" t="s">
+      <c r="G181" s="13" t="s">
         <v>348</v>
       </c>
       <c r="H181" s="7"/>
@@ -5614,7 +5624,7 @@
       <c r="F182" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="G182" s="12" t="s">
+      <c r="G182" s="13" t="s">
         <v>350</v>
       </c>
       <c r="H182" s="7"/>
@@ -5632,7 +5642,7 @@
       <c r="F183" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="G183" s="12" t="s">
+      <c r="G183" s="13" t="s">
         <v>352</v>
       </c>
       <c r="H183" s="7"/>
@@ -5650,7 +5660,7 @@
       <c r="F184" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="G184" s="12" t="s">
+      <c r="G184" s="13" t="s">
         <v>354</v>
       </c>
       <c r="H184" s="9"/>
@@ -5668,7 +5678,7 @@
       <c r="F185" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="G185" s="12" t="s">
+      <c r="G185" s="13" t="s">
         <v>356</v>
       </c>
       <c r="H185" s="9"/>
@@ -5686,7 +5696,7 @@
       <c r="F186" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="G186" s="15" t="s">
+      <c r="G186" s="16" t="s">
         <v>358</v>
       </c>
       <c r="H186" s="9"/>
@@ -5704,7 +5714,7 @@
       <c r="F187" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="G187" s="12" t="s">
+      <c r="G187" s="13" t="s">
         <v>360</v>
       </c>
       <c r="H187" s="9"/>
@@ -5722,7 +5732,7 @@
       <c r="F188" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="G188" s="12" t="s">
+      <c r="G188" s="13" t="s">
         <v>362</v>
       </c>
       <c r="H188" s="11"/>
@@ -5740,7 +5750,7 @@
       <c r="F189" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="G189" s="15" t="s">
+      <c r="G189" s="16" t="s">
         <v>364</v>
       </c>
       <c r="H189" s="11"/>
@@ -5753,12 +5763,12 @@
         <v>9</v>
       </c>
       <c r="E190" s="6">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="G190" s="15" t="s">
+      <c r="G190" s="16" t="s">
         <v>366</v>
       </c>
       <c r="H190" s="9"/>
@@ -5771,12 +5781,12 @@
         <v>9</v>
       </c>
       <c r="E191" s="6">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F191" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="G191" s="15" t="s">
+      <c r="G191" s="16" t="s">
         <v>368</v>
       </c>
       <c r="H191" s="9"/>
@@ -5794,12 +5804,12 @@
       <c r="F192" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="G192" s="12" t="s">
+      <c r="G192" s="13" t="s">
         <v>370</v>
       </c>
       <c r="H192" s="11"/>
     </row>
-    <row r="193" spans="1:8">
+    <row r="193" spans="1:9">
       <c r="C193" s="4">
         <v>189</v>
       </c>
@@ -5812,12 +5822,12 @@
       <c r="F193" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="G193" s="12" t="s">
+      <c r="G193" s="13" t="s">
         <v>372</v>
       </c>
       <c r="H193" s="11"/>
     </row>
-    <row r="194" spans="1:8">
+    <row r="194" spans="1:9">
       <c r="C194" s="4">
         <v>190</v>
       </c>
@@ -5825,17 +5835,17 @@
         <v>9</v>
       </c>
       <c r="E194" s="6">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="G194" s="15" t="s">
+      <c r="G194" s="16" t="s">
         <v>374</v>
       </c>
-      <c r="H194" s="2"/>
-    </row>
-    <row r="195" spans="1:8">
+      <c r="H194" s="11"/>
+    </row>
+    <row r="195" spans="1:9">
       <c r="C195" s="4">
         <v>191</v>
       </c>
@@ -5843,17 +5853,17 @@
         <v>9</v>
       </c>
       <c r="E195" s="6">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F195" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="G195" s="15" t="s">
+      <c r="G195" s="16" t="s">
         <v>376</v>
       </c>
-      <c r="H195" s="2"/>
-    </row>
-    <row r="196" spans="1:8">
+      <c r="H195" s="11"/>
+    </row>
+    <row r="196" spans="1:9">
       <c r="C196" s="4">
         <v>192</v>
       </c>
@@ -5866,12 +5876,12 @@
       <c r="F196" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="G196" s="12" t="s">
+      <c r="G196" s="13" t="s">
         <v>378</v>
       </c>
       <c r="H196" s="11"/>
     </row>
-    <row r="197" spans="1:8">
+    <row r="197" spans="1:9">
       <c r="C197" s="4">
         <v>193</v>
       </c>
@@ -5884,12 +5894,12 @@
       <c r="F197" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="G197" s="15" t="s">
+      <c r="G197" s="16" t="s">
         <v>380</v>
       </c>
       <c r="H197" s="11"/>
     </row>
-    <row r="198" spans="1:8">
+    <row r="198" spans="1:9">
       <c r="C198" s="4">
         <v>194</v>
       </c>
@@ -5902,12 +5912,12 @@
       <c r="F198" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="G198" s="15" t="s">
+      <c r="G198" s="16" t="s">
         <v>382</v>
       </c>
       <c r="H198" s="7"/>
     </row>
-    <row r="199" spans="1:8">
+    <row r="199" spans="1:9">
       <c r="C199" s="4">
         <v>195</v>
       </c>
@@ -5920,12 +5930,12 @@
       <c r="F199" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="G199" s="15" t="s">
+      <c r="G199" s="16" t="s">
         <v>384</v>
       </c>
       <c r="H199" s="7"/>
     </row>
-    <row r="200" spans="1:8">
+    <row r="200" spans="1:9">
       <c r="C200" s="4">
         <v>196</v>
       </c>
@@ -5938,12 +5948,12 @@
       <c r="F200" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="G200" s="15" t="s">
+      <c r="G200" s="16" t="s">
         <v>386</v>
       </c>
       <c r="H200" s="11"/>
     </row>
-    <row r="201" spans="1:8">
+    <row r="201" spans="1:9">
       <c r="C201" s="4">
         <v>197</v>
       </c>
@@ -5956,12 +5966,12 @@
       <c r="F201" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="G201" s="15" t="s">
+      <c r="G201" s="16" t="s">
         <v>388</v>
       </c>
       <c r="H201" s="11"/>
     </row>
-    <row r="202" spans="1:8">
+    <row r="202" spans="1:9">
       <c r="C202" s="4">
         <v>198</v>
       </c>
@@ -5974,11 +5984,12 @@
       <c r="F202" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="G202" s="15" t="s">
+      <c r="G202" s="16" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="203" ht="20" customHeight="1" spans="1:8">
+      <c r="H202" s="12"/>
+    </row>
+    <row r="203" ht="20" customHeight="1" spans="1:9">
       <c r="C203" s="4">
         <v>199</v>
       </c>
@@ -5986,16 +5997,17 @@
         <v>9</v>
       </c>
       <c r="E203" s="6">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F203" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="G203" s="15" t="s">
+      <c r="G203" s="16" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="204" spans="1:8">
+      <c r="H203" s="12"/>
+    </row>
+    <row r="204" spans="1:9">
       <c r="C204" s="4">
         <v>200</v>
       </c>
@@ -6008,45 +6020,48 @@
       <c r="F204" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="G204" s="15" t="s">
+      <c r="G204" s="16" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="205" s="2" customFormat="1" spans="1:8">
-      <c r="C205" s="16">
+      <c r="H204" s="11"/>
+    </row>
+    <row r="205" s="2" customFormat="1" spans="1:9">
+      <c r="C205" s="17">
         <v>202</v>
       </c>
-      <c r="D205" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E205" s="17">
+      <c r="D205" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E205" s="18">
         <v>202</v>
       </c>
-      <c r="F205" s="17" t="s">
+      <c r="F205" s="18" t="s">
         <v>395</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="206" s="2" customFormat="1" spans="1:8">
-      <c r="C206" s="16">
+      <c r="I205" s="11"/>
+    </row>
+    <row r="206" s="2" customFormat="1" spans="1:9">
+      <c r="C206" s="17">
         <v>203</v>
       </c>
-      <c r="D206" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E206" s="17">
+      <c r="D206" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E206" s="18">
         <v>203</v>
       </c>
-      <c r="F206" s="17" t="s">
+      <c r="F206" s="18" t="s">
         <v>397</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="207" spans="1:8">
+      <c r="I206" s="11"/>
+    </row>
+    <row r="207" spans="1:9">
       <c r="A207" s="3" t="s">
         <v>399</v>
       </c>
@@ -6057,16 +6072,17 @@
         <v>9</v>
       </c>
       <c r="E207" s="6">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="F207" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="G207" s="15" t="s">
+      <c r="G207" s="16" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="208" spans="1:8">
+      <c r="H207" s="11"/>
+    </row>
+    <row r="208" spans="1:9">
       <c r="C208" s="4">
         <v>212</v>
       </c>
@@ -6079,11 +6095,12 @@
       <c r="F208" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="G208" s="15" t="s">
+      <c r="G208" s="16" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="209" spans="3:7">
+      <c r="H208" s="12"/>
+    </row>
+    <row r="209" spans="3:8">
       <c r="C209" s="4">
         <v>213</v>
       </c>
@@ -6091,16 +6108,17 @@
         <v>9</v>
       </c>
       <c r="E209" s="6">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F209" s="6" t="s">
         <v>404</v>
       </c>
-      <c r="G209" s="15" t="s">
+      <c r="G209" s="16" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="210" spans="3:7">
+      <c r="H209" s="12"/>
+    </row>
+    <row r="210" spans="3:8">
       <c r="C210" s="4">
         <v>214</v>
       </c>
@@ -6113,11 +6131,11 @@
       <c r="F210" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="G210" s="15" t="s">
+      <c r="G210" s="16" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="211" spans="3:7">
+    <row r="211" spans="3:8">
       <c r="C211" s="4">
         <v>215</v>
       </c>
@@ -6130,11 +6148,11 @@
       <c r="F211" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="G211" s="15" t="s">
+      <c r="G211" s="16" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="212" spans="3:7">
+    <row r="212" spans="3:8">
       <c r="C212" s="4">
         <v>216</v>
       </c>
@@ -6147,11 +6165,11 @@
       <c r="F212" s="6" t="s">
         <v>410</v>
       </c>
-      <c r="G212" s="15" t="s">
+      <c r="G212" s="16" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="213" spans="3:7">
+    <row r="213" spans="3:8">
       <c r="C213" s="4">
         <v>217</v>
       </c>
@@ -6164,7 +6182,9 @@
       <c r="F213" s="6" t="s">
         <v>412</v>
       </c>
-      <c r="G213" s="15"/>
+      <c r="G213" s="16" t="s">
+        <v>413</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="415">
   <si>
     <t>Id</t>
   </si>
@@ -1318,6 +1318,9 @@
   </si>
   <si>
     <t>惊鸿</t>
+  </si>
+  <si>
+    <t>WJBeta218</t>
   </si>
 </sst>
 </file>
@@ -2395,7 +2398,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I213"/>
+  <dimension ref="A3:I214"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6186,6 +6189,21 @@
         <v>413</v>
       </c>
     </row>
+    <row r="214" spans="3:8">
+      <c r="C214" s="4">
+        <v>218</v>
+      </c>
+      <c r="D214" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E214" s="6">
+        <v>218</v>
+      </c>
+      <c r="F214" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="G214" s="16"/>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="416">
   <si>
     <t>Id</t>
   </si>
@@ -1321,6 +1321,9 @@
   </si>
   <si>
     <t>WJBeta218</t>
+  </si>
+  <si>
+    <t>观星台</t>
   </si>
 </sst>
 </file>
@@ -1523,12 +1526,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -6202,7 +6205,9 @@
       <c r="F214" s="6" t="s">
         <v>414</v>
       </c>
-      <c r="G214" s="16"/>
+      <c r="G214" s="16" t="s">
+        <v>415</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="417">
   <si>
     <t>Id</t>
   </si>
@@ -1324,6 +1324,9 @@
   </si>
   <si>
     <t>观星台</t>
+  </si>
+  <si>
+    <t>WJBeta219</t>
   </si>
 </sst>
 </file>
@@ -2401,7 +2404,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I214"/>
+  <dimension ref="A3:I215"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6209,6 +6212,21 @@
         <v>415</v>
       </c>
     </row>
+    <row r="215" spans="3:8">
+      <c r="C215" s="4">
+        <v>219</v>
+      </c>
+      <c r="D215" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E215" s="6">
+        <v>219</v>
+      </c>
+      <c r="F215" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="G215" s="16"/>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="418">
   <si>
     <t>Id</t>
   </si>
@@ -1327,6 +1327,9 @@
   </si>
   <si>
     <t>WJBeta219</t>
+  </si>
+  <si>
+    <t>星月同辉</t>
   </si>
 </sst>
 </file>
@@ -1529,12 +1532,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -6225,7 +6228,9 @@
       <c r="F215" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="G215" s="16"/>
+      <c r="G215" s="16" t="s">
+        <v>417</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="419">
   <si>
     <t>Id</t>
   </si>
@@ -1330,6 +1330,9 @@
   </si>
   <si>
     <t>星月同辉</t>
+  </si>
+  <si>
+    <t>WJBeta220</t>
   </si>
 </sst>
 </file>
@@ -2407,7 +2410,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I215"/>
+  <dimension ref="A3:I216"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6232,6 +6235,21 @@
         <v>417</v>
       </c>
     </row>
+    <row r="216" spans="3:8">
+      <c r="C216" s="4">
+        <v>220</v>
+      </c>
+      <c r="D216" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E216" s="6">
+        <v>220</v>
+      </c>
+      <c r="F216" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="G216" s="16"/>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="420">
   <si>
     <t>Id</t>
   </si>
@@ -1333,6 +1333,9 @@
   </si>
   <si>
     <t>WJBeta220</t>
+  </si>
+  <si>
+    <t>九天揽星</t>
   </si>
 </sst>
 </file>
@@ -2030,7 +2033,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2062,6 +2065,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6248,7 +6252,9 @@
       <c r="F216" s="6" t="s">
         <v>418</v>
       </c>
-      <c r="G216" s="16"/>
+      <c r="G216" s="19" t="s">
+        <v>419</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="421">
   <si>
     <t>Id</t>
   </si>
@@ -1336,6 +1336,9 @@
   </si>
   <si>
     <t>九天揽星</t>
+  </si>
+  <si>
+    <t>WJBeta221</t>
   </si>
 </sst>
 </file>
@@ -2033,7 +2036,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2065,7 +2068,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2414,7 +2416,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I216"/>
+  <dimension ref="A3:I217"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6252,8 +6254,25 @@
       <c r="F216" s="6" t="s">
         <v>418</v>
       </c>
-      <c r="G216" s="19" t="s">
+      <c r="G216" s="13" t="s">
         <v>419</v>
+      </c>
+    </row>
+    <row r="217" spans="3:8">
+      <c r="C217" s="4">
+        <v>221</v>
+      </c>
+      <c r="D217" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E217" s="6">
+        <v>221</v>
+      </c>
+      <c r="F217" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="G217" s="16" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="422">
   <si>
     <t>Id</t>
   </si>
@@ -1339,6 +1339,9 @@
   </si>
   <si>
     <t>WJBeta221</t>
+  </si>
+  <si>
+    <t>WJBeta222</t>
   </si>
 </sst>
 </file>
@@ -2416,7 +2419,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I217"/>
+  <dimension ref="A3:I218"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6275,6 +6278,21 @@
         <v>40</v>
       </c>
     </row>
+    <row r="218" spans="3:8">
+      <c r="C218" s="4">
+        <v>222</v>
+      </c>
+      <c r="D218" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E218" s="6">
+        <v>222</v>
+      </c>
+      <c r="F218" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="G218" s="16"/>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="423">
   <si>
     <t>Id</t>
   </si>
@@ -1342,6 +1342,9 @@
   </si>
   <si>
     <t>WJBeta222</t>
+  </si>
+  <si>
+    <t>绿茵世界</t>
   </si>
 </sst>
 </file>
@@ -1555,7 +1558,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1595,6 +1598,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1915,7 +1924,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1939,16 +1948,16 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1957,89 +1966,89 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2071,6 +2080,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5903,7 +5913,7 @@
       <c r="G196" s="13" t="s">
         <v>378</v>
       </c>
-      <c r="H196" s="11"/>
+      <c r="H196" s="7"/>
     </row>
     <row r="197" spans="1:9">
       <c r="C197" s="4">
@@ -5921,7 +5931,7 @@
       <c r="G197" s="16" t="s">
         <v>380</v>
       </c>
-      <c r="H197" s="11"/>
+      <c r="H197" s="7"/>
     </row>
     <row r="198" spans="1:9">
       <c r="C198" s="4">
@@ -5931,7 +5941,7 @@
         <v>9</v>
       </c>
       <c r="E198" s="6">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>381</v>
@@ -5949,7 +5959,7 @@
         <v>9</v>
       </c>
       <c r="E199" s="6">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F199" s="6" t="s">
         <v>383</v>
@@ -5975,7 +5985,7 @@
       <c r="G200" s="16" t="s">
         <v>386</v>
       </c>
-      <c r="H200" s="11"/>
+      <c r="H200" s="9"/>
     </row>
     <row r="201" spans="1:9">
       <c r="C201" s="4">
@@ -5993,7 +6003,7 @@
       <c r="G201" s="16" t="s">
         <v>388</v>
       </c>
-      <c r="H201" s="11"/>
+      <c r="H201" s="9"/>
     </row>
     <row r="202" spans="1:9">
       <c r="C202" s="4">
@@ -6003,7 +6013,7 @@
         <v>9</v>
       </c>
       <c r="E202" s="6">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>389</v>
@@ -6011,7 +6021,7 @@
       <c r="G202" s="16" t="s">
         <v>390</v>
       </c>
-      <c r="H202" s="12"/>
+      <c r="H202" s="9"/>
     </row>
     <row r="203" ht="20" customHeight="1" spans="1:9">
       <c r="C203" s="4">
@@ -6021,7 +6031,7 @@
         <v>9</v>
       </c>
       <c r="E203" s="6">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F203" s="6" t="s">
         <v>391</v>
@@ -6029,7 +6039,7 @@
       <c r="G203" s="16" t="s">
         <v>392</v>
       </c>
-      <c r="H203" s="12"/>
+      <c r="H203" s="9"/>
     </row>
     <row r="204" spans="1:9">
       <c r="C204" s="4">
@@ -6158,6 +6168,7 @@
       <c r="G210" s="16" t="s">
         <v>407</v>
       </c>
+      <c r="H210" s="19"/>
     </row>
     <row r="211" spans="3:8">
       <c r="C211" s="4">
@@ -6167,7 +6178,7 @@
         <v>9</v>
       </c>
       <c r="E211" s="6">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F211" s="6" t="s">
         <v>408</v>
@@ -6175,6 +6186,7 @@
       <c r="G211" s="16" t="s">
         <v>409</v>
       </c>
+      <c r="H211" s="19"/>
     </row>
     <row r="212" spans="3:8">
       <c r="C212" s="4">
@@ -6192,6 +6204,7 @@
       <c r="G212" s="16" t="s">
         <v>411</v>
       </c>
+      <c r="H212" s="12"/>
     </row>
     <row r="213" spans="3:8">
       <c r="C213" s="4">
@@ -6201,7 +6214,7 @@
         <v>9</v>
       </c>
       <c r="E213" s="6">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F213" s="6" t="s">
         <v>412</v>
@@ -6209,6 +6222,7 @@
       <c r="G213" s="16" t="s">
         <v>413</v>
       </c>
+      <c r="H213" s="12"/>
     </row>
     <row r="214" spans="3:8">
       <c r="C214" s="4">
@@ -6291,7 +6305,9 @@
       <c r="F218" s="6" t="s">
         <v>421</v>
       </c>
-      <c r="G218" s="16"/>
+      <c r="G218" s="16" t="s">
+        <v>422</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="425">
   <si>
     <t>Id</t>
   </si>
@@ -1345,6 +1345,12 @@
   </si>
   <si>
     <t>绿茵世界</t>
+  </si>
+  <si>
+    <t>WJBeta223</t>
+  </si>
+  <si>
+    <t>飞龙在天</t>
   </si>
 </sst>
 </file>
@@ -2429,7 +2435,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I218"/>
+  <dimension ref="A3:I219"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6309,6 +6315,23 @@
         <v>422</v>
       </c>
     </row>
+    <row r="219" spans="3:8">
+      <c r="C219" s="4">
+        <v>223</v>
+      </c>
+      <c r="D219" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E219" s="6">
+        <v>223</v>
+      </c>
+      <c r="F219" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="G219" s="13" t="s">
+        <v>424</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="427">
   <si>
     <t>Id</t>
   </si>
@@ -1351,6 +1351,12 @@
   </si>
   <si>
     <t>飞龙在天</t>
+  </si>
+  <si>
+    <t>WJBeta224</t>
+  </si>
+  <si>
+    <t>永恒秘境</t>
   </si>
 </sst>
 </file>
@@ -2435,7 +2441,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I219"/>
+  <dimension ref="A3:I220"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6332,6 +6338,23 @@
         <v>424</v>
       </c>
     </row>
+    <row r="220" spans="3:8">
+      <c r="C220" s="4">
+        <v>224</v>
+      </c>
+      <c r="D220" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E220" s="6">
+        <v>224</v>
+      </c>
+      <c r="F220" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="G220" s="16" t="s">
+        <v>426</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="428">
   <si>
     <t>Id</t>
   </si>
@@ -1357,6 +1357,9 @@
   </si>
   <si>
     <t>永恒秘境</t>
+  </si>
+  <si>
+    <t>WJBeta225</t>
   </si>
 </sst>
 </file>
@@ -2441,7 +2444,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I220"/>
+  <dimension ref="A3:I221"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6355,6 +6358,21 @@
         <v>426</v>
       </c>
     </row>
+    <row r="221" spans="3:8">
+      <c r="C221" s="4">
+        <v>225</v>
+      </c>
+      <c r="D221" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E221" s="6">
+        <v>225</v>
+      </c>
+      <c r="F221" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="G221" s="13"/>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="429">
   <si>
     <t>Id</t>
   </si>
@@ -1360,6 +1360,9 @@
   </si>
   <si>
     <t>WJBeta225</t>
+  </si>
+  <si>
+    <t>陌上花开</t>
   </si>
 </sst>
 </file>
@@ -6371,7 +6374,9 @@
       <c r="F221" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="G221" s="13"/>
+      <c r="G221" s="13" t="s">
+        <v>428</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="431">
   <si>
     <t>Id</t>
   </si>
@@ -1363,6 +1363,12 @@
   </si>
   <si>
     <t>陌上花开</t>
+  </si>
+  <si>
+    <t>WJBeta226</t>
+  </si>
+  <si>
+    <t>一剑惊鸿</t>
   </si>
 </sst>
 </file>
@@ -2447,7 +2453,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I221"/>
+  <dimension ref="A3:I222"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6378,6 +6384,23 @@
         <v>428</v>
       </c>
     </row>
+    <row r="222" spans="3:8">
+      <c r="C222" s="4">
+        <v>226</v>
+      </c>
+      <c r="D222" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E222" s="6">
+        <v>226</v>
+      </c>
+      <c r="F222" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="G222" s="16" t="s">
+        <v>430</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="432">
   <si>
     <t>Id</t>
   </si>
@@ -1369,6 +1369,9 @@
   </si>
   <si>
     <t>一剑惊鸿</t>
+  </si>
+  <si>
+    <t>WJBeta227</t>
   </si>
 </sst>
 </file>
@@ -2453,7 +2456,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I222"/>
+  <dimension ref="A3:I223"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6401,6 +6404,21 @@
         <v>430</v>
       </c>
     </row>
+    <row r="223" spans="3:8">
+      <c r="C223" s="4">
+        <v>227</v>
+      </c>
+      <c r="D223" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E223" s="6">
+        <v>227</v>
+      </c>
+      <c r="F223" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="G223" s="16"/>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="433">
   <si>
     <t>Id</t>
   </si>
@@ -1372,6 +1372,9 @@
   </si>
   <si>
     <t>WJBeta227</t>
+  </si>
+  <si>
+    <t>逐光</t>
   </si>
 </sst>
 </file>
@@ -6417,7 +6420,9 @@
       <c r="F223" s="6" t="s">
         <v>431</v>
       </c>
-      <c r="G223" s="16"/>
+      <c r="G223" s="16" t="s">
+        <v>432</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="434">
   <si>
     <t>Id</t>
   </si>
@@ -1375,6 +1375,9 @@
   </si>
   <si>
     <t>逐光</t>
+  </si>
+  <si>
+    <t>WJBeta228</t>
   </si>
 </sst>
 </file>
@@ -2459,7 +2462,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I223"/>
+  <dimension ref="A3:I224"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6424,6 +6427,21 @@
         <v>432</v>
       </c>
     </row>
+    <row r="224" spans="3:8">
+      <c r="C224" s="4">
+        <v>228</v>
+      </c>
+      <c r="D224" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E224" s="6">
+        <v>228</v>
+      </c>
+      <c r="F224" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="G224" s="13"/>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -5730,7 +5730,7 @@
       <c r="G184" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="H184" s="9"/>
+      <c r="H184" s="12"/>
     </row>
     <row r="185" spans="3:8">
       <c r="C185" s="4">
@@ -5748,7 +5748,7 @@
       <c r="G185" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="H185" s="9"/>
+      <c r="H185" s="12"/>
     </row>
     <row r="186" spans="3:8">
       <c r="C186" s="4">
@@ -5766,7 +5766,7 @@
       <c r="G186" s="16" t="s">
         <v>358</v>
       </c>
-      <c r="H186" s="9"/>
+      <c r="H186" s="12"/>
     </row>
     <row r="187" spans="3:8">
       <c r="C187" s="4">
@@ -5784,7 +5784,7 @@
       <c r="G187" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="H187" s="9"/>
+      <c r="H187" s="12"/>
     </row>
     <row r="188" spans="3:8">
       <c r="C188" s="4">
@@ -5794,7 +5794,7 @@
         <v>9</v>
       </c>
       <c r="E188" s="6">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>361</v>
@@ -5802,7 +5802,7 @@
       <c r="G188" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="H188" s="11"/>
+      <c r="H188" s="12"/>
     </row>
     <row r="189" spans="3:8">
       <c r="C189" s="4">
@@ -5812,7 +5812,7 @@
         <v>9</v>
       </c>
       <c r="E189" s="6">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F189" s="6" t="s">
         <v>363</v>
@@ -5820,7 +5820,7 @@
       <c r="G189" s="16" t="s">
         <v>364</v>
       </c>
-      <c r="H189" s="11"/>
+      <c r="H189" s="12"/>
     </row>
     <row r="190" spans="3:8">
       <c r="C190" s="4">
@@ -5830,7 +5830,7 @@
         <v>9</v>
       </c>
       <c r="E190" s="6">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>365</v>
@@ -5838,7 +5838,7 @@
       <c r="G190" s="16" t="s">
         <v>366</v>
       </c>
-      <c r="H190" s="9"/>
+      <c r="H190" s="12"/>
     </row>
     <row r="191" spans="3:8">
       <c r="C191" s="4">
@@ -5848,7 +5848,7 @@
         <v>9</v>
       </c>
       <c r="E191" s="6">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F191" s="6" t="s">
         <v>367</v>
@@ -5856,7 +5856,7 @@
       <c r="G191" s="16" t="s">
         <v>368</v>
       </c>
-      <c r="H191" s="9"/>
+      <c r="H191" s="12"/>
     </row>
     <row r="192" spans="3:8">
       <c r="C192" s="4">
@@ -5874,7 +5874,7 @@
       <c r="G192" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="H192" s="11"/>
+      <c r="H192" s="7"/>
     </row>
     <row r="193" spans="1:9">
       <c r="C193" s="4">
@@ -5892,7 +5892,7 @@
       <c r="G193" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="H193" s="11"/>
+      <c r="H193" s="7"/>
     </row>
     <row r="194" spans="1:9">
       <c r="C194" s="4">
@@ -5910,7 +5910,7 @@
       <c r="G194" s="16" t="s">
         <v>374</v>
       </c>
-      <c r="H194" s="11"/>
+      <c r="H194" s="7"/>
     </row>
     <row r="195" spans="1:9">
       <c r="C195" s="4">
@@ -5928,7 +5928,7 @@
       <c r="G195" s="16" t="s">
         <v>376</v>
       </c>
-      <c r="H195" s="11"/>
+      <c r="H195" s="7"/>
     </row>
     <row r="196" spans="1:9">
       <c r="C196" s="4">
@@ -5938,7 +5938,7 @@
         <v>9</v>
       </c>
       <c r="E196" s="6">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>377</v>
@@ -5956,7 +5956,7 @@
         <v>9</v>
       </c>
       <c r="E197" s="6">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F197" s="6" t="s">
         <v>379</v>
@@ -5974,7 +5974,7 @@
         <v>9</v>
       </c>
       <c r="E198" s="6">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>381</v>
@@ -5992,7 +5992,7 @@
         <v>9</v>
       </c>
       <c r="E199" s="6">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F199" s="6" t="s">
         <v>383</v>
@@ -6108,7 +6108,7 @@
       <c r="G205" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="I205" s="11"/>
+      <c r="I205" s="12"/>
     </row>
     <row r="206" s="2" customFormat="1" spans="1:9">
       <c r="C206" s="17">
@@ -6126,7 +6126,7 @@
       <c r="G206" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="I206" s="11"/>
+      <c r="I206" s="12"/>
     </row>
     <row r="207" spans="1:9">
       <c r="A207" s="3" t="s">
@@ -6157,7 +6157,7 @@
         <v>9</v>
       </c>
       <c r="E208" s="6">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>402</v>
@@ -6165,7 +6165,7 @@
       <c r="G208" s="16" t="s">
         <v>403</v>
       </c>
-      <c r="H208" s="12"/>
+      <c r="H208" s="11"/>
     </row>
     <row r="209" spans="3:8">
       <c r="C209" s="4">
@@ -6175,7 +6175,7 @@
         <v>9</v>
       </c>
       <c r="E209" s="6">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="F209" s="6" t="s">
         <v>404</v>
@@ -6183,7 +6183,7 @@
       <c r="G209" s="16" t="s">
         <v>405</v>
       </c>
-      <c r="H209" s="12"/>
+      <c r="H209" s="11"/>
     </row>
     <row r="210" spans="3:8">
       <c r="C210" s="4">
@@ -6273,6 +6273,7 @@
       <c r="G214" s="16" t="s">
         <v>415</v>
       </c>
+      <c r="H214" s="11"/>
     </row>
     <row r="215" spans="3:8">
       <c r="C215" s="4">
@@ -6282,7 +6283,7 @@
         <v>9</v>
       </c>
       <c r="E215" s="6">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F215" s="6" t="s">
         <v>416</v>
@@ -6290,6 +6291,7 @@
       <c r="G215" s="16" t="s">
         <v>417</v>
       </c>
+      <c r="H215" s="11"/>
     </row>
     <row r="216" spans="3:8">
       <c r="C216" s="4">
@@ -6307,6 +6309,7 @@
       <c r="G216" s="13" t="s">
         <v>419</v>
       </c>
+      <c r="H216" s="9"/>
     </row>
     <row r="217" spans="3:8">
       <c r="C217" s="4">
@@ -6316,7 +6319,7 @@
         <v>9</v>
       </c>
       <c r="E217" s="6">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F217" s="6" t="s">
         <v>420</v>
@@ -6324,6 +6327,7 @@
       <c r="G217" s="16" t="s">
         <v>40</v>
       </c>
+      <c r="H217" s="9"/>
     </row>
     <row r="218" spans="3:8">
       <c r="C218" s="4">
@@ -6341,6 +6345,7 @@
       <c r="G218" s="16" t="s">
         <v>422</v>
       </c>
+      <c r="H218" s="11"/>
     </row>
     <row r="219" spans="3:8">
       <c r="C219" s="4">
@@ -6350,7 +6355,7 @@
         <v>9</v>
       </c>
       <c r="E219" s="6">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F219" s="6" t="s">
         <v>423</v>
@@ -6358,6 +6363,7 @@
       <c r="G219" s="13" t="s">
         <v>424</v>
       </c>
+      <c r="H219" s="11"/>
     </row>
     <row r="220" spans="3:8">
       <c r="C220" s="4">

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="13905" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="StartZoneConfig" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="436">
   <si>
     <t>Id</t>
   </si>
@@ -1378,6 +1378,12 @@
   </si>
   <si>
     <t>WJBeta228</t>
+  </si>
+  <si>
+    <t>长安故梦</t>
+  </si>
+  <si>
+    <t>WJBeta229</t>
   </si>
 </sst>
 </file>
@@ -2462,7 +2468,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I224"/>
+  <dimension ref="A3:I225"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6446,7 +6452,24 @@
       <c r="F224" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="G224" s="13"/>
+      <c r="G224" s="13" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="225" spans="3:7">
+      <c r="C225" s="4">
+        <v>229</v>
+      </c>
+      <c r="D225" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E225" s="6">
+        <v>229</v>
+      </c>
+      <c r="F225" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="G225" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13905" windowHeight="11775"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="StartZoneConfig" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="437">
   <si>
     <t>Id</t>
   </si>
@@ -1384,6 +1384,9 @@
   </si>
   <si>
     <t>WJBeta229</t>
+  </si>
+  <si>
+    <t>星尘圣殿</t>
   </si>
 </sst>
 </file>
@@ -2087,7 +2090,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2120,6 +2123,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6469,7 +6473,9 @@
       <c r="F225" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="G225" s="13"/>
+      <c r="G225" s="20" t="s">
+        <v>436</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Localhost\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="StartZoneConfig" sheetId="1" r:id="rId1"/>
@@ -59,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="438">
   <si>
     <t>Id</t>
   </si>
@@ -1387,6 +1392,9 @@
   </si>
   <si>
     <t>星尘圣殿</t>
+  </si>
+  <si>
+    <t>WJBeta230</t>
   </si>
 </sst>
 </file>
@@ -2090,7 +2098,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2123,7 +2131,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2472,7 +2479,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I225"/>
+  <dimension ref="A3:I226"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6473,9 +6480,24 @@
       <c r="F225" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="G225" s="20" t="s">
+      <c r="G225" s="13" t="s">
         <v>436</v>
       </c>
+    </row>
+    <row r="226" spans="3:7">
+      <c r="C226" s="4">
+        <v>230</v>
+      </c>
+      <c r="D226" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E226" s="6">
+        <v>230</v>
+      </c>
+      <c r="F226" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="G226" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Localhost\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing20220362\Excel\StartConfig\Localhost\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="440">
   <si>
     <t>Id</t>
   </si>
@@ -1395,6 +1395,12 @@
   </si>
   <si>
     <t>WJBeta230</t>
+  </si>
+  <si>
+    <t>风语神殿</t>
+  </si>
+  <si>
+    <t>WJBeta231</t>
   </si>
 </sst>
 </file>
@@ -1597,12 +1603,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2479,7 +2485,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I226"/>
+  <dimension ref="A3:I227"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6497,7 +6503,24 @@
       <c r="F226" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="G226" s="13"/>
+      <c r="G226" s="13" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="227" spans="3:7">
+      <c r="C227" s="4">
+        <v>231</v>
+      </c>
+      <c r="D227" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E227" s="6">
+        <v>231</v>
+      </c>
+      <c r="F227" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="G227" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing20220362\Excel\StartConfig\Localhost\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Localhost\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="441">
   <si>
     <t>Id</t>
   </si>
@@ -1401,6 +1401,9 @@
   </si>
   <si>
     <t>WJBeta231</t>
+  </si>
+  <si>
+    <t>霜烬王座</t>
   </si>
 </sst>
 </file>
@@ -1603,12 +1606,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2104,7 +2107,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2137,6 +2140,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6520,7 +6524,9 @@
       <c r="F227" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="G227" s="13"/>
+      <c r="G227" s="20" t="s">
+        <v>440</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="442">
   <si>
     <t>Id</t>
   </si>
@@ -1404,6 +1404,9 @@
   </si>
   <si>
     <t>霜烬王座</t>
+  </si>
+  <si>
+    <t>WJBeta232</t>
   </si>
 </sst>
 </file>
@@ -1606,12 +1609,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2107,7 +2110,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2140,7 +2143,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2489,7 +2491,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I227"/>
+  <dimension ref="A3:I228"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6524,9 +6526,24 @@
       <c r="F227" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="G227" s="20" t="s">
+      <c r="G227" s="13" t="s">
         <v>440</v>
       </c>
+    </row>
+    <row r="228" spans="3:7">
+      <c r="C228" s="4">
+        <v>232</v>
+      </c>
+      <c r="D228" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E228" s="6">
+        <v>232</v>
+      </c>
+      <c r="F228" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="G228" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="443">
   <si>
     <t>Id</t>
   </si>
@@ -1407,6 +1407,9 @@
   </si>
   <si>
     <t>WJBeta232</t>
+  </si>
+  <si>
+    <t>神之岛屿</t>
   </si>
 </sst>
 </file>
@@ -1609,12 +1612,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -6543,7 +6546,9 @@
       <c r="F228" s="6" t="s">
         <v>441</v>
       </c>
-      <c r="G228" s="13"/>
+      <c r="G228" s="13" t="s">
+        <v>442</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Localhost\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing20220362\Excel\StartConfig\Localhost\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="444">
   <si>
     <t>Id</t>
   </si>
@@ -1410,6 +1410,9 @@
   </si>
   <si>
     <t>神之岛屿</t>
+  </si>
+  <si>
+    <t>WJBeta233</t>
   </si>
 </sst>
 </file>
@@ -2494,7 +2497,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I228"/>
+  <dimension ref="A3:I229"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6550,6 +6553,21 @@
         <v>442</v>
       </c>
     </row>
+    <row r="229" spans="3:7">
+      <c r="C229" s="4">
+        <v>233</v>
+      </c>
+      <c r="D229" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E229" s="6">
+        <v>233</v>
+      </c>
+      <c r="F229" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="G229" s="13"/>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing20220362\Excel\StartConfig\Localhost\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Localhost\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="445">
   <si>
     <t>Id</t>
   </si>
@@ -1413,6 +1413,9 @@
   </si>
   <si>
     <t>WJBeta233</t>
+  </si>
+  <si>
+    <t>炽焰圣殿</t>
   </si>
 </sst>
 </file>
@@ -6566,7 +6569,9 @@
       <c r="F229" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="G229" s="13"/>
+      <c r="G229" s="13" t="s">
+        <v>444</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="447">
   <si>
     <t>Id</t>
   </si>
@@ -1416,6 +1416,12 @@
   </si>
   <si>
     <t>炽焰圣殿</t>
+  </si>
+  <si>
+    <t>WJBeta234</t>
+  </si>
+  <si>
+    <t>不朽之城</t>
   </si>
 </sst>
 </file>
@@ -1618,12 +1624,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2119,7 +2125,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2152,6 +2158,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2500,7 +2507,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I229"/>
+  <dimension ref="A3:I230"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6573,6 +6580,23 @@
         <v>444</v>
       </c>
     </row>
+    <row r="230" spans="3:7">
+      <c r="C230" s="4">
+        <v>234</v>
+      </c>
+      <c r="D230" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E230" s="6">
+        <v>234</v>
+      </c>
+      <c r="F230" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="G230" s="20" t="s">
+        <v>446</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="448">
   <si>
     <t>Id</t>
   </si>
@@ -1422,6 +1422,9 @@
   </si>
   <si>
     <t>不朽之城</t>
+  </si>
+  <si>
+    <t>WJBeta235</t>
   </si>
 </sst>
 </file>
@@ -1624,12 +1627,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2125,7 +2128,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2158,7 +2161,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2507,7 +2509,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I230"/>
+  <dimension ref="A3:I231"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6593,9 +6595,24 @@
       <c r="F230" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="G230" s="20" t="s">
+      <c r="G230" s="13" t="s">
         <v>446</v>
       </c>
+    </row>
+    <row r="231" spans="3:7">
+      <c r="C231" s="4">
+        <v>235</v>
+      </c>
+      <c r="D231" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E231" s="6">
+        <v>235</v>
+      </c>
+      <c r="F231" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="G231" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="446">
   <si>
     <t>Id</t>
   </si>
@@ -117,9 +117,6 @@
     <t>先锋1</t>
   </si>
   <si>
-    <t>12合区34合区</t>
-  </si>
-  <si>
     <t>WJBeta6</t>
   </si>
   <si>
@@ -142,9 +139,6 @@
   </si>
   <si>
     <t>先锋5</t>
-  </si>
-  <si>
-    <t>567合区</t>
   </si>
   <si>
     <t>WJBeta10</t>
@@ -2523,7 +2517,7 @@
     <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:8">
+    <row r="3" spans="3:7">
       <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
@@ -2537,7 +2531,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="3:8">
+    <row r="4" spans="3:7">
       <c r="C4" s="5" t="s">
         <v>0</v>
       </c>
@@ -2551,7 +2545,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="3:8">
+    <row r="5" spans="3:7">
       <c r="C5" s="5" t="s">
         <v>7</v>
       </c>
@@ -2565,7 +2559,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="3:8">
+    <row r="6" s="1" customFormat="1" spans="3:7">
       <c r="C6" s="6">
         <v>1</v>
       </c>
@@ -2579,7 +2573,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="3:8">
+    <row r="7" spans="3:7">
       <c r="C7" s="4">
         <v>2</v>
       </c>
@@ -2596,7 +2590,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="3:8">
+    <row r="8" spans="3:7">
       <c r="C8" s="4">
         <v>3</v>
       </c>
@@ -2613,7 +2607,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="3:8">
+    <row r="9" spans="3:7">
       <c r="C9" s="4">
         <v>4</v>
       </c>
@@ -2630,7 +2624,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="3:8">
+    <row r="10" spans="3:7">
       <c r="C10" s="4">
         <v>5</v>
       </c>
@@ -2646,11 +2640,8 @@
       <c r="G10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="3:8">
+    </row>
+    <row r="11" spans="3:7">
       <c r="C11" s="4">
         <v>6</v>
       </c>
@@ -2661,13 +2652,13 @@
         <v>5</v>
       </c>
       <c r="F11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="3:8">
+    </row>
+    <row r="12" spans="3:7">
       <c r="C12" s="6">
         <v>7</v>
       </c>
@@ -2678,13 +2669,13 @@
         <v>5</v>
       </c>
       <c r="F12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="3:8">
+    </row>
+    <row r="13" spans="3:7">
       <c r="C13" s="4">
         <v>8</v>
       </c>
@@ -2695,33 +2686,30 @@
         <v>5</v>
       </c>
       <c r="F13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="3" t="s">
+    </row>
+    <row r="14" spans="3:7">
+      <c r="C14" s="4">
+        <v>9</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="4">
+        <v>9</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="14" spans="3:8">
-      <c r="C14" s="4">
-        <v>9</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="4">
-        <v>9</v>
-      </c>
-      <c r="F14" s="6" t="s">
+      <c r="G14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="3:8">
+    </row>
+    <row r="15" spans="3:7">
       <c r="C15" s="4">
         <v>10</v>
       </c>
@@ -2732,13 +2720,13 @@
         <v>9</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="3:8">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="3:7">
       <c r="C16" s="6">
         <v>11</v>
       </c>
@@ -2749,10 +2737,10 @@
         <v>9</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="3:8">
@@ -2766,10 +2754,10 @@
         <v>12</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H17" s="7"/>
     </row>
@@ -2784,10 +2772,10 @@
         <v>12</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H18" s="7"/>
     </row>
@@ -2802,10 +2790,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H19" s="7"/>
     </row>
@@ -2820,10 +2808,10 @@
         <v>12</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H20" s="7"/>
     </row>
@@ -2838,10 +2826,10 @@
         <v>12</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H21" s="7"/>
     </row>
@@ -2856,10 +2844,10 @@
         <v>12</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H22" s="7"/>
     </row>
@@ -2874,10 +2862,10 @@
         <v>12</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H23" s="8"/>
     </row>
@@ -2892,10 +2880,10 @@
         <v>12</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H24" s="8"/>
     </row>
@@ -2910,10 +2898,10 @@
         <v>12</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H25" s="7"/>
     </row>
@@ -2928,10 +2916,10 @@
         <v>12</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H26" s="7"/>
     </row>
@@ -2946,10 +2934,10 @@
         <v>12</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H27" s="8"/>
     </row>
@@ -2964,10 +2952,10 @@
         <v>12</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H28" s="8"/>
     </row>
@@ -2982,10 +2970,10 @@
         <v>12</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H29" s="8"/>
     </row>
@@ -3000,10 +2988,10 @@
         <v>12</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H30" s="8"/>
     </row>
@@ -3018,10 +3006,10 @@
         <v>12</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H31" s="7"/>
     </row>
@@ -3036,10 +3024,10 @@
         <v>12</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H32" s="7"/>
     </row>
@@ -3054,10 +3042,10 @@
         <v>12</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H33" s="7"/>
     </row>
@@ -3072,10 +3060,10 @@
         <v>12</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H34" s="8"/>
     </row>
@@ -3090,10 +3078,10 @@
         <v>12</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H35" s="7"/>
     </row>
@@ -3108,10 +3096,10 @@
         <v>12</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H36" s="7"/>
     </row>
@@ -3123,13 +3111,13 @@
         <v>9</v>
       </c>
       <c r="E37" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H37" s="9"/>
     </row>
@@ -3141,13 +3129,13 @@
         <v>9</v>
       </c>
       <c r="E38" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H38" s="9"/>
     </row>
@@ -3159,13 +3147,13 @@
         <v>9</v>
       </c>
       <c r="E39" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H39" s="9"/>
     </row>
@@ -3177,13 +3165,13 @@
         <v>9</v>
       </c>
       <c r="E40" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H40" s="9"/>
     </row>
@@ -3195,13 +3183,13 @@
         <v>9</v>
       </c>
       <c r="E41" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H41" s="9"/>
     </row>
@@ -3213,13 +3201,13 @@
         <v>9</v>
       </c>
       <c r="E42" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H42" s="9"/>
     </row>
@@ -3231,13 +3219,13 @@
         <v>9</v>
       </c>
       <c r="E43" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H43" s="10"/>
     </row>
@@ -3249,13 +3237,13 @@
         <v>9</v>
       </c>
       <c r="E44" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H44" s="10"/>
     </row>
@@ -3267,13 +3255,13 @@
         <v>9</v>
       </c>
       <c r="E45" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H45" s="9"/>
     </row>
@@ -3285,13 +3273,13 @@
         <v>9</v>
       </c>
       <c r="E46" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H46" s="9"/>
     </row>
@@ -3303,13 +3291,13 @@
         <v>9</v>
       </c>
       <c r="E47" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H47" s="9"/>
     </row>
@@ -3321,13 +3309,13 @@
         <v>9</v>
       </c>
       <c r="E48" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H48" s="9"/>
     </row>
@@ -3339,13 +3327,13 @@
         <v>9</v>
       </c>
       <c r="E49" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H49" s="9"/>
     </row>
@@ -3357,13 +3345,13 @@
         <v>9</v>
       </c>
       <c r="E50" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H50" s="9"/>
     </row>
@@ -3375,13 +3363,13 @@
         <v>9</v>
       </c>
       <c r="E51" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H51" s="9"/>
     </row>
@@ -3393,13 +3381,13 @@
         <v>9</v>
       </c>
       <c r="E52" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H52" s="9"/>
     </row>
@@ -3414,10 +3402,10 @@
         <v>48</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H53" s="11"/>
     </row>
@@ -3432,10 +3420,10 @@
         <v>48</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H54" s="11"/>
     </row>
@@ -3450,10 +3438,10 @@
         <v>48</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H55" s="11"/>
     </row>
@@ -3468,10 +3456,10 @@
         <v>48</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H56" s="11"/>
     </row>
@@ -3486,10 +3474,10 @@
         <v>48</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H57" s="11"/>
     </row>
@@ -3504,10 +3492,10 @@
         <v>48</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H58" s="11"/>
     </row>
@@ -3522,10 +3510,10 @@
         <v>48</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H59" s="11"/>
     </row>
@@ -3540,10 +3528,10 @@
         <v>48</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H60" s="11"/>
     </row>
@@ -3558,10 +3546,10 @@
         <v>48</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H61" s="11"/>
     </row>
@@ -3576,10 +3564,10 @@
         <v>48</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H62" s="11"/>
     </row>
@@ -3594,10 +3582,10 @@
         <v>48</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H63" s="11"/>
     </row>
@@ -3612,10 +3600,10 @@
         <v>48</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H64" s="11"/>
     </row>
@@ -3630,10 +3618,10 @@
         <v>48</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H65" s="11"/>
     </row>
@@ -3648,10 +3636,10 @@
         <v>48</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H66" s="11"/>
     </row>
@@ -3666,10 +3654,10 @@
         <v>48</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H67" s="11"/>
     </row>
@@ -3684,10 +3672,10 @@
         <v>48</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H68" s="11"/>
     </row>
@@ -3699,13 +3687,13 @@
         <v>9</v>
       </c>
       <c r="E69" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H69" s="12"/>
     </row>
@@ -3717,13 +3705,13 @@
         <v>9</v>
       </c>
       <c r="E70" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H70" s="12"/>
     </row>
@@ -3735,13 +3723,13 @@
         <v>9</v>
       </c>
       <c r="E71" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H71" s="12"/>
     </row>
@@ -3753,13 +3741,13 @@
         <v>9</v>
       </c>
       <c r="E72" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H72" s="12"/>
     </row>
@@ -3771,13 +3759,13 @@
         <v>9</v>
       </c>
       <c r="E73" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H73" s="12"/>
     </row>
@@ -3789,13 +3777,13 @@
         <v>9</v>
       </c>
       <c r="E74" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H74" s="12"/>
     </row>
@@ -3807,13 +3795,13 @@
         <v>9</v>
       </c>
       <c r="E75" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H75" s="12"/>
     </row>
@@ -3825,13 +3813,13 @@
         <v>9</v>
       </c>
       <c r="E76" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H76" s="12"/>
     </row>
@@ -3843,13 +3831,13 @@
         <v>9</v>
       </c>
       <c r="E77" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H77" s="12"/>
     </row>
@@ -3861,13 +3849,13 @@
         <v>9</v>
       </c>
       <c r="E78" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H78" s="12"/>
     </row>
@@ -3879,13 +3867,13 @@
         <v>9</v>
       </c>
       <c r="E79" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H79" s="12"/>
     </row>
@@ -3897,13 +3885,13 @@
         <v>9</v>
       </c>
       <c r="E80" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H80" s="12"/>
     </row>
@@ -3915,13 +3903,13 @@
         <v>9</v>
       </c>
       <c r="E81" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H81" s="12"/>
     </row>
@@ -3933,13 +3921,13 @@
         <v>9</v>
       </c>
       <c r="E82" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H82" s="12"/>
     </row>
@@ -3951,13 +3939,13 @@
         <v>9</v>
       </c>
       <c r="E83" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H83" s="12"/>
     </row>
@@ -3969,13 +3957,13 @@
         <v>9</v>
       </c>
       <c r="E84" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H84" s="12"/>
     </row>
@@ -3990,10 +3978,10 @@
         <v>80</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H85" s="7"/>
     </row>
@@ -4008,10 +3996,10 @@
         <v>80</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H86" s="7"/>
     </row>
@@ -4026,10 +4014,10 @@
         <v>80</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H87" s="7"/>
     </row>
@@ -4044,10 +4032,10 @@
         <v>80</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H88" s="7"/>
     </row>
@@ -4062,10 +4050,10 @@
         <v>84</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I89" s="7"/>
     </row>
@@ -4080,10 +4068,10 @@
         <v>80</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H90" s="7"/>
     </row>
@@ -4098,10 +4086,10 @@
         <v>80</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H91" s="7"/>
     </row>
@@ -4116,10 +4104,10 @@
         <v>80</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H92" s="7"/>
     </row>
@@ -4134,10 +4122,10 @@
         <v>80</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H93" s="7"/>
     </row>
@@ -4149,13 +4137,13 @@
         <v>9</v>
       </c>
       <c r="E94" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H94" s="11"/>
     </row>
@@ -4167,13 +4155,13 @@
         <v>9</v>
       </c>
       <c r="E95" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H95" s="11"/>
     </row>
@@ -4185,13 +4173,13 @@
         <v>9</v>
       </c>
       <c r="E96" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H96" s="11"/>
     </row>
@@ -4203,13 +4191,13 @@
         <v>9</v>
       </c>
       <c r="E97" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G97" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H97" s="11"/>
     </row>
@@ -4221,13 +4209,13 @@
         <v>9</v>
       </c>
       <c r="E98" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H98" s="11"/>
     </row>
@@ -4239,13 +4227,13 @@
         <v>9</v>
       </c>
       <c r="E99" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H99" s="11"/>
     </row>
@@ -4257,13 +4245,13 @@
         <v>9</v>
       </c>
       <c r="E100" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H100" s="11"/>
     </row>
@@ -4275,13 +4263,13 @@
         <v>9</v>
       </c>
       <c r="E101" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H101" s="11"/>
     </row>
@@ -4293,13 +4281,13 @@
         <v>9</v>
       </c>
       <c r="E102" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G102" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H102" s="11"/>
     </row>
@@ -4311,13 +4299,13 @@
         <v>9</v>
       </c>
       <c r="E103" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H103" s="11"/>
     </row>
@@ -4329,13 +4317,13 @@
         <v>9</v>
       </c>
       <c r="E104" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H104" s="11"/>
     </row>
@@ -4347,13 +4335,13 @@
         <v>9</v>
       </c>
       <c r="E105" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H105" s="11"/>
     </row>
@@ -4365,13 +4353,13 @@
         <v>9</v>
       </c>
       <c r="E106" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G106" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H106" s="11"/>
     </row>
@@ -4383,13 +4371,13 @@
         <v>9</v>
       </c>
       <c r="E107" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H107" s="11"/>
     </row>
@@ -4401,13 +4389,13 @@
         <v>9</v>
       </c>
       <c r="E108" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H108" s="11"/>
     </row>
@@ -4419,13 +4407,13 @@
         <v>9</v>
       </c>
       <c r="E109" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G109" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H109" s="11"/>
     </row>
@@ -4440,10 +4428,10 @@
         <v>105</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G110" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H110" s="12"/>
     </row>
@@ -4458,10 +4446,10 @@
         <v>105</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H111" s="12"/>
     </row>
@@ -4476,10 +4464,10 @@
         <v>105</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H112" s="12"/>
     </row>
@@ -4494,10 +4482,10 @@
         <v>105</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H113" s="12"/>
     </row>
@@ -4512,10 +4500,10 @@
         <v>105</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G114" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H114" s="12"/>
     </row>
@@ -4530,10 +4518,10 @@
         <v>105</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H115" s="12"/>
     </row>
@@ -4548,10 +4536,10 @@
         <v>105</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G116" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H116" s="12"/>
     </row>
@@ -4566,10 +4554,10 @@
         <v>105</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G117" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H117" s="12"/>
     </row>
@@ -4584,10 +4572,10 @@
         <v>105</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H118" s="12"/>
     </row>
@@ -4602,10 +4590,10 @@
         <v>105</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G119" s="13" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H119" s="12"/>
     </row>
@@ -4620,10 +4608,10 @@
         <v>105</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G120" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H120" s="12"/>
     </row>
@@ -4638,10 +4626,10 @@
         <v>105</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G121" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="H121" s="12"/>
     </row>
@@ -4656,10 +4644,10 @@
         <v>105</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G122" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H122" s="12"/>
     </row>
@@ -4674,10 +4662,10 @@
         <v>105</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G123" s="13" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H123" s="12"/>
     </row>
@@ -4692,10 +4680,10 @@
         <v>105</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G124" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H124" s="12"/>
     </row>
@@ -4710,10 +4698,10 @@
         <v>105</v>
       </c>
       <c r="F125" s="6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G125" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H125" s="12"/>
     </row>
@@ -4725,13 +4713,13 @@
         <v>9</v>
       </c>
       <c r="E126" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G126" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H126" s="11"/>
     </row>
@@ -4743,13 +4731,13 @@
         <v>9</v>
       </c>
       <c r="E127" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G127" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H127" s="11"/>
     </row>
@@ -4761,13 +4749,13 @@
         <v>9</v>
       </c>
       <c r="E128" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G128" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H128" s="11"/>
     </row>
@@ -4779,13 +4767,13 @@
         <v>9</v>
       </c>
       <c r="E129" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G129" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H129" s="11"/>
     </row>
@@ -4797,13 +4785,13 @@
         <v>9</v>
       </c>
       <c r="E130" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F130" s="6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G130" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H130" s="14"/>
     </row>
@@ -4815,13 +4803,13 @@
         <v>9</v>
       </c>
       <c r="E131" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G131" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H131" s="14"/>
     </row>
@@ -4833,13 +4821,13 @@
         <v>9</v>
       </c>
       <c r="E132" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G132" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H132" s="14"/>
     </row>
@@ -4854,10 +4842,10 @@
         <v>128</v>
       </c>
       <c r="F133" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G133" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="I133" s="12"/>
     </row>
@@ -4869,13 +4857,13 @@
         <v>9</v>
       </c>
       <c r="E134" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G134" s="13" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="H134" s="14"/>
     </row>
@@ -4887,13 +4875,13 @@
         <v>9</v>
       </c>
       <c r="E135" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F135" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G135" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="H135" s="14"/>
     </row>
@@ -4905,13 +4893,13 @@
         <v>9</v>
       </c>
       <c r="E136" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="H136" s="11"/>
     </row>
@@ -4923,13 +4911,13 @@
         <v>9</v>
       </c>
       <c r="E137" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G137" s="13" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H137" s="11"/>
     </row>
@@ -4941,13 +4929,13 @@
         <v>9</v>
       </c>
       <c r="E138" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G138" s="13" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H138" s="11"/>
     </row>
@@ -4959,13 +4947,13 @@
         <v>9</v>
       </c>
       <c r="E139" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F139" s="6" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G139" s="13" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H139" s="11"/>
     </row>
@@ -4977,13 +4965,13 @@
         <v>9</v>
       </c>
       <c r="E140" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F140" s="6" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G140" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H140" s="11"/>
     </row>
@@ -4995,13 +4983,13 @@
         <v>9</v>
       </c>
       <c r="E141" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F141" s="6" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G141" s="13" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H141" s="11"/>
     </row>
@@ -5013,13 +5001,13 @@
         <v>9</v>
       </c>
       <c r="E142" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F142" s="6" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G142" s="13" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H142" s="11"/>
     </row>
@@ -5031,13 +5019,13 @@
         <v>9</v>
       </c>
       <c r="E143" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F143" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G143" s="13" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="H143" s="11"/>
     </row>
@@ -5052,10 +5040,10 @@
         <v>139</v>
       </c>
       <c r="F144" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G144" s="13" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="H144" s="15"/>
     </row>
@@ -5070,10 +5058,10 @@
         <v>139</v>
       </c>
       <c r="F145" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G145" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H145" s="15"/>
     </row>
@@ -5088,10 +5076,10 @@
         <v>139</v>
       </c>
       <c r="F146" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G146" s="13" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H146" s="15"/>
     </row>
@@ -5106,10 +5094,10 @@
         <v>139</v>
       </c>
       <c r="F147" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G147" s="13" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H147" s="15"/>
     </row>
@@ -5124,10 +5112,10 @@
         <v>139</v>
       </c>
       <c r="F148" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G148" s="13" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="H148" s="12"/>
     </row>
@@ -5142,10 +5130,10 @@
         <v>139</v>
       </c>
       <c r="F149" s="6" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G149" s="13" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="H149" s="12"/>
     </row>
@@ -5160,10 +5148,10 @@
         <v>139</v>
       </c>
       <c r="F150" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G150" s="13" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H150" s="12"/>
     </row>
@@ -5178,10 +5166,10 @@
         <v>139</v>
       </c>
       <c r="F151" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G151" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H151" s="12"/>
     </row>
@@ -5196,10 +5184,10 @@
         <v>139</v>
       </c>
       <c r="F152" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G152" s="13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H152" s="12"/>
     </row>
@@ -5214,10 +5202,10 @@
         <v>139</v>
       </c>
       <c r="F153" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G153" s="13" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H153" s="12"/>
     </row>
@@ -5232,10 +5220,10 @@
         <v>139</v>
       </c>
       <c r="F154" s="6" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G154" s="13" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H154" s="12"/>
     </row>
@@ -5250,10 +5238,10 @@
         <v>139</v>
       </c>
       <c r="F155" s="6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G155" s="13" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H155" s="12"/>
     </row>
@@ -5268,10 +5256,10 @@
         <v>139</v>
       </c>
       <c r="F156" s="6" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G156" s="13" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="H156" s="12"/>
     </row>
@@ -5286,10 +5274,10 @@
         <v>139</v>
       </c>
       <c r="F157" s="6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G157" s="13" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="H157" s="12"/>
     </row>
@@ -5304,10 +5292,10 @@
         <v>139</v>
       </c>
       <c r="F158" s="6" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G158" s="13" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H158" s="12"/>
     </row>
@@ -5322,10 +5310,10 @@
         <v>139</v>
       </c>
       <c r="F159" s="6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G159" s="13" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H159" s="12"/>
     </row>
@@ -5337,13 +5325,13 @@
         <v>9</v>
       </c>
       <c r="E160" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F160" s="6" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G160" s="13" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H160" s="11"/>
     </row>
@@ -5355,13 +5343,13 @@
         <v>9</v>
       </c>
       <c r="E161" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F161" s="6" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G161" s="13" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H161" s="11"/>
     </row>
@@ -5373,13 +5361,13 @@
         <v>9</v>
       </c>
       <c r="E162" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F162" s="6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G162" s="13" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H162" s="11"/>
     </row>
@@ -5391,13 +5379,13 @@
         <v>9</v>
       </c>
       <c r="E163" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F163" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G163" s="13" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H163" s="11"/>
     </row>
@@ -5409,13 +5397,13 @@
         <v>9</v>
       </c>
       <c r="E164" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F164" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G164" s="13" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H164" s="11"/>
     </row>
@@ -5427,13 +5415,13 @@
         <v>9</v>
       </c>
       <c r="E165" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F165" s="6" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G165" s="13" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H165" s="11"/>
     </row>
@@ -5445,13 +5433,13 @@
         <v>9</v>
       </c>
       <c r="E166" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F166" s="6" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G166" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H166" s="11"/>
     </row>
@@ -5463,13 +5451,13 @@
         <v>9</v>
       </c>
       <c r="E167" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F167" s="6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G167" s="13" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="H167" s="11"/>
     </row>
@@ -5481,13 +5469,13 @@
         <v>9</v>
       </c>
       <c r="E168" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F168" s="6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G168" s="13" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="H168" s="11"/>
     </row>
@@ -5499,13 +5487,13 @@
         <v>9</v>
       </c>
       <c r="E169" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F169" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G169" s="13" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H169" s="11"/>
     </row>
@@ -5517,13 +5505,13 @@
         <v>9</v>
       </c>
       <c r="E170" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F170" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G170" s="13" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H170" s="11"/>
     </row>
@@ -5535,13 +5523,13 @@
         <v>9</v>
       </c>
       <c r="E171" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F171" s="6" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G171" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H171" s="11"/>
     </row>
@@ -5553,13 +5541,13 @@
         <v>9</v>
       </c>
       <c r="E172" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F172" s="6" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G172" s="13" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="H172" s="11"/>
     </row>
@@ -5571,13 +5559,13 @@
         <v>9</v>
       </c>
       <c r="E173" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F173" s="6" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G173" s="13" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H173" s="11"/>
     </row>
@@ -5589,13 +5577,13 @@
         <v>9</v>
       </c>
       <c r="E174" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F174" s="6" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G174" s="13" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H174" s="11"/>
     </row>
@@ -5607,13 +5595,13 @@
         <v>9</v>
       </c>
       <c r="E175" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F175" s="6" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G175" s="13" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H175" s="11"/>
     </row>
@@ -5628,10 +5616,10 @@
         <v>172</v>
       </c>
       <c r="F176" s="6" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G176" s="13" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H176" s="7"/>
     </row>
@@ -5646,10 +5634,10 @@
         <v>172</v>
       </c>
       <c r="F177" s="6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G177" s="13" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H177" s="7"/>
     </row>
@@ -5664,10 +5652,10 @@
         <v>172</v>
       </c>
       <c r="F178" s="6" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G178" s="13" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="H178" s="7"/>
     </row>
@@ -5682,10 +5670,10 @@
         <v>172</v>
       </c>
       <c r="F179" s="6" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G179" s="13" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H179" s="7"/>
     </row>
@@ -5700,10 +5688,10 @@
         <v>172</v>
       </c>
       <c r="F180" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G180" s="13" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H180" s="7"/>
     </row>
@@ -5718,10 +5706,10 @@
         <v>172</v>
       </c>
       <c r="F181" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G181" s="13" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H181" s="7"/>
     </row>
@@ -5736,10 +5724,10 @@
         <v>172</v>
       </c>
       <c r="F182" s="6" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G182" s="13" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="H182" s="7"/>
     </row>
@@ -5754,10 +5742,10 @@
         <v>172</v>
       </c>
       <c r="F183" s="6" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G183" s="13" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="H183" s="7"/>
     </row>
@@ -5769,13 +5757,13 @@
         <v>9</v>
       </c>
       <c r="E184" s="6">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F184" s="6" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G184" s="13" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H184" s="12"/>
     </row>
@@ -5787,13 +5775,13 @@
         <v>9</v>
       </c>
       <c r="E185" s="6">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F185" s="6" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G185" s="13" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="H185" s="12"/>
     </row>
@@ -5805,13 +5793,13 @@
         <v>9</v>
       </c>
       <c r="E186" s="6">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F186" s="6" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G186" s="16" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H186" s="12"/>
     </row>
@@ -5823,13 +5811,13 @@
         <v>9</v>
       </c>
       <c r="E187" s="6">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F187" s="6" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G187" s="13" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="H187" s="12"/>
     </row>
@@ -5841,13 +5829,13 @@
         <v>9</v>
       </c>
       <c r="E188" s="6">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F188" s="6" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G188" s="13" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="H188" s="12"/>
     </row>
@@ -5859,13 +5847,13 @@
         <v>9</v>
       </c>
       <c r="E189" s="6">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F189" s="6" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G189" s="16" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="H189" s="12"/>
     </row>
@@ -5877,13 +5865,13 @@
         <v>9</v>
       </c>
       <c r="E190" s="6">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F190" s="6" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="G190" s="16" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="H190" s="12"/>
     </row>
@@ -5895,13 +5883,13 @@
         <v>9</v>
       </c>
       <c r="E191" s="6">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F191" s="6" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="G191" s="16" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="H191" s="12"/>
     </row>
@@ -5916,10 +5904,10 @@
         <v>188</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G192" s="13" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="H192" s="7"/>
     </row>
@@ -5934,10 +5922,10 @@
         <v>188</v>
       </c>
       <c r="F193" s="6" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G193" s="13" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="H193" s="7"/>
     </row>
@@ -5952,10 +5940,10 @@
         <v>188</v>
       </c>
       <c r="F194" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G194" s="16" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="H194" s="7"/>
     </row>
@@ -5970,10 +5958,10 @@
         <v>188</v>
       </c>
       <c r="F195" s="6" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G195" s="16" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H195" s="7"/>
     </row>
@@ -5988,10 +5976,10 @@
         <v>188</v>
       </c>
       <c r="F196" s="6" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G196" s="13" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H196" s="7"/>
     </row>
@@ -6006,10 +5994,10 @@
         <v>188</v>
       </c>
       <c r="F197" s="6" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G197" s="16" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="H197" s="7"/>
     </row>
@@ -6024,10 +6012,10 @@
         <v>188</v>
       </c>
       <c r="F198" s="6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="G198" s="16" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="H198" s="7"/>
     </row>
@@ -6042,10 +6030,10 @@
         <v>188</v>
       </c>
       <c r="F199" s="6" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="G199" s="16" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="H199" s="7"/>
     </row>
@@ -6060,10 +6048,10 @@
         <v>196</v>
       </c>
       <c r="F200" s="6" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G200" s="16" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H200" s="9"/>
     </row>
@@ -6078,10 +6066,10 @@
         <v>196</v>
       </c>
       <c r="F201" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G201" s="16" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H201" s="9"/>
     </row>
@@ -6096,10 +6084,10 @@
         <v>196</v>
       </c>
       <c r="F202" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G202" s="16" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H202" s="9"/>
     </row>
@@ -6114,10 +6102,10 @@
         <v>196</v>
       </c>
       <c r="F203" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="G203" s="16" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="H203" s="9"/>
     </row>
@@ -6129,13 +6117,13 @@
         <v>9</v>
       </c>
       <c r="E204" s="6">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F204" s="6" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G204" s="16" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H204" s="11"/>
     </row>
@@ -6150,10 +6138,10 @@
         <v>202</v>
       </c>
       <c r="F205" s="18" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="I205" s="12"/>
     </row>
@@ -6168,16 +6156,16 @@
         <v>203</v>
       </c>
       <c r="F206" s="18" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="I206" s="12"/>
     </row>
     <row r="207" spans="1:9">
       <c r="A207" s="3" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C207" s="4">
         <v>211</v>
@@ -6186,13 +6174,13 @@
         <v>9</v>
       </c>
       <c r="E207" s="6">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F207" s="6" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G207" s="16" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H207" s="11"/>
     </row>
@@ -6204,13 +6192,13 @@
         <v>9</v>
       </c>
       <c r="E208" s="6">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F208" s="6" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="G208" s="16" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="H208" s="11"/>
     </row>
@@ -6222,13 +6210,13 @@
         <v>9</v>
       </c>
       <c r="E209" s="6">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F209" s="6" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="G209" s="16" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="H209" s="11"/>
     </row>
@@ -6243,10 +6231,10 @@
         <v>214</v>
       </c>
       <c r="F210" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="G210" s="16" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H210" s="19"/>
     </row>
@@ -6261,10 +6249,10 @@
         <v>214</v>
       </c>
       <c r="F211" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="G211" s="16" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H211" s="19"/>
     </row>
@@ -6276,13 +6264,13 @@
         <v>9</v>
       </c>
       <c r="E212" s="6">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F212" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="G212" s="16" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H212" s="12"/>
     </row>
@@ -6294,13 +6282,13 @@
         <v>9</v>
       </c>
       <c r="E213" s="6">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F213" s="6" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="G213" s="16" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H213" s="12"/>
     </row>
@@ -6315,10 +6303,10 @@
         <v>218</v>
       </c>
       <c r="F214" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="G214" s="16" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H214" s="11"/>
     </row>
@@ -6333,10 +6321,10 @@
         <v>218</v>
       </c>
       <c r="F215" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="G215" s="16" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="H215" s="11"/>
     </row>
@@ -6348,13 +6336,13 @@
         <v>9</v>
       </c>
       <c r="E216" s="6">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F216" s="6" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="G216" s="13" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="H216" s="9"/>
     </row>
@@ -6366,13 +6354,13 @@
         <v>9</v>
       </c>
       <c r="E217" s="6">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F217" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="G217" s="16" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H217" s="9"/>
     </row>
@@ -6387,10 +6375,10 @@
         <v>222</v>
       </c>
       <c r="F218" s="6" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="G218" s="16" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H218" s="11"/>
     </row>
@@ -6405,10 +6393,10 @@
         <v>222</v>
       </c>
       <c r="F219" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G219" s="13" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H219" s="11"/>
     </row>
@@ -6423,10 +6411,10 @@
         <v>224</v>
       </c>
       <c r="F220" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G220" s="16" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="221" spans="3:8">
@@ -6437,13 +6425,13 @@
         <v>9</v>
       </c>
       <c r="E221" s="6">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F221" s="6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="G221" s="13" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="222" spans="3:8">
@@ -6457,10 +6445,10 @@
         <v>226</v>
       </c>
       <c r="F222" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G222" s="16" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="223" spans="3:8">
@@ -6471,13 +6459,13 @@
         <v>9</v>
       </c>
       <c r="E223" s="6">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F223" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="G223" s="16" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="224" spans="3:8">
@@ -6491,10 +6479,10 @@
         <v>228</v>
       </c>
       <c r="F224" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="G224" s="13" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="225" spans="3:7">
@@ -6505,13 +6493,13 @@
         <v>9</v>
       </c>
       <c r="E225" s="6">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F225" s="6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="G225" s="13" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="226" spans="3:7">
@@ -6525,10 +6513,10 @@
         <v>230</v>
       </c>
       <c r="F226" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="G226" s="13" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="227" spans="3:7">
@@ -6539,13 +6527,13 @@
         <v>9</v>
       </c>
       <c r="E227" s="6">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F227" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="G227" s="13" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="228" spans="3:7">
@@ -6559,10 +6547,10 @@
         <v>232</v>
       </c>
       <c r="F228" s="6" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="G228" s="13" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="229" spans="3:7">
@@ -6576,10 +6564,10 @@
         <v>233</v>
       </c>
       <c r="F229" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="G229" s="13" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="230" spans="3:7">
@@ -6593,10 +6581,10 @@
         <v>234</v>
       </c>
       <c r="F230" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="G230" s="13" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="231" spans="3:7">
@@ -6610,7 +6598,7 @@
         <v>235</v>
       </c>
       <c r="F231" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="G231" s="13"/>
     </row>
